--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -7830,11 +7830,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Headspace volumes of CO2 per pulse; &gt;=1 flushes, 1.3 = full sweep + margin.</t>
+          <t>Headspace volumes of CO₂ per pulse. 1.0 = exactly one headspace flush (the minimum that fully sweeps it). Raise for margin.</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="D36">
-        <f>MAXIFS('CO2 flows'!$O$4:$O$50,'CO2 flows'!$N$4:$N$50,Reactor)</f>
+        <f>SUMPRODUCT(MAX(('CO2 flows'!$N$4:$N$50=Reactor)*'CO2 flows'!$O$4:$O$50))</f>
         <v/>
       </c>
       <c r="E36" t="inlineStr">
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="D37">
-        <f>LOOKUP(2,1/(('CO2 flows'!$N$4:$N$50=Reactor)*('CO2 flows'!$O$4:$O$50=latest_date)),'CO2 flows'!$P$4:$P$50)</f>
+        <f>SUMPRODUCT(('CO2 flows'!$N$4:$N$50=Reactor)*('CO2 flows'!$O$4:$O$50=latest_date)*'CO2 flows'!$P$4:$P$50)</f>
         <v/>
       </c>
       <c r="E37" t="inlineStr">
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="D38">
-        <f>LOOKUP(2,1/(('CO2 flows'!$N$4:$N$50=Reactor)*('CO2 flows'!$O$4:$O$50=latest_date)),'CO2 flows'!$Q$4:$Q$50)</f>
+        <f>SUMPRODUCT(('CO2 flows'!$N$4:$N$50=Reactor)*('CO2 flows'!$O$4:$O$50=latest_date)*'CO2 flows'!$Q$4:$Q$50)</f>
         <v/>
       </c>
       <c r="E38" t="inlineStr">

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -270,7 +270,7 @@
     <numFmt numFmtId="171" formatCode="0.0000000"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -404,6 +404,10 @@
     <font>
       <i val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="17">
@@ -599,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -707,6 +711,8 @@
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1057,7 +1063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1454,8 +1460,83 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="29" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="73" t="inlineStr">
+        <is>
+          <t>EXPERIMENT SELECTORS  (dropdowns auto-extend from the lookup tables; wired to calcs next stage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Reactor</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Reactor_sel</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Electrode</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>electrode_sel</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MMO tube</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HOB organism</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>organism_sel</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Cupriavidus necator</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>media_sel</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sydow 2017 minimal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="7">
     <dataValidation sqref="D3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"AEP0.1.1,AEP0.2"</formula1>
     </dataValidation>
@@ -1464,6 +1545,18 @@
     </dataValidation>
     <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"0,1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Geometry!$A$53:$A$82</formula1>
+    </dataValidation>
+    <dataValidation sqref="D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Electrochemistry!$A$32:$A$40</formula1>
+    </dataValidation>
+    <dataValidation sqref="D35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Biology!$A$47:$A$60</formula1>
+    </dataValidation>
+    <dataValidation sqref="D36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Biology!$A$56:$A$64</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1478,7 +1571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2652,6 +2745,482 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>From Summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="73" t="inlineStr">
+        <is>
+          <t>REACTOR LOOKUP  (reactor ID → type)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="69" t="inlineStr">
+        <is>
+          <t>Reactor</t>
+        </is>
+      </c>
+      <c r="B52" s="69" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>imp01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AEP0.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>imp02</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AEP0.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>imp03</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AEP0.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>imp04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AEP0.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>imp05</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AEP0.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>imp06</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AEP0.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ed01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AEP0.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ed02</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AEP0.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ed03</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AEP0.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MEP0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ed05</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MEP0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ed06</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AEP0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ed07</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AEP0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ed08</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AEP0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>imp07</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AEP0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>imp08</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AEP0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>imp09</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AEP0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>imp10</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>AEP0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>imp11</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>AEP0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>imp12</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AEP0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>nm01</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>AEP0.2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>nm02</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AEP0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="73" t="inlineStr">
+        <is>
+          <t>REACTOR-TYPE LOOKUP  (geometry &amp; stir bar; pulled by type)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="69" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B77" s="69" t="inlineStr">
+        <is>
+          <t>Pioreactor</t>
+        </is>
+      </c>
+      <c r="C77" s="69" t="inlineStr">
+        <is>
+          <t>vial (mL)</t>
+        </is>
+      </c>
+      <c r="D77" s="69" t="inlineStr">
+        <is>
+          <t>usable depth (mm)</t>
+        </is>
+      </c>
+      <c r="E77" s="69" t="inlineStr">
+        <is>
+          <t>max working (mL)</t>
+        </is>
+      </c>
+      <c r="F77" s="69" t="inlineStr">
+        <is>
+          <t>total vial (mL)</t>
+        </is>
+      </c>
+      <c r="G77" s="69" t="inlineStr">
+        <is>
+          <t>vial OD (mm)</t>
+        </is>
+      </c>
+      <c r="H77" s="69" t="inlineStr">
+        <is>
+          <t>stir bar L (mm)</t>
+        </is>
+      </c>
+      <c r="I77" s="69" t="inlineStr">
+        <is>
+          <t>stir bar dia (mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>AEP0.1.1</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>20</v>
+      </c>
+      <c r="D78" t="n">
+        <v>55</v>
+      </c>
+      <c r="E78" t="n">
+        <v>16</v>
+      </c>
+      <c r="F78" t="n">
+        <v>20</v>
+      </c>
+      <c r="G78" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="H78" t="n">
+        <v>12</v>
+      </c>
+      <c r="I78" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MEP0.3</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>20</v>
+      </c>
+      <c r="D79" t="n">
+        <v>55</v>
+      </c>
+      <c r="E79" t="n">
+        <v>16</v>
+      </c>
+      <c r="F79" t="n">
+        <v>20</v>
+      </c>
+      <c r="G79" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="H79" t="n">
+        <v>12</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>AEP0.2</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>40</v>
+      </c>
+      <c r="D80" t="n">
+        <v>95</v>
+      </c>
+      <c r="E80" t="n">
+        <v>30</v>
+      </c>
+      <c r="F80" t="n">
+        <v>42</v>
+      </c>
+      <c r="G80" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="H80" t="n">
+        <v>15</v>
+      </c>
+      <c r="I80" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AEP0.2a</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>40</v>
+      </c>
+      <c r="D81" t="n">
+        <v>95</v>
+      </c>
+      <c r="E81" t="n">
+        <v>30</v>
+      </c>
+      <c r="F81" t="n">
+        <v>42</v>
+      </c>
+      <c r="G81" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="H81" t="n">
+        <v>15</v>
+      </c>
+      <c r="I81" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="72" t="inlineStr">
+        <is>
+          <t>40 mL OD = 20 mL diameter (Pioreactor source); depths/volumes confirm by measurement.</t>
         </is>
       </c>
     </row>
@@ -2667,7 +3236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3300,6 +3869,190 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>From Dosing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="73" t="inlineStr">
+        <is>
+          <t>ELECTRODE LOOKUP  (selecting the electrode sets sparger, porosity, cathode)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="69" t="inlineStr">
+        <is>
+          <t>Electrode</t>
+        </is>
+      </c>
+      <c r="B31" s="69" t="inlineStr">
+        <is>
+          <t>anode material</t>
+        </is>
+      </c>
+      <c r="C31" s="69" t="inlineStr">
+        <is>
+          <t>anode dia (mm)</t>
+        </is>
+      </c>
+      <c r="D31" s="69" t="inlineStr">
+        <is>
+          <t>sparger</t>
+        </is>
+      </c>
+      <c r="E31" s="69" t="inlineStr">
+        <is>
+          <t>sinter porosity</t>
+        </is>
+      </c>
+      <c r="F31" s="69" t="inlineStr">
+        <is>
+          <t>cathode</t>
+        </is>
+      </c>
+      <c r="G31" s="69" t="inlineStr">
+        <is>
+          <t>cathode dia (mm)</t>
+        </is>
+      </c>
+      <c r="H31" s="69" t="inlineStr">
+        <is>
+          <t>etaF</t>
+        </is>
+      </c>
+      <c r="I31" s="69" t="inlineStr">
+        <is>
+          <t>z_e_ORR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Pt/Ti rod</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pt/Ti</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Tube</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SS rod</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" s="74" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MMO rod</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Tube</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SS rod</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" s="74" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MMO tube</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sintered</t>
+        </is>
+      </c>
+      <c r="E34" s="74" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SS rod</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" s="74" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="72" t="inlineStr">
+        <is>
+          <t>z_e_ORR=2 assumed (peroxide, non-Pt SS cathode, neutral pH); etaF unmeasured - both live here per electrode.</t>
         </is>
       </c>
     </row>
@@ -3323,7 +4076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4341,6 +5094,290 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>From Geometry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="73" t="inlineStr">
+        <is>
+          <t>HOB LOOKUP  (dissolved O₂ thresholds, mg/L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="69" t="inlineStr">
+        <is>
+          <t>Organism</t>
+        </is>
+      </c>
+      <c r="B46" s="69" t="inlineStr">
+        <is>
+          <t>minimum DO</t>
+        </is>
+      </c>
+      <c r="C46" s="69" t="inlineStr">
+        <is>
+          <t>optimum DO</t>
+        </is>
+      </c>
+      <c r="D46" s="69" t="inlineStr">
+        <is>
+          <t>impairment DO</t>
+        </is>
+      </c>
+      <c r="E46" s="69" t="inlineStr">
+        <is>
+          <t>toxic DO</t>
+        </is>
+      </c>
+      <c r="F46" s="69" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Cupriavidus necator</t>
+        </is>
+      </c>
+      <c r="B47" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Amer &amp; Kim 2023; Wilde &amp; Schlegel 1982</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Xanthobacter autotrophicus</t>
+        </is>
+      </c>
+      <c r="B48" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C48" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D48" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Wilde &amp; Schlegel 1982 (~0.30 atm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Xanthobacter flavus</t>
+        </is>
+      </c>
+      <c r="B49" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C49" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D49" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="E49" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>no species data — assume genus ~11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Xanthobacter tagetidis</t>
+        </is>
+      </c>
+      <c r="B50" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C50" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D50" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="E50" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>no species data — assume genus ~11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Cupriavidus metallidurans</t>
+        </is>
+      </c>
+      <c r="B51" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C51" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D51" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="E51" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>no species data — assume genus ~11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>UdG (mixed)</t>
+        </is>
+      </c>
+      <c r="B52" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C52" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D52" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="E52" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Rovira-Alsina 2025; Pous 2022/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="73" t="inlineStr">
+        <is>
+          <t>MEDIA LOOKUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="69" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B55" s="69" t="inlineStr">
+        <is>
+          <t>buffer</t>
+        </is>
+      </c>
+      <c r="C55" s="69" t="inlineStr">
+        <is>
+          <t>buffer conc (mM)</t>
+        </is>
+      </c>
+      <c r="D55" s="69" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="E55" s="69" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sydow 2017 minimal</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>phosphate</t>
+        </is>
+      </c>
+      <c r="C56" s="74" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>low-chloride, organic-free</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Sydow et al. 2017</t>
         </is>
       </c>
     </row>
@@ -7855,7 +8892,7 @@
         </is>
       </c>
       <c r="D36">
-        <f>SUMPRODUCT(MAX(('CO2 flows'!$N$4:$N$50=Reactor)*'CO2 flows'!$O$4:$O$50))</f>
+        <f>SUMPRODUCT(MAX(('CO2 flows'!$A$51:$A$80=Reactor)*'CO2 flows'!$B$51:$B$80))</f>
         <v/>
       </c>
       <c r="E36" t="inlineStr">
@@ -7881,7 +8918,7 @@
         </is>
       </c>
       <c r="D37">
-        <f>SUMPRODUCT(('CO2 flows'!$N$4:$N$50=Reactor)*('CO2 flows'!$O$4:$O$50=latest_date)*'CO2 flows'!$P$4:$P$50)</f>
+        <f>SUMPRODUCT(('CO2 flows'!$A$51:$A$80=Reactor)*('CO2 flows'!$B$51:$B$80=latest_date)*'CO2 flows'!$C$51:$C$80)</f>
         <v/>
       </c>
       <c r="E37" t="inlineStr">
@@ -7907,7 +8944,7 @@
         </is>
       </c>
       <c r="D38">
-        <f>SUMPRODUCT(('CO2 flows'!$N$4:$N$50=Reactor)*('CO2 flows'!$O$4:$O$50=latest_date)*'CO2 flows'!$Q$4:$Q$50)</f>
+        <f>SUMPRODUCT(('CO2 flows'!$A$51:$A$80=Reactor)*('CO2 flows'!$B$51:$B$80=latest_date)*'CO2 flows'!$D$51:$D$80)</f>
         <v/>
       </c>
       <c r="E38" t="inlineStr">
@@ -7954,7 +8991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="9"/>
@@ -8019,11 +9056,7 @@
           <t>KEY</t>
         </is>
       </c>
-      <c r="N2" s="69" t="inlineStr">
-        <is>
-          <t>CALIBRATION SUMMARY (model lookup source)</t>
-        </is>
-      </c>
+      <c r="N2" s="69" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="58" t="n"/>
@@ -8068,26 +9101,10 @@
           <t>Flowrate set by inspection, as maximum to not give bubbles rising into vial neck</t>
         </is>
       </c>
-      <c r="N3" s="69" t="inlineStr">
-        <is>
-          <t>Reactor</t>
-        </is>
-      </c>
-      <c r="O3" s="69" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="P3" s="69" t="inlineStr">
-        <is>
-          <t>Flowrate</t>
-        </is>
-      </c>
-      <c r="Q3" s="69" t="inlineStr">
-        <is>
-          <t>Min sparge</t>
-        </is>
-      </c>
+      <c r="N3" s="69" t="n"/>
+      <c r="O3" s="69" t="n"/>
+      <c r="P3" s="69" t="n"/>
+      <c r="Q3" s="69" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8109,20 +9126,8 @@
           <t>First or last data point removed as suspect outlier</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="O4" s="70" t="n">
-        <v>46190</v>
-      </c>
-      <c r="P4" s="71" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="O4" s="70" t="n"/>
+      <c r="P4" s="71" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8154,11 +9159,7 @@
         <f>AVERAGE(G5)</f>
         <v/>
       </c>
-      <c r="N5" s="72" t="inlineStr">
-        <is>
-          <t>(add a row per reactor/date as calibrations are collected)</t>
-        </is>
-      </c>
+      <c r="N5" s="72" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8226,11 +9227,7 @@
           <t>CO2 collected in measuring cyclinder over CO2-saturated water</t>
         </is>
       </c>
-      <c r="N7" s="69" t="inlineStr">
-        <is>
-          <t>Min sparge justification:</t>
-        </is>
-      </c>
+      <c r="N7" s="69" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8266,11 +9263,6 @@
           <t>Collected using inlet CO2 tube rather than outlet as MEP vialcap leaking</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0.25 s. Deliveries are exactly repeatable at 0.25 s (1 ml every shot) and at 0.5 s (2 ml). At 0.2 s and below the per-pulse flowrate is erratic (2-6 ml/s): the ~0.4 ml fixed open/close bolus and millisecond timing jitter dominate, so dosing stops being linear or repeatable. Flowrate 3.33 ml/s = inspection-set max (no bubbles into the vial neck), confirmed by the long-pulse calibration slope.</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9281,6 +10273,72 @@
     </row>
     <row r="47">
       <c r="B47" s="66" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="73" t="inlineStr">
+        <is>
+          <t>CALIBRATION SUMMARY (model lookup source — latest date per reactor is used)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="69" t="inlineStr">
+        <is>
+          <t>Reactor</t>
+        </is>
+      </c>
+      <c r="B50" s="69" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C50" s="69" t="inlineStr">
+        <is>
+          <t>Flowrate (ml/s)</t>
+        </is>
+      </c>
+      <c r="D50" s="69" t="inlineStr">
+        <is>
+          <t>Min sparge (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B51" s="70" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="72" t="inlineStr">
+        <is>
+          <t>(add a row per reactor/date as calibrations are collected)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="73" t="inlineStr">
+        <is>
+          <t>Min sparge justification</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0.25 s. Repeatable at 0.25 s (1 ml/shot) and 0.5 s (2 ml); at &lt;=0.2 s the per-pulse flowrate is erratic (2-6 ml/s) - the ~0.4 ml fixed open/close bolus and timing jitter dominate. Flowrate 3.33 ml/s = inspection-set max (no bubbles into the neck), confirmed by the long-pulse slope.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H5:H46">

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -37,7 +37,6 @@
     <definedName name="interface_A" localSheetId="1">Geometry!$D$39</definedName>
     <definedName name="rod_d" localSheetId="1">Geometry!$D$21</definedName>
     <definedName name="rod_n" localSheetId="1">Geometry!$D$22</definedName>
-    <definedName name="rx_ver" localSheetId="1">Geometry!$D$48</definedName>
     <definedName name="sparge_depth" localSheetId="1">Geometry!$D$38</definedName>
     <definedName name="spg_disp" localSheetId="1">Geometry!$D$32</definedName>
     <definedName name="spg_ID" localSheetId="1">Geometry!$D$26</definedName>
@@ -62,6 +61,9 @@
     <definedName name="xtube_n" localSheetId="1">Geometry!$D$41</definedName>
     <definedName name="xtube_OD" localSheetId="1">Geometry!$D$40</definedName>
     <definedName name="xtube_pro" localSheetId="1">Geometry!$D$42</definedName>
+    <definedName name="reactor_sel" localSheetId="1">Geometry!$D$48</definedName>
+    <definedName name="rx_ver" localSheetId="1">Geometry!$D$49</definedName>
+    <definedName name="stir_bar_L" localSheetId="1">Geometry!$D$50</definedName>
     <definedName name="etaF" localSheetId="2">Electrochemistry!$D$11</definedName>
     <definedName name="etaF_OER" localSheetId="2">Electrochemistry!$D$19</definedName>
     <definedName name="F_const" localSheetId="2">Electrochemistry!$D$8</definedName>
@@ -252,6 +254,9 @@
     <definedName name="latest_date" localSheetId="5">Dosing!$D$36</definedName>
     <definedName name="flowrate_cal" localSheetId="5">Dosing!$D$37</definedName>
     <definedName name="min_sparge_cal" localSheetId="5">Dosing!$D$38</definedName>
+    <definedName name="cal_exact_n" localSheetId="5">Dosing!$D$39</definedName>
+    <definedName name="cal_type" localSheetId="5">Dosing!$D$40</definedName>
+    <definedName name="cal_warning" localSheetId="5">Dosing!$D$41</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -270,7 +275,7 @@
     <numFmt numFmtId="171" formatCode="0.0000000"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -409,6 +414,9 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <color rgb="FF000000"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -501,7 +509,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -599,11 +607,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="7"/>
+      </left>
+      <right style="medium">
+        <color theme="7"/>
+      </right>
+      <top style="medium">
+        <color theme="7"/>
+      </top>
+      <bottom style="medium">
+        <color theme="7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="9"/>
+      </left>
+      <right style="medium">
+        <color theme="9"/>
+      </right>
+      <top style="medium">
+        <color theme="9"/>
+      </top>
+      <bottom style="medium">
+        <color theme="9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -713,6 +763,13 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1109,7 +1166,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Reactor version</t>
+          <t>Reactor version (resolved from reactor)</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -1122,10 +1179,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
-        <is>
-          <t>AEP0.1.1</t>
-        </is>
+      <c r="D3" s="75">
+        <f>Geometry!$D$49</f>
+        <v/>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
@@ -1382,6 +1438,17 @@
         <is>
           <t>From Biology.</t>
         </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Calibration source</t>
+        </is>
+      </c>
+      <c r="D20" s="76">
+        <f>Dosing!$D$41</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1536,10 +1603,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation sqref="D3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
-      <formula1>"AEP0.1.1,AEP0.2"</formula1>
-    </dataValidation>
+  <dataValidations count="6">
     <dataValidation sqref="D4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"Tube,Sintered"</formula1>
     </dataValidation>
@@ -1883,8 +1947,8 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D13" s="32">
-        <f>IF(rx_ver=ver_name_1,vial_OD_1,IF(rx_ver=ver_name_2,vial_OD_2,NA()))</f>
+      <c r="D13" s="77">
+        <f>VLOOKUP(rx_ver,$A$78:$I$81,7,FALSE)</f>
         <v/>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -1986,8 +2050,8 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D17" s="33">
-        <f>IF(rx_ver=ver_name_1,D_int_1,IF(rx_ver=ver_name_2,D_int_2,NA()))</f>
+      <c r="D17" s="78">
+        <f>VLOOKUP(rx_ver,$A$78:$I$81,4,FALSE)</f>
         <v/>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -2012,8 +2076,8 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D18" s="33">
-        <f>IF(rx_ver=ver_name_1,Vmax_1,IF(rx_ver=ver_name_2,Vmax_2,NA()))</f>
+      <c r="D18" s="78">
+        <f>VLOOKUP(rx_ver,$A$78:$I$81,5,FALSE)</f>
         <v/>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -2038,8 +2102,8 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D19" s="33">
-        <f>IF(rx_ver=ver_name_1,Vtot_1,IF(rx_ver=ver_name_2,Vtot_2,NA()))</f>
+      <c r="D19" s="78">
+        <f>VLOOKUP(rx_ver,$A$78:$I$81,6,FALSE)</f>
         <v/>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -2718,34 +2782,66 @@
     <row r="47">
       <c r="A47" s="64" t="inlineStr">
         <is>
-          <t>IMPORTS (from other tabs)</t>
+          <t>IMPORTS &amp; REACTOR-DERIVED</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>(import) Reactor version</t>
+          <t>(import) Reactor selection</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>reactor_sel</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="79">
+        <f>Summary!$D$33</f>
+        <v/>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>From Summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Reactor type (resolved from reactor)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>rx_ver</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48">
-        <f>Summary!$D$3</f>
-        <v/>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>From Summary.</t>
-        </is>
+      <c r="D49" s="80">
+        <f>VLOOKUP(reactor_sel,$A$53:$B$74,2,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Stir-bar length (from reactor type)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>stir_bar_L</t>
+        </is>
+      </c>
+      <c r="D50" s="80">
+        <f>VLOOKUP(rx_ver,$A$78:$I$81,8,FALSE)</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -6505,7 +6601,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Stir-bar length</t>
+          <t>(import) Stir-bar length (from reactor type)</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -6518,8 +6614,9 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D44" s="52" t="n">
-        <v>12</v>
+      <c r="D44" s="81">
+        <f>Geometry!$D$50</f>
+        <v/>
       </c>
       <c r="E44" s="53" t="inlineStr">
         <is>
@@ -8071,7 +8168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8839,10 +8936,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
+      <c r="D34" s="79">
+        <f>Summary!$D$33</f>
+        <v/>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -8891,8 +8987,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D36">
-        <f>SUMPRODUCT(MAX(('CO2 flows'!$A$51:$A$80=Reactor)*'CO2 flows'!$B$51:$B$80))</f>
+      <c r="D36" s="80">
+        <f>IF(cal_exact_n&gt;0,SUMPRODUCT(MAX(('CO2 flows'!$A$51:$A$70=Reactor)*'CO2 flows'!$B$51:$B$70)),SUMPRODUCT(MAX(('CO2 flows'!$E$51:$E$70=cal_type)*'CO2 flows'!$B$51:$B$70)))</f>
         <v/>
       </c>
       <c r="E36" t="inlineStr">
@@ -8917,8 +9013,8 @@
           <t>ml/s</t>
         </is>
       </c>
-      <c r="D37">
-        <f>SUMPRODUCT(('CO2 flows'!$A$51:$A$80=Reactor)*('CO2 flows'!$B$51:$B$80=latest_date)*'CO2 flows'!$C$51:$C$80)</f>
+      <c r="D37" s="80">
+        <f>IF(cal_exact_n&gt;0,SUMPRODUCT(('CO2 flows'!$A$51:$A$70=Reactor)*('CO2 flows'!$B$51:$B$70=latest_date)*'CO2 flows'!$C$51:$C$70)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$51:$A$70=Reactor)*('CO2 flows'!$B$51:$B$70=latest_date)*1)),SUMPRODUCT(('CO2 flows'!$E$51:$E$70=cal_type)*('CO2 flows'!$B$51:$B$70=latest_date)*'CO2 flows'!$C$51:$C$70)/MAX(1,SUMPRODUCT(('CO2 flows'!$E$51:$E$70=cal_type)*('CO2 flows'!$B$51:$B$70=latest_date)*1)))</f>
         <v/>
       </c>
       <c r="E37" t="inlineStr">
@@ -8943,14 +9039,62 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D38">
-        <f>SUMPRODUCT(('CO2 flows'!$A$51:$A$80=Reactor)*('CO2 flows'!$B$51:$B$80=latest_date)*'CO2 flows'!$D$51:$D$80)</f>
+      <c r="D38" s="80">
+        <f>IF(cal_exact_n&gt;0,SUMPRODUCT(('CO2 flows'!$A$51:$A$70=Reactor)*('CO2 flows'!$B$51:$B$70=latest_date)*'CO2 flows'!$D$51:$D$70)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$51:$A$70=Reactor)*('CO2 flows'!$B$51:$B$70=latest_date)*1)),SUMPRODUCT(('CO2 flows'!$E$51:$E$70=cal_type)*('CO2 flows'!$B$51:$B$70=latest_date)*'CO2 flows'!$D$51:$D$70)/MAX(1,SUMPRODUCT(('CO2 flows'!$E$51:$E$70=cal_type)*('CO2 flows'!$B$51:$B$70=latest_date)*1)))</f>
         <v/>
       </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>Pulled from CO2 flows (latest date for reactor).</t>
         </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>calibration rows for this reactor</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>cal_exact_n</t>
+        </is>
+      </c>
+      <c r="D39" s="80">
+        <f>SUMPRODUCT(('CO2 flows'!$A$51:$A$70=Reactor)*1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>reactor type (for nearest-match)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>cal_type</t>
+        </is>
+      </c>
+      <c r="D40" s="80">
+        <f>IFERROR(VLOOKUP(Reactor,Geometry!$A$53:$B$74,2,FALSE),"?")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>calibration source</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>cal_warning</t>
+        </is>
+      </c>
+      <c r="D41" s="80">
+        <f>IF(cal_exact_n&gt;0,"exact: "&amp;Reactor,"NEAREST TYPE ("&amp;cal_type&amp;") - no calibration for "&amp;Reactor)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -8991,7 +9135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S55"/>
+  <dimension ref="A1:Q76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="9"/>
@@ -10302,6 +10446,11 @@
           <t>Min sparge (s)</t>
         </is>
       </c>
+      <c r="E50" s="69" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -10318,23 +10467,150 @@
       <c r="D51" t="n">
         <v>0.25</v>
       </c>
+      <c r="E51">
+        <f>IFERROR(VLOOKUP(A51,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="72" t="inlineStr">
-        <is>
-          <t>(add a row per reactor/date as calibrations are collected)</t>
-        </is>
+      <c r="A52" s="72" t="n"/>
+      <c r="E52">
+        <f>IFERROR(VLOOKUP(A52,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="E53">
+        <f>IFERROR(VLOOKUP(A53,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="73" t="inlineStr">
+      <c r="A54" s="73" t="n"/>
+      <c r="E54">
+        <f>IFERROR(VLOOKUP(A54,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="E55">
+        <f>IFERROR(VLOOKUP(A55,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="E56">
+        <f>IFERROR(VLOOKUP(A56,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="E57">
+        <f>IFERROR(VLOOKUP(A57,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="E58">
+        <f>IFERROR(VLOOKUP(A58,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="E59">
+        <f>IFERROR(VLOOKUP(A59,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="E60">
+        <f>IFERROR(VLOOKUP(A60,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="E61">
+        <f>IFERROR(VLOOKUP(A61,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="E62">
+        <f>IFERROR(VLOOKUP(A62,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="E63">
+        <f>IFERROR(VLOOKUP(A63,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="E64">
+        <f>IFERROR(VLOOKUP(A64,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="E65">
+        <f>IFERROR(VLOOKUP(A65,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="E66">
+        <f>IFERROR(VLOOKUP(A66,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="E67">
+        <f>IFERROR(VLOOKUP(A67,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="E68">
+        <f>IFERROR(VLOOKUP(A68,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="E69">
+        <f>IFERROR(VLOOKUP(A69,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="E70">
+        <f>IFERROR(VLOOKUP(A70,Geometry!$A$53:$B$74,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="72" t="inlineStr">
+        <is>
+          <t>Add one row per reactor + calibration date below the header (row 50); rows 51-70 are the lookup range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="72" t="inlineStr">
+        <is>
+          <t>The latest date for a reactor is used; if a reactor has no row, the latest row of the same reactor type is used (flagged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="73" t="inlineStr">
         <is>
           <t>Min sparge justification</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>0.25 s. Repeatable at 0.25 s (1 ml/shot) and 0.5 s (2 ml); at &lt;=0.2 s the per-pulse flowrate is erratic (2-6 ml/s) - the ~0.4 ml fixed open/close bolus and timing jitter dominate. Flowrate 3.33 ml/s = inspection-set max (no bubbles into the neck), confirmed by the long-pulse slope.</t>
         </is>

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -87,6 +87,8 @@
     <definedName name="z_e_H2" localSheetId="2">Electrochemistry!$D$9</definedName>
     <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$10</definedName>
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$20</definedName>
+    <definedName name="electrode_sel" localSheetId="2">Electrochemistry!$D$38</definedName>
+    <definedName name="sparger_e" localSheetId="2">Electrochemistry!$D$39</definedName>
     <definedName name="bio_CO2" localSheetId="3">Biology!$D$5</definedName>
     <definedName name="bio_H2" localSheetId="3">Biology!$D$3</definedName>
     <definedName name="bio_O2" localSheetId="3">Biology!$D$4</definedName>
@@ -125,6 +127,11 @@
     <definedName name="T_K" localSheetId="3">Biology!$D$11</definedName>
     <definedName name="T_ref" localSheetId="3">Biology!$D$16</definedName>
     <definedName name="V_charge" localSheetId="3">Biology!$D$42</definedName>
+    <definedName name="organism_sel" localSheetId="3">Biology!$D$57</definedName>
+    <definedName name="DO_min" localSheetId="3">Biology!$D$58</definedName>
+    <definedName name="DO_opt" localSheetId="3">Biology!$D$59</definedName>
+    <definedName name="DO_impair" localSheetId="3">Biology!$D$60</definedName>
+    <definedName name="DO_toxic" localSheetId="3">Biology!$D$61</definedName>
     <definedName name="a_int" localSheetId="4">'Mass Transfer'!$D$25</definedName>
     <definedName name="a_surf" localSheetId="4">'Mass Transfer'!$D$48</definedName>
     <definedName name="A_x" localSheetId="4">'Mass Transfer'!$D$96</definedName>
@@ -222,6 +229,13 @@
     <definedName name="We_orifice" localSheetId="4">'Mass Transfer'!$D$39</definedName>
     <definedName name="y_O2_vent" localSheetId="4">'Mass Transfer'!$D$52</definedName>
     <definedName name="flush_factor" localSheetId="4">'Mass Transfer'!$D$102</definedName>
+    <definedName name="DO_opt" localSheetId="4">'Mass Transfer'!$D$103</definedName>
+    <definedName name="DO_impair" localSheetId="4">'Mass Transfer'!$D$104</definedName>
+    <definedName name="DO_toxic" localSheetId="4">'Mass Transfer'!$D$105</definedName>
+    <definedName name="DO_min" localSheetId="4">'Mass Transfer'!$D$106</definedName>
+    <definedName name="DO_ss" localSheetId="4">'Mass Transfer'!$D$109</definedName>
+    <definedName name="DO_ss_vs_opt" localSheetId="4">'Mass Transfer'!$D$110</definedName>
+    <definedName name="DO_ss_vs_min" localSheetId="4">'Mass Transfer'!$D$111</definedName>
     <definedName name="CO2_cons" localSheetId="5">Dosing!$D$25</definedName>
     <definedName name="CO2_pulse" localSheetId="5">Dosing!$D$10</definedName>
     <definedName name="CO2_sd_ratio" localSheetId="5">Dosing!$D$14</definedName>
@@ -509,7 +523,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -649,11 +663,53 @@
         <color theme="9"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="8"/>
+      </left>
+      <right style="medium">
+        <color theme="8"/>
+      </right>
+      <top style="medium">
+        <color theme="8"/>
+      </top>
+      <bottom style="medium">
+        <color theme="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5"/>
+      </left>
+      <right style="medium">
+        <color theme="5"/>
+      </right>
+      <top style="medium">
+        <color theme="5"/>
+      </top>
+      <bottom style="medium">
+        <color theme="5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="6"/>
+      </left>
+      <right style="medium">
+        <color theme="6"/>
+      </right>
+      <top style="medium">
+        <color theme="6"/>
+      </top>
+      <bottom style="medium">
+        <color theme="6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -770,6 +826,11 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1120,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1192,7 +1253,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Sparger type</t>
+          <t>Sparger type (resolved from electrode)</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -1205,10 +1266,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
-        <is>
-          <t>Sintered</t>
-        </is>
+      <c r="D4" s="82">
+        <f>Electrochemistry!$D$39</f>
+        <v/>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
@@ -1602,11 +1662,41 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Steady-state DO (surface, mg/L)</t>
+        </is>
+      </c>
+      <c r="D39" s="83">
+        <f>'Mass Transfer'!$D$109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DO vs organism optimum</t>
+        </is>
+      </c>
+      <c r="D40" s="83">
+        <f>'Mass Transfer'!$D$110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DO vs organism minimum</t>
+        </is>
+      </c>
+      <c r="D41" s="83">
+        <f>'Mass Transfer'!$D$111</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation sqref="D4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
-      <formula1>"Tube,Sintered"</formula1>
-    </dataValidation>
+  <dataValidations count="5">
     <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"0,1,2,3,4,5"</formula1>
     </dataValidation>
@@ -3332,7 +3422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3822,8 +3912,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D20" s="24" t="n">
-        <v>4</v>
+      <c r="D20" s="77">
+        <f>VLOOKUP(electrode_sel,$A$32:$I$34,9,FALSE)</f>
+        <v/>
       </c>
       <c r="E20" s="25" t="inlineStr">
         <is>
@@ -4150,6 +4241,38 @@
         <is>
           <t>z_e_ORR=2 assumed (peroxide, non-Pt SS cathode, neutral pH); etaF unmeasured - both live here per electrode.</t>
         </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>(import) Electrode selection</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>electrode_sel</t>
+        </is>
+      </c>
+      <c r="D38" s="79">
+        <f>Summary!$D$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sparger (from electrode)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sparger_e</t>
+        </is>
+      </c>
+      <c r="D39" s="80">
+        <f>VLOOKUP(electrode_sel,$A$32:$I$34,4,FALSE)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -4172,7 +4295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5475,6 +5598,86 @@
         <is>
           <t>Sydow et al. 2017</t>
         </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>(import) HOB organism</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>organism_sel</t>
+        </is>
+      </c>
+      <c r="D57" s="79">
+        <f>Summary!$D$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Minimum DO (organism)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>DO_min</t>
+        </is>
+      </c>
+      <c r="D58" s="84">
+        <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$47:$F$52,2,FALSE)),VLOOKUP(organism_sel,$A$47:$F$52,2,FALSE),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Optimum DO (organism)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>DO_opt</t>
+        </is>
+      </c>
+      <c r="D59" s="80">
+        <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$47:$F$52,3,FALSE)),VLOOKUP(organism_sel,$A$47:$F$52,3,FALSE),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Impairment DO (organism)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>DO_impair</t>
+        </is>
+      </c>
+      <c r="D60" s="80">
+        <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$47:$F$52,4,FALSE)),VLOOKUP(organism_sel,$A$47:$F$52,4,FALSE),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Toxic/inhibition DO (organism)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>DO_toxic</t>
+        </is>
+      </c>
+      <c r="D61" s="80">
+        <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$47:$F$52,5,FALSE)),VLOOKUP(organism_sel,$A$47:$F$52,5,FALSE),NA())</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -5506,7 +5709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7042,7 +7245,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Target dissolved-O₂ ceiling fraction</t>
+          <t>Target DO fraction (organism optimum / inhibition)</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -7055,8 +7258,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D61" s="52" t="n">
-        <v>0.5</v>
+      <c r="D61" s="85">
+        <f>IF(AND(ISNUMBER(DO_opt),ISNUMBER(DO_toxic)),DO_opt/DO_toxic,0.5)</f>
+        <v/>
       </c>
       <c r="E61" s="25" t="inlineStr">
         <is>
@@ -8008,7 +8212,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>(import) Sparger type</t>
+          <t>(import) Sparger type (from electrode)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8021,8 +8225,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D100">
-        <f>Summary!$D$4</f>
+      <c r="D100" s="82">
+        <f>Electrochemistry!$D$39</f>
         <v/>
       </c>
       <c r="E100" t="inlineStr">
@@ -8055,6 +8259,125 @@
         <is>
           <t>From Dosing.</t>
         </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>(import) Optimum DO (organism)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>DO_opt</t>
+        </is>
+      </c>
+      <c r="D103" s="86">
+        <f>Biology!$D$59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>(import) Impairment DO (organism)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>DO_impair</t>
+        </is>
+      </c>
+      <c r="D104" s="86">
+        <f>Biology!$D$60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>(import) Toxic/inhibition DO (organism)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>DO_toxic</t>
+        </is>
+      </c>
+      <c r="D105" s="86">
+        <f>Biology!$D$61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>(import) Minimum DO (organism)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>DO_min</t>
+        </is>
+      </c>
+      <c r="D106" s="86">
+        <f>Biology!$D$58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="69" t="inlineStr">
+        <is>
+          <t>STEADY-STATE DO CHECK (surface stripping vs organism band)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Steady-state DO under surface stripping</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>DO_ss</t>
+        </is>
+      </c>
+      <c r="D109" s="80">
+        <f>O2_excess/(kLa_surf_used*3600*(V_charge/1000000))*32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DO_ss vs optimum (organism)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>DO_ss_vs_opt</t>
+        </is>
+      </c>
+      <c r="D110" s="80">
+        <f>IF(ISNUMBER(DO_opt),IF(DO_ss&lt;=DO_opt,"at/under optimum",IF(DO_ss&lt;DO_impair,"above optimum, under impairment","OVER IMPAIRMENT - surface strip insufficient")),"organism optimum unknown")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DO_ss vs minimum (organism)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>DO_ss_vs_min</t>
+        </is>
+      </c>
+      <c r="D111" s="80">
+        <f>IF(ISNUMBER(DO_min),IF(DO_ss&gt;=DO_min,"above minimum","BELOW MINIMUM"),"minimum DO unknown - measure")</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -268,9 +268,8 @@
     <definedName name="latest_date" localSheetId="5">Dosing!$D$36</definedName>
     <definedName name="flowrate_cal" localSheetId="5">Dosing!$D$37</definedName>
     <definedName name="min_sparge_cal" localSheetId="5">Dosing!$D$38</definedName>
-    <definedName name="cal_exact_n" localSheetId="5">Dosing!$D$39</definedName>
-    <definedName name="cal_type" localSheetId="5">Dosing!$D$40</definedName>
     <definedName name="cal_warning" localSheetId="5">Dosing!$D$41</definedName>
+    <definedName name="has_cal" localSheetId="5">Dosing!$D$39</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -9311,7 +9310,7 @@
         </is>
       </c>
       <c r="D36" s="80">
-        <f>IF(cal_exact_n&gt;0,SUMPRODUCT(MAX(('CO2 flows'!$A$51:$A$70=Reactor)*'CO2 flows'!$B$51:$B$70)),SUMPRODUCT(MAX(('CO2 flows'!$E$51:$E$70=cal_type)*'CO2 flows'!$B$51:$B$70)))</f>
+        <f>SUMPRODUCT(MAX(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$J$4:$J$200&gt;0)*'CO2 flows'!$B$4:$B$200))</f>
         <v/>
       </c>
       <c r="E36" t="inlineStr">
@@ -9337,7 +9336,7 @@
         </is>
       </c>
       <c r="D37" s="80">
-        <f>IF(cal_exact_n&gt;0,SUMPRODUCT(('CO2 flows'!$A$51:$A$70=Reactor)*('CO2 flows'!$B$51:$B$70=latest_date)*'CO2 flows'!$C$51:$C$70)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$51:$A$70=Reactor)*('CO2 flows'!$B$51:$B$70=latest_date)*1)),SUMPRODUCT(('CO2 flows'!$E$51:$E$70=cal_type)*('CO2 flows'!$B$51:$B$70=latest_date)*'CO2 flows'!$C$51:$C$70)/MAX(1,SUMPRODUCT(('CO2 flows'!$E$51:$E$70=cal_type)*('CO2 flows'!$B$51:$B$70=latest_date)*1)))</f>
+        <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*'CO2 flows'!$J$4:$J$200)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*('CO2 flows'!$J$4:$J$200&gt;0)*1))</f>
         <v/>
       </c>
       <c r="E37" t="inlineStr">
@@ -9363,7 +9362,7 @@
         </is>
       </c>
       <c r="D38" s="80">
-        <f>IF(cal_exact_n&gt;0,SUMPRODUCT(('CO2 flows'!$A$51:$A$70=Reactor)*('CO2 flows'!$B$51:$B$70=latest_date)*'CO2 flows'!$D$51:$D$70)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$51:$A$70=Reactor)*('CO2 flows'!$B$51:$B$70=latest_date)*1)),SUMPRODUCT(('CO2 flows'!$E$51:$E$70=cal_type)*('CO2 flows'!$B$51:$B$70=latest_date)*'CO2 flows'!$D$51:$D$70)/MAX(1,SUMPRODUCT(('CO2 flows'!$E$51:$E$70=cal_type)*('CO2 flows'!$B$51:$B$70=latest_date)*1)))</f>
+        <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*'CO2 flows'!$I$4:$I$200)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*('CO2 flows'!$J$4:$J$200&gt;0)*1))</f>
         <v/>
       </c>
       <c r="E38" t="inlineStr">
@@ -9375,34 +9374,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>calibration rows for this reactor</t>
+          <t>reactor has a calibration row?</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>cal_exact_n</t>
+          <t>has_cal</t>
         </is>
       </c>
       <c r="D39" s="80">
-        <f>SUMPRODUCT(('CO2 flows'!$A$51:$A$70=Reactor)*1)</f>
+        <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$J$4:$J$200&gt;0)*1)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>reactor type (for nearest-match)</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>cal_type</t>
-        </is>
-      </c>
-      <c r="D40" s="80">
-        <f>IFERROR(VLOOKUP(Reactor,Geometry!$A$53:$B$74,2,FALSE),"?")</f>
-        <v/>
-      </c>
+      <c r="D40" s="80" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9416,7 +9402,7 @@
         </is>
       </c>
       <c r="D41" s="80">
-        <f>IF(cal_exact_n&gt;0,"exact: "&amp;Reactor,"NEAREST TYPE ("&amp;cal_type&amp;") - no calibration for "&amp;Reactor)</f>
+        <f>IF(has_cal&gt;0,"calibrated: "&amp;Reactor,"NO CALIBRATION for "&amp;Reactor&amp;" - add a row in CO2 flows with nominal flowrate + minimum sparge")</f>
         <v/>
       </c>
     </row>
@@ -9518,6 +9504,11 @@
           <t>minimum sparge</t>
         </is>
       </c>
+      <c r="J2" s="69" t="inlineStr">
+        <is>
+          <t>nominal flowrate</t>
+        </is>
+      </c>
       <c r="L2" s="59" t="inlineStr">
         <is>
           <t>KEY</t>
@@ -9563,6 +9554,11 @@
           <t>s</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ml/s</t>
+        </is>
+      </c>
       <c r="L3" s="68" t="inlineStr">
         <is>
           <t>Flowrate set by inspection, as maximum to not give bubbles rising into vial neck</t>
@@ -9588,6 +9584,12 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="I4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.33</v>
+      </c>
       <c r="L4" s="67" t="inlineStr">
         <is>
           <t>First or last data point removed as suspect outlier</t>
@@ -10741,204 +10743,55 @@
     <row r="47">
       <c r="B47" s="66" t="n"/>
     </row>
+    <row r="48"/>
     <row r="49">
-      <c r="A49" s="73" t="inlineStr">
-        <is>
-          <t>CALIBRATION SUMMARY (model lookup source — latest date per reactor is used)</t>
-        </is>
-      </c>
+      <c r="A49" s="73" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="69" t="inlineStr">
-        <is>
-          <t>Reactor</t>
-        </is>
-      </c>
-      <c r="B50" s="69" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C50" s="69" t="inlineStr">
-        <is>
-          <t>Flowrate (ml/s)</t>
-        </is>
-      </c>
-      <c r="D50" s="69" t="inlineStr">
-        <is>
-          <t>Min sparge (s)</t>
-        </is>
-      </c>
-      <c r="E50" s="69" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
+      <c r="A50" s="69" t="n"/>
+      <c r="B50" s="69" t="n"/>
+      <c r="C50" s="69" t="n"/>
+      <c r="D50" s="69" t="n"/>
+      <c r="E50" s="69" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B51" s="70" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C51" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E51">
-        <f>IFERROR(VLOOKUP(A51,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
+      <c r="B51" s="70" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="72" t="n"/>
-      <c r="E52">
-        <f>IFERROR(VLOOKUP(A52,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="E53">
-        <f>IFERROR(VLOOKUP(A53,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
+    </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="73" t="n"/>
-      <c r="E54">
-        <f>IFERROR(VLOOKUP(A54,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="E55">
-        <f>IFERROR(VLOOKUP(A55,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="E56">
-        <f>IFERROR(VLOOKUP(A56,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="E57">
-        <f>IFERROR(VLOOKUP(A57,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="E58">
-        <f>IFERROR(VLOOKUP(A58,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="E59">
-        <f>IFERROR(VLOOKUP(A59,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="E60">
-        <f>IFERROR(VLOOKUP(A60,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="E61">
-        <f>IFERROR(VLOOKUP(A61,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="E62">
-        <f>IFERROR(VLOOKUP(A62,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="E63">
-        <f>IFERROR(VLOOKUP(A63,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="E64">
-        <f>IFERROR(VLOOKUP(A64,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="E65">
-        <f>IFERROR(VLOOKUP(A65,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="E66">
-        <f>IFERROR(VLOOKUP(A66,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="E67">
-        <f>IFERROR(VLOOKUP(A67,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="E68">
-        <f>IFERROR(VLOOKUP(A68,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="E69">
-        <f>IFERROR(VLOOKUP(A69,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="E70">
-        <f>IFERROR(VLOOKUP(A70,Geometry!$A$53:$B$74,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
     <row r="72">
-      <c r="A72" s="72" t="inlineStr">
-        <is>
-          <t>Add one row per reactor + calibration date below the header (row 50); rows 51-70 are the lookup range.</t>
-        </is>
-      </c>
+      <c r="A72" s="72" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="72" t="inlineStr">
-        <is>
-          <t>The latest date for a reactor is used; if a reactor has no row, the latest row of the same reactor type is used (flagged).</t>
-        </is>
-      </c>
-    </row>
+      <c r="A73" s="72" t="n"/>
+    </row>
+    <row r="74"/>
     <row r="75">
-      <c r="A75" s="73" t="inlineStr">
-        <is>
-          <t>Min sparge justification</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>0.25 s. Repeatable at 0.25 s (1 ml/shot) and 0.5 s (2 ml); at &lt;=0.2 s the per-pulse flowrate is erratic (2-6 ml/s) - the ~0.4 ml fixed open/close bolus and timing jitter dominate. Flowrate 3.33 ml/s = inspection-set max (no bubbles into the neck), confirmed by the long-pulse slope.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A75" s="73" t="n"/>
+    </row>
+    <row r="76"/>
   </sheetData>
   <conditionalFormatting sqref="H5:H46">
     <cfRule type="dataBar" priority="1">

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -18,6 +18,11 @@
     <definedName name="por_grade" localSheetId="0">Summary!$D$5</definedName>
     <definedName name="rx_ver" localSheetId="0">Summary!$D$3</definedName>
     <definedName name="sparger" localSheetId="0">Summary!$D$4</definedName>
+    <definedName name="led_intensity" localSheetId="0">Summary!$D$37</definedName>
+    <definedName name="stir_rpm_set" localSheetId="0">Summary!$D$38</definedName>
+    <definedName name="media_volume" localSheetId="0">Summary!$D$39</definedName>
+    <definedName name="temp_C" localSheetId="0">Summary!$D$40</definedName>
+    <definedName name="P_atm_set" localSheetId="0">Summary!$D$41</definedName>
     <definedName name="A_x" localSheetId="1">Geometry!$D$16</definedName>
     <definedName name="D_int" localSheetId="1">Geometry!$D$17</definedName>
     <definedName name="D_int_1" localSheetId="1">Geometry!$D$7</definedName>
@@ -64,6 +69,9 @@
     <definedName name="reactor_sel" localSheetId="1">Geometry!$D$48</definedName>
     <definedName name="rx_ver" localSheetId="1">Geometry!$D$49</definedName>
     <definedName name="stir_bar_L" localSheetId="1">Geometry!$D$50</definedName>
+    <definedName name="media_volume" localSheetId="1">Geometry!$D$85</definedName>
+    <definedName name="media_vol_warn" localSheetId="1">Geometry!$D$86</definedName>
+    <definedName name="depth_warn" localSheetId="1">Geometry!$D$87</definedName>
     <definedName name="etaF" localSheetId="2">Electrochemistry!$D$11</definedName>
     <definedName name="etaF_OER" localSheetId="2">Electrochemistry!$D$19</definedName>
     <definedName name="F_const" localSheetId="2">Electrochemistry!$D$8</definedName>
@@ -236,6 +244,7 @@
     <definedName name="DO_ss" localSheetId="4">'Mass Transfer'!$D$109</definedName>
     <definedName name="DO_ss_vs_opt" localSheetId="4">'Mass Transfer'!$D$110</definedName>
     <definedName name="DO_ss_vs_min" localSheetId="4">'Mass Transfer'!$D$111</definedName>
+    <definedName name="tip_warn" localSheetId="4">'Mass Transfer'!$D$112</definedName>
     <definedName name="CO2_cons" localSheetId="5">Dosing!$D$25</definedName>
     <definedName name="CO2_pulse" localSheetId="5">Dosing!$D$10</definedName>
     <definedName name="CO2_sd_ratio" localSheetId="5">Dosing!$D$14</definedName>
@@ -288,7 +297,7 @@
     <numFmt numFmtId="171" formatCode="0.0000000"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -429,6 +438,14 @@
     </font>
     <font>
       <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="17">
@@ -708,7 +725,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -830,11 +847,20 @@
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -920,6 +946,20 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF63BE7B"/>
           <bgColor rgb="FF63BE7B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1180,7 +1220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1300,6 +1340,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="59" t="inlineStr">
         <is>
@@ -1317,10 +1358,9 @@
         <f>'Mass Transfer'!$D$67</f>
         <v/>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
+      <c r="E8" s="87">
+        <f>HYPERLINK("#'Mass Transfer'!D67","From Mass Transfer")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1333,10 +1373,9 @@
         <f>'Mass Transfer'!$D$68</f>
         <v/>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
+      <c r="E9" s="87">
+        <f>HYPERLINK("#'Mass Transfer'!D68","From Mass Transfer")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1349,10 +1388,9 @@
         <f>'Mass Transfer'!$D$55</f>
         <v/>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
+      <c r="E10" s="87">
+        <f>HYPERLINK("#'Mass Transfer'!D55","From Mass Transfer")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1365,10 +1403,9 @@
         <f>'Mass Transfer'!$D$56</f>
         <v/>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
+      <c r="E11" s="87">
+        <f>HYPERLINK("#'Mass Transfer'!D56","From Mass Transfer")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1381,10 +1418,9 @@
         <f>Biology!$D$28</f>
         <v/>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
+      <c r="E12" s="87">
+        <f>HYPERLINK("#Biology!D28","From Biology")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1397,10 +1433,9 @@
         <f>Dosing!$D$14</f>
         <v/>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>From Dosing.</t>
-        </is>
+      <c r="E13" s="87">
+        <f>HYPERLINK("#Dosing!D14","From Dosing")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1413,10 +1448,9 @@
         <f>Electrochemistry!$D$13</f>
         <v/>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>From Electrochemistry.</t>
-        </is>
+      <c r="E14" s="87">
+        <f>HYPERLINK("#Electrochemistry!D13","From Electrochemistry")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1429,10 +1463,9 @@
         <f>'Mass Transfer'!$D$35</f>
         <v/>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
+      <c r="E15" s="87">
+        <f>HYPERLINK("#'Mass Transfer'!D35","From Mass Transfer")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1445,10 +1478,9 @@
         <f>'Mass Transfer'!$D$40</f>
         <v/>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
+      <c r="E16" s="87">
+        <f>HYPERLINK("#'Mass Transfer'!D40","From Mass Transfer")</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1461,10 +1493,9 @@
         <f>Dosing!$D$19</f>
         <v/>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>From Dosing.</t>
-        </is>
+      <c r="E17" s="87">
+        <f>HYPERLINK("#Dosing!D19","From Dosing")</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1477,10 +1508,9 @@
         <f>'Mass Transfer'!$D$72</f>
         <v/>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
+      <c r="E18" s="87">
+        <f>HYPERLINK("#'Mass Transfer'!D72","From Mass Transfer")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1493,10 +1523,9 @@
         <f>Biology!$D$37</f>
         <v/>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
+      <c r="E19" s="87">
+        <f>HYPERLINK("#Biology!D37","From Biology")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1507,6 +1536,10 @@
       </c>
       <c r="D20" s="76">
         <f>Dosing!$D$41</f>
+        <v/>
+      </c>
+      <c r="E20" s="87">
+        <f>HYPERLINK("#Dosing!D41","From Dosing")</f>
         <v/>
       </c>
     </row>
@@ -1586,6 +1619,7 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="29" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="73" t="inlineStr">
         <is>
@@ -1661,40 +1695,393 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LED intensity setpoint</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>led_intensity</t>
+        </is>
+      </c>
+      <c r="D37" s="88" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Stirrer rate (rpm)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>stir_rpm_set</t>
+        </is>
+      </c>
+      <c r="D38" s="88" t="n">
+        <v>500</v>
+      </c>
+    </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Steady-state DO (surface, mg/L)</t>
-        </is>
-      </c>
-      <c r="D39" s="83">
-        <f>'Mass Transfer'!$D$109</f>
-        <v/>
-      </c>
+          <t>Media volume (mL) - blank = recommended max</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>media_volume</t>
+        </is>
+      </c>
+      <c r="D39" s="89" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DO vs organism optimum</t>
-        </is>
-      </c>
-      <c r="D40" s="83">
-        <f>'Mass Transfer'!$D$110</f>
-        <v/>
+          <t>Temperature (degC)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>temp_C</t>
+        </is>
+      </c>
+      <c r="D40" s="89" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Ambient pressure (Pa)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P_atm_set</t>
+        </is>
+      </c>
+      <c r="D41" s="89" t="n">
+        <v>101325</v>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="69" t="inlineStr">
+        <is>
+          <t>DO BAND (organism)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Steady-state DO (surface, mg/L)</t>
+        </is>
+      </c>
+      <c r="D44" s="80">
+        <f>'Mass Transfer'!$D$109</f>
+        <v/>
+      </c>
+      <c r="E44" s="87">
+        <f>HYPERLINK("#'Mass Transfer'!D109","From Mass Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DO vs organism optimum</t>
+        </is>
+      </c>
+      <c r="D45" s="80">
+        <f>'Mass Transfer'!$D$110</f>
+        <v/>
+      </c>
+      <c r="E45" s="87">
+        <f>HYPERLINK("#'Mass Transfer'!D110","From Mass Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>DO vs organism minimum</t>
         </is>
       </c>
-      <c r="D41" s="83">
+      <c r="D46" s="80">
         <f>'Mass Transfer'!$D$111</f>
         <v/>
       </c>
+      <c r="E46" s="87">
+        <f>HYPERLINK("#'Mass Transfer'!D111","From Mass Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="69" t="inlineStr">
+        <is>
+          <t>Media-volume / depth / tip warnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Media vs max working</t>
+        </is>
+      </c>
+      <c r="D48" s="79">
+        <f>Geometry!$D$86</f>
+        <v/>
+      </c>
+      <c r="E48" s="87">
+        <f>HYPERLINK("#Geometry!D86","From Geometry")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Liquid vs usable depth</t>
+        </is>
+      </c>
+      <c r="D49" s="79">
+        <f>Geometry!$D$87</f>
+        <v/>
+      </c>
+      <c r="E49" s="87">
+        <f>HYPERLINK("#Geometry!D87","From Geometry")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Tip speed (m/s)</t>
+        </is>
+      </c>
+      <c r="D50" s="80">
+        <f>'Mass Transfer'!$D$45</f>
+        <v/>
+      </c>
+      <c r="E50" s="87">
+        <f>HYPERLINK("#'Mass Transfer'!D45","From Mass Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Tip-speed shear</t>
+        </is>
+      </c>
+      <c r="D51" s="80">
+        <f>'Mass Transfer'!$D$112</f>
+        <v/>
+      </c>
+      <c r="E51" s="87">
+        <f>HYPERLINK("#'Mass Transfer'!D112","From Mass Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="69" t="inlineStr">
+        <is>
+          <t>RANKED IMPROVEMENTS (by impact, with effort)</t>
+        </is>
+      </c>
+      <c r="B53" s="69" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C53" s="69" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="E53" s="69" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1 Measure surface kLa (kL_surf)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>375% sensitivity; decides whether DO stays in the organism band</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2 Measure cathodic Faradaic efficiency (etaF)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>sets the H2/O2 split and net O2; currently assumed 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3 Determine organism minimum DO</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>lower DO guardrail; currently a gap for every organism</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4 Calibrate flow for each reactor used</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>each experiment; only ed04 calibrated so far</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>5 Confirm knallgas uptake ratio (H2:O2:CO2)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>carbon/O2 balance; needs a growing culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>6 Measure sinter porosity grade</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>bubble size when sparger = sintered</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>7 Record lab ambient pressure</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Henry solubilities + gas volumes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D7:D20">
+    <cfRule type="expression" priority="1" dxfId="11">
+      <formula>OR(ISNUMBER(SEARCH("RISK",D7)),ISNUMBER(SEARCH("OVER",D7)),ISNUMBER(SEARCH("BELOW",D7)),ISNUMBER(SEARCH("EXCEED",D7)),ISNUMBER(SEARCH("NO CALIB",D7)),ISNUMBER(SEARCH("NEAREST",D7)),ISNUMBER(SEARCH("EXPLOSIVE",D7)),ISNUMBER(SEARCH("LOW",D7)),ISNUMBER(SEARCH("TIGHT",D7)),ISNUMBER(SEARCH("insufficient",D7)))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="12">
+      <formula>OR(ISNUMBER(SEARCH("OK",D7)),ISNUMBER(SEARCH("calibrated",D7)),ISNUMBER(SEARCH("under optimum",D7)),ISNUMBER(SEARCH("above min",D7)),ISNUMBER(SEARCH("exact",D7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D44:D51">
+    <cfRule type="expression" priority="3" dxfId="11">
+      <formula>OR(ISNUMBER(SEARCH("RISK",D44)),ISNUMBER(SEARCH("OVER",D44)),ISNUMBER(SEARCH("BELOW",D44)),ISNUMBER(SEARCH("EXCEED",D44)),ISNUMBER(SEARCH("NO CALIB",D44)),ISNUMBER(SEARCH("NEAREST",D44)),ISNUMBER(SEARCH("EXPLOSIVE",D44)),ISNUMBER(SEARCH("LOW",D44)),ISNUMBER(SEARCH("TIGHT",D44)),ISNUMBER(SEARCH("insufficient",D44)))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="12">
+      <formula>OR(ISNUMBER(SEARCH("OK",D44)),ISNUMBER(SEARCH("calibrated",D44)),ISNUMBER(SEARCH("under optimum",D44)),ISNUMBER(SEARCH("above min",D44)),ISNUMBER(SEARCH("exact",D44)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"0,1,2,3,4,5"</formula1>
@@ -1724,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2626,8 +3013,8 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D36" s="38">
-        <f>ROUND(V_max-disp_tot,0)</f>
+      <c r="D36" s="90">
+        <f>IF(media_volume&gt;0,media_volume,ROUND(V_max-disp_tot,0))</f>
         <v/>
       </c>
       <c r="E36" s="14" t="inlineStr">
@@ -2868,6 +3255,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="64" t="inlineStr">
         <is>
@@ -3216,6 +3604,7 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="73" t="inlineStr">
         <is>
@@ -3402,6 +3791,7 @@
         <v>6</v>
       </c>
     </row>
+    <row r="82"/>
     <row r="83">
       <c r="A83" s="72" t="inlineStr">
         <is>
@@ -3409,7 +3799,64 @@
         </is>
       </c>
     </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>(import) Media volume (set)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>media_volume</t>
+        </is>
+      </c>
+      <c r="D85" s="79">
+        <f>Summary!$D$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Media vs max working volume</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>media_vol_warn</t>
+        </is>
+      </c>
+      <c r="D86" s="80">
+        <f>IF(V_charge&gt;V_max,"MEDIA &gt; MAX WORKING VOLUME","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Liquid level vs usable depth</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>depth_warn</t>
+        </is>
+      </c>
+      <c r="D87" s="80">
+        <f>IF(h_actual&gt;D_int,"LIQUID OVER USABLE DEPTH","OK")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="D86:D87">
+    <cfRule type="expression" priority="1" dxfId="11">
+      <formula>OR(ISNUMBER(SEARCH("RISK",D86)),ISNUMBER(SEARCH("OVER",D86)),ISNUMBER(SEARCH("BELOW",D86)),ISNUMBER(SEARCH("EXCEED",D86)),ISNUMBER(SEARCH("NO CALIB",D86)),ISNUMBER(SEARCH("NEAREST",D86)),ISNUMBER(SEARCH("EXPLOSIVE",D86)),ISNUMBER(SEARCH("LOW",D86)),ISNUMBER(SEARCH("TIGHT",D86)),ISNUMBER(SEARCH("insufficient",D86)))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="12">
+      <formula>OR(ISNUMBER(SEARCH("OK",D86)),ISNUMBER(SEARCH("calibrated",D86)),ISNUMBER(SEARCH("under optimum",D86)),ISNUMBER(SEARCH("above min",D86)),ISNUMBER(SEARCH("exact",D86)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3479,8 +3926,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D3" s="39" t="n">
-        <v>3</v>
+      <c r="D3" s="91">
+        <f>Summary!$D$37</f>
+        <v/>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
@@ -3973,6 +4421,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="64" t="inlineStr">
         <is>
@@ -4058,6 +4507,8 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="73" t="inlineStr">
         <is>
@@ -4235,6 +4686,7 @@
         <v>2</v>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="72" t="inlineStr">
         <is>
@@ -4242,6 +4694,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -4531,8 +4984,9 @@
           <t>°C</t>
         </is>
       </c>
-      <c r="D10" s="31" t="n">
-        <v>30</v>
+      <c r="D10" s="92">
+        <f>Summary!$D$40</f>
+        <v/>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -4582,8 +5036,9 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n">
-        <v>101325</v>
+      <c r="D12" s="79">
+        <f>Summary!$D$41</f>
+        <v/>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
@@ -5230,6 +5685,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="64" t="inlineStr">
         <is>
@@ -5315,6 +5771,8 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="73" t="inlineStr">
         <is>
@@ -5538,6 +5996,7 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="73" t="inlineStr">
         <is>
@@ -5708,7 +6167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6791,8 +7250,9 @@
           <t>1/min</t>
         </is>
       </c>
-      <c r="D43" s="52" t="n">
-        <v>500</v>
+      <c r="D43" s="93">
+        <f>Summary!$D$38</f>
+        <v/>
       </c>
       <c r="E43" s="25" t="inlineStr">
         <is>
@@ -7629,6 +8089,7 @@
         </is>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="64" t="inlineStr">
         <is>
@@ -8198,7 +8659,7 @@
           <t>0-5</t>
         </is>
       </c>
-      <c r="D99">
+      <c r="D99" s="94">
         <f>Summary!$D$5</f>
         <v/>
       </c>
@@ -8234,6 +8695,7 @@
         </is>
       </c>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
@@ -8324,6 +8786,7 @@
         <v/>
       </c>
     </row>
+    <row r="107"/>
     <row r="108">
       <c r="A108" s="69" t="inlineStr">
         <is>
@@ -8377,6 +8840,27 @@
       <c r="D111" s="80">
         <f>IF(ISNUMBER(DO_min),IF(DO_ss&gt;=DO_min,"above minimum","BELOW MINIMUM"),"minimum DO unknown - measure")</f>
         <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Tip-speed shear flag (&lt;1.5 m/s)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>tip_warn</t>
+        </is>
+      </c>
+      <c r="D112" s="80">
+        <f>IF(tip_speed&gt;1.5,"TIP SPEED &gt; 1.5 m/s","OK")</f>
+        <v/>
+      </c>
+      <c r="E112" s="95" t="inlineStr">
+        <is>
+          <t>Conservative shear limit: &lt;1.5 m/s impeller-tip velocity recommended to avoid adverse cell-growth effects (BioProcess International, cell-culture norm); precautionary for robust HOB.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8479,6 +8963,14 @@
       <formula>"TIGHT"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D110:D112">
+    <cfRule type="expression" priority="14" dxfId="11">
+      <formula>OR(ISNUMBER(SEARCH("RISK",D110)),ISNUMBER(SEARCH("OVER",D110)),ISNUMBER(SEARCH("BELOW",D110)),ISNUMBER(SEARCH("EXCEED",D110)),ISNUMBER(SEARCH("NO CALIB",D110)),ISNUMBER(SEARCH("NEAREST",D110)),ISNUMBER(SEARCH("EXPLOSIVE",D110)),ISNUMBER(SEARCH("LOW",D110)),ISNUMBER(SEARCH("TIGHT",D110)),ISNUMBER(SEARCH("insufficient",D110)))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="12">
+      <formula>OR(ISNUMBER(SEARCH("OK",D110)),ISNUMBER(SEARCH("calibrated",D110)),ISNUMBER(SEARCH("under optimum",D110)),ISNUMBER(SEARCH("above min",D110)),ISNUMBER(SEARCH("exact",D110)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8968,6 +9460,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="64" t="inlineStr">
         <is>
@@ -9235,6 +9728,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="69" t="inlineStr">
         <is>
@@ -9426,6 +9920,20 @@
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
       <formula>"LOW"</formula>
     </cfRule>
+    <cfRule type="expression" priority="4" dxfId="11">
+      <formula>OR(ISNUMBER(SEARCH("RISK",D19)),ISNUMBER(SEARCH("OVER",D19)),ISNUMBER(SEARCH("BELOW",D19)),ISNUMBER(SEARCH("EXCEED",D19)),ISNUMBER(SEARCH("NO CALIB",D19)),ISNUMBER(SEARCH("NEAREST",D19)),ISNUMBER(SEARCH("EXPLOSIVE",D19)),ISNUMBER(SEARCH("LOW",D19)),ISNUMBER(SEARCH("TIGHT",D19)),ISNUMBER(SEARCH("insufficient",D19)))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="12">
+      <formula>OR(ISNUMBER(SEARCH("OK",D19)),ISNUMBER(SEARCH("calibrated",D19)),ISNUMBER(SEARCH("under optimum",D19)),ISNUMBER(SEARCH("above min",D19)),ISNUMBER(SEARCH("exact",D19)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D41">
+    <cfRule type="expression" priority="6" dxfId="11">
+      <formula>OR(ISNUMBER(SEARCH("RISK",D41)),ISNUMBER(SEARCH("OVER",D41)),ISNUMBER(SEARCH("BELOW",D41)),ISNUMBER(SEARCH("EXCEED",D41)),ISNUMBER(SEARCH("NO CALIB",D41)),ISNUMBER(SEARCH("NEAREST",D41)),ISNUMBER(SEARCH("EXPLOSIVE",D41)),ISNUMBER(SEARCH("LOW",D41)),ISNUMBER(SEARCH("TIGHT",D41)),ISNUMBER(SEARCH("insufficient",D41)))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="12">
+      <formula>OR(ISNUMBER(SEARCH("OK",D41)),ISNUMBER(SEARCH("calibrated",D41)),ISNUMBER(SEARCH("under optimum",D41)),ISNUMBER(SEARCH("above min",D41)),ISNUMBER(SEARCH("exact",D41)))</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="D58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
@@ -9444,7 +9952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="9"/>
@@ -10791,7 +11299,6 @@
     <row r="75">
       <c r="A75" s="73" t="n"/>
     </row>
-    <row r="76"/>
   </sheetData>
   <conditionalFormatting sqref="H5:H46">
     <cfRule type="dataBar" priority="1">

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -245,6 +245,8 @@
     <definedName name="DO_ss_vs_opt" localSheetId="4">'Mass Transfer'!$D$110</definedName>
     <definedName name="DO_ss_vs_min" localSheetId="4">'Mass Transfer'!$D$111</definedName>
     <definedName name="tip_warn" localSheetId="4">'Mass Transfer'!$D$112</definedName>
+    <definedName name="spg_int_carbon" localSheetId="4">'Mass Transfer'!$D$113</definedName>
+    <definedName name="sched_regime" localSheetId="4">'Mass Transfer'!$D$114</definedName>
     <definedName name="CO2_cons" localSheetId="5">Dosing!$D$25</definedName>
     <definedName name="CO2_pulse" localSheetId="5">Dosing!$D$10</definedName>
     <definedName name="CO2_sd_ratio" localSheetId="5">Dosing!$D$14</definedName>
@@ -1220,7 +1222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1340,7 +1342,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="59" t="inlineStr">
         <is>
@@ -1619,7 +1620,6 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="29" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="73" t="inlineStr">
         <is>
@@ -1768,7 +1768,6 @@
         <v>101325</v>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="69" t="inlineStr">
         <is>
@@ -1888,7 +1887,6 @@
         <v/>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="69" t="inlineStr">
         <is>
@@ -2063,6 +2061,50 @@
         <is>
           <t>Henry solubilities + gas volumes</t>
         </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="69" t="inlineStr">
+        <is>
+          <t>SCHEDULE REGIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Interval - O2-limited (conservative, model optimum, min)</t>
+        </is>
+      </c>
+      <c r="D63" s="80">
+        <f>'Mass Transfer'!$D$68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Interval - carbon-limited if O2 handled by surface (min)</t>
+        </is>
+      </c>
+      <c r="D64" s="80">
+        <f>'Mass Transfer'!$D$113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Which regime</t>
+        </is>
+      </c>
+      <c r="D65" s="80">
+        <f>'Mass Transfer'!$D$114</f>
+        <v/>
+      </c>
+      <c r="E65">
+        <f>'Mass Transfer'!$E$114</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3255,7 +3297,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="64" t="inlineStr">
         <is>
@@ -3604,7 +3645,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="73" t="inlineStr">
         <is>
@@ -3791,7 +3831,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82"/>
     <row r="83">
       <c r="A83" s="72" t="inlineStr">
         <is>
@@ -3799,7 +3838,6 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -4421,7 +4459,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="64" t="inlineStr">
         <is>
@@ -4507,8 +4544,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="73" t="inlineStr">
         <is>
@@ -4686,7 +4721,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="72" t="inlineStr">
         <is>
@@ -4694,7 +4728,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -5685,7 +5718,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="64" t="inlineStr">
         <is>
@@ -5771,8 +5803,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="73" t="inlineStr">
         <is>
@@ -5996,7 +6026,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="73" t="inlineStr">
         <is>
@@ -6167,7 +6196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8089,7 +8118,6 @@
         </is>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="64" t="inlineStr">
         <is>
@@ -8695,7 +8723,6 @@
         </is>
       </c>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
@@ -8786,7 +8813,6 @@
         <v/>
       </c>
     </row>
-    <row r="107"/>
     <row r="108">
       <c r="A108" s="69" t="inlineStr">
         <is>
@@ -8860,6 +8886,43 @@
       <c r="E112" s="95" t="inlineStr">
         <is>
           <t>Conservative shear limit: &lt;1.5 m/s impeller-tip velocity recommended to avoid adverse cell-growth effects (BioProcess International, cell-culture norm); precautionary for robust HOB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Interval if surface stripping handles O2 (carbon-limited)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>spg_int_carbon</t>
+        </is>
+      </c>
+      <c r="D113" s="80">
+        <f>spg_dur_opt/(60*duty_carbon)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Schedule regime (which interval applies)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>sched_regime</t>
+        </is>
+      </c>
+      <c r="D114" s="80">
+        <f>IF(ISNUMBER(DO_ss),IF(DO_ss&lt;DO_impair,"Surface stripping holds DO under impairment - sparge is CARBON-limited (long interval); the O2-limited interval is the conservative fallback until kL_surf is measured","Surface stripping insufficient - sparge must vent O2 - use the O2-limited interval"),"organism DO unknown")</f>
+        <v/>
+      </c>
+      <c r="E114" s="95" t="inlineStr">
+        <is>
+          <t>Resolved by measuring kL_surf (improvement #1).</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9523,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="64" t="inlineStr">
         <is>
@@ -9728,7 +9790,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="69" t="inlineStr">
         <is>
@@ -11251,7 +11312,6 @@
     <row r="47">
       <c r="B47" s="66" t="n"/>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="73" t="n"/>
     </row>
@@ -11268,34 +11328,15 @@
     <row r="52">
       <c r="A52" s="72" t="n"/>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="73" t="n"/>
     </row>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="72" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="72" t="n"/>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="73" t="n"/>
     </row>

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="580" windowWidth="20400" windowHeight="18060" tabRatio="500" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="580" windowWidth="20400" windowHeight="18060" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,8 +11,7 @@
     <sheet name="Electrochemistry" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Biology" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Mass Transfer" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Dosing" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CO2 flows" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CO2 flows" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="por_grade" localSheetId="0">Summary!$D$5</definedName>
@@ -247,40 +246,22 @@
     <definedName name="tip_warn" localSheetId="4">'Mass Transfer'!$D$112</definedName>
     <definedName name="spg_int_carbon" localSheetId="4">'Mass Transfer'!$D$113</definedName>
     <definedName name="sched_regime" localSheetId="4">'Mass Transfer'!$D$114</definedName>
-    <definedName name="CO2_cons" localSheetId="5">Dosing!$D$25</definedName>
-    <definedName name="CO2_pulse" localSheetId="5">Dosing!$D$10</definedName>
-    <definedName name="CO2_sd_ratio" localSheetId="5">Dosing!$D$14</definedName>
-    <definedName name="CO2_supply" localSheetId="5">Dosing!$D$13</definedName>
-    <definedName name="dur_ok" localSheetId="5">Dosing!$D$19</definedName>
-    <definedName name="duty" localSheetId="5">Dosing!$D$15</definedName>
-    <definedName name="M_CO2" localSheetId="5">Dosing!$D$8</definedName>
-    <definedName name="nCO2_rate" localSheetId="5">Dosing!$D$9</definedName>
-    <definedName name="O2_accum" localSheetId="5">Dosing!$D$16</definedName>
-    <definedName name="O2_excess" localSheetId="5">Dosing!$D$22</definedName>
-    <definedName name="O2_strip_pulse" localSheetId="5">Dosing!$D$17</definedName>
-    <definedName name="P_atm" localSheetId="5">Dosing!$D$24</definedName>
-    <definedName name="pulse_floor" localSheetId="5">Dosing!$D$6</definedName>
-    <definedName name="pulses_d" localSheetId="5">Dosing!$D$12</definedName>
-    <definedName name="pulses_h" localSheetId="5">Dosing!$D$11</definedName>
-    <definedName name="Q_CO2" localSheetId="5">Dosing!$D$3</definedName>
-    <definedName name="R_gas" localSheetId="5">Dosing!$D$7</definedName>
-    <definedName name="sched_bal" localSheetId="5">Dosing!$D$18</definedName>
-    <definedName name="sched_mode" localSheetId="5">Dosing!$D$27</definedName>
-    <definedName name="spg_dur" localSheetId="5">Dosing!$D$4</definedName>
-    <definedName name="spg_dur_man" localSheetId="5">Dosing!$D$30</definedName>
-    <definedName name="spg_dur_opt" localSheetId="5">Dosing!$D$28</definedName>
-    <definedName name="spg_int" localSheetId="5">Dosing!$D$5</definedName>
-    <definedName name="spg_int_man" localSheetId="5">Dosing!$D$26</definedName>
-    <definedName name="spg_int_opt" localSheetId="5">Dosing!$D$31</definedName>
-    <definedName name="strip_sparge" localSheetId="5">Dosing!$D$29</definedName>
-    <definedName name="T_K" localSheetId="5">Dosing!$D$23</definedName>
-    <definedName name="Reactor" localSheetId="5">Dosing!$D$34</definedName>
-    <definedName name="flush_factor" localSheetId="5">Dosing!$D$35</definedName>
-    <definedName name="latest_date" localSheetId="5">Dosing!$D$36</definedName>
-    <definedName name="flowrate_cal" localSheetId="5">Dosing!$D$37</definedName>
-    <definedName name="min_sparge_cal" localSheetId="5">Dosing!$D$38</definedName>
-    <definedName name="cal_warning" localSheetId="5">Dosing!$D$41</definedName>
-    <definedName name="has_cal" localSheetId="5">Dosing!$D$39</definedName>
+    <definedName name="Reactor" localSheetId="4">'Mass Transfer'!$D$117</definedName>
+    <definedName name="latest_date" localSheetId="4">'Mass Transfer'!$D$118</definedName>
+    <definedName name="flowrate_cal" localSheetId="4">'Mass Transfer'!$D$119</definedName>
+    <definedName name="min_sparge_cal" localSheetId="4">'Mass Transfer'!$D$120</definedName>
+    <definedName name="has_cal" localSheetId="4">'Mass Transfer'!$D$121</definedName>
+    <definedName name="cal_warning" localSheetId="4">'Mass Transfer'!$D$122</definedName>
+    <definedName name="spg_dur" localSheetId="4">'Mass Transfer'!$D$123</definedName>
+    <definedName name="spg_int" localSheetId="4">'Mass Transfer'!$D$124</definedName>
+    <definedName name="CO2_pulse" localSheetId="4">'Mass Transfer'!$D$125</definedName>
+    <definedName name="pulses_h" localSheetId="4">'Mass Transfer'!$D$126</definedName>
+    <definedName name="pulses_d" localSheetId="4">'Mass Transfer'!$D$127</definedName>
+    <definedName name="CO2_sd_ratio" localSheetId="4">'Mass Transfer'!$D$128</definedName>
+    <definedName name="O2_accum" localSheetId="4">'Mass Transfer'!$D$129</definedName>
+    <definedName name="O2_strip_pulse" localSheetId="4">'Mass Transfer'!$D$130</definedName>
+    <definedName name="sched_bal" localSheetId="4">'Mass Transfer'!$D$131</definedName>
+    <definedName name="dur_ok" localSheetId="4">'Mass Transfer'!$D$132</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -299,7 +280,7 @@
     <numFmt numFmtId="171" formatCode="0.0000000"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -449,6 +430,9 @@
       <color rgb="FF0000FF"/>
       <u val="single"/>
     </font>
+    <font>
+      <color rgb="FF7030A0"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -541,7 +525,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -723,11 +707,12 @@
         <color theme="6"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -858,6 +843,8 @@
     <xf numFmtId="164" fontId="23" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1430,12 +1417,12 @@
           <t>CO₂ supply:demand</t>
         </is>
       </c>
-      <c r="D13" s="62">
-        <f>Dosing!$D$14</f>
+      <c r="D13" s="79">
+        <f>'Mass Transfer'!$D$128</f>
         <v/>
       </c>
       <c r="E13" s="87">
-        <f>HYPERLINK("#Dosing!D14","From Dosing")</f>
+        <f>HYPERLINK("#'Mass Transfer'!D128","From Mass Transfer")</f>
         <v/>
       </c>
     </row>
@@ -1490,12 +1477,12 @@
           <t>Pulse≥floor</t>
         </is>
       </c>
-      <c r="D17" s="62">
-        <f>Dosing!$D$19</f>
+      <c r="D17" s="79">
+        <f>'Mass Transfer'!$D$132</f>
         <v/>
       </c>
       <c r="E17" s="87">
-        <f>HYPERLINK("#Dosing!D19","From Dosing")</f>
+        <f>HYPERLINK("#'Mass Transfer'!D132","From Mass Transfer")</f>
         <v/>
       </c>
     </row>
@@ -1535,12 +1522,12 @@
           <t>Calibration source</t>
         </is>
       </c>
-      <c r="D20" s="76">
-        <f>Dosing!$D$41</f>
+      <c r="D20" s="79">
+        <f>'Mass Transfer'!$D$122</f>
         <v/>
       </c>
       <c r="E20" s="87">
-        <f>HYPERLINK("#Dosing!D41","From Dosing")</f>
+        <f>HYPERLINK("#'Mass Transfer'!D122","From Mass Transfer")</f>
         <v/>
       </c>
     </row>
@@ -4535,7 +4522,7 @@
         </is>
       </c>
       <c r="D27" s="62">
-        <f>Dosing!$D$7</f>
+        <f>'Mass Transfer'!$D$87</f>
         <v/>
       </c>
       <c r="E27" t="inlineStr">
@@ -6196,7 +6183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8310,7 +8297,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>(import) Min reliable pulse (solenoid floor)</t>
+          <t>Min reliable pulse (solenoid floor)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8323,8 +8310,8 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D85" s="62">
-        <f>Dosing!$D$6</f>
+      <c r="D85" s="96">
+        <f>min_sparge_cal</f>
         <v/>
       </c>
       <c r="E85" t="inlineStr">
@@ -8336,7 +8323,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>(import) Average CO₂ supply rate</t>
+          <t>Average CO₂ supply rate</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8349,8 +8336,8 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D86" s="62">
-        <f>Dosing!$D$13</f>
+      <c r="D86" s="96">
+        <f>CO2_pulse*pulses_h</f>
         <v/>
       </c>
       <c r="E86" t="inlineStr">
@@ -8362,7 +8349,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>(import) Ideal gas constant</t>
+          <t>Ideal gas constant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8375,9 +8362,8 @@
           <t>J/mol/K</t>
         </is>
       </c>
-      <c r="D87" s="62">
-        <f>Dosing!$D$7</f>
-        <v/>
+      <c r="D87" s="97" t="n">
+        <v>8.314462618</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -8388,7 +8374,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>(import) CO₂ volumetric flow rate</t>
+          <t>CO₂ volumetric flow rate</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8401,8 +8387,8 @@
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D88" s="62">
-        <f>Dosing!$D$3</f>
+      <c r="D88" s="96">
+        <f>flowrate_cal*60</f>
         <v/>
       </c>
       <c r="E88" t="inlineStr">
@@ -8414,7 +8400,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>(import) Molar mass CO₂</t>
+          <t>Molar mass CO₂</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8427,9 +8413,8 @@
           <t>g/mol</t>
         </is>
       </c>
-      <c r="D89" s="62">
-        <f>Dosing!$D$8</f>
-        <v/>
+      <c r="D89" s="97" t="n">
+        <v>44.0095</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -8440,7 +8425,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>(import) CO₂ molar flow during sparge</t>
+          <t>CO₂ molar flow during sparge</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8453,8 +8438,8 @@
           <t>mol/s</t>
         </is>
       </c>
-      <c r="D90" s="62">
-        <f>Dosing!$D$9</f>
+      <c r="D90" s="96">
+        <f>P_atm*(Q_CO2/1000000/60)/(R_gas*T_K)</f>
         <v/>
       </c>
       <c r="E90" t="inlineStr">
@@ -8466,7 +8451,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>(import) Sparge duty cycle</t>
+          <t>Sparge duty cycle</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8479,8 +8464,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D91" s="62">
-        <f>Dosing!$D$15</f>
+      <c r="D91" s="96">
+        <f>spg_dur/(spg_int*60)</f>
         <v/>
       </c>
       <c r="E91" t="inlineStr">
@@ -8726,7 +8711,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>(import) CO2 per pulse (headspace vols)</t>
+          <t>CO2 per pulse (headspace volumes)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8739,9 +8724,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D102">
-        <f>Dosing!$D$35</f>
-        <v/>
+      <c r="D102" s="97" t="n">
+        <v>1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -8924,6 +8908,269 @@
         <is>
           <t>Resolved by measuring kL_surf (improvement #1).</t>
         </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="69" t="inlineStr">
+        <is>
+          <t>CO₂ DOSING &amp; SCHEDULE (folded from Dosing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Reactor (calibration key)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Reactor</t>
+        </is>
+      </c>
+      <c r="D117" s="79">
+        <f>Summary!$D$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>latest calibration date</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>latest_date</t>
+        </is>
+      </c>
+      <c r="D118" s="80">
+        <f>SUMPRODUCT(MAX(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$J$4:$J$200&gt;0)*'CO2 flows'!$B$4:$B$200))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>flowrate (calibrated)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>flowrate_cal</t>
+        </is>
+      </c>
+      <c r="D119" s="80">
+        <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*'CO2 flows'!$J$4:$J$200)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*('CO2 flows'!$J$4:$J$200&gt;0)*1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>min sparge (calibrated)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>min_sparge_cal</t>
+        </is>
+      </c>
+      <c r="D120" s="80">
+        <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*'CO2 flows'!$I$4:$I$200)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*('CO2 flows'!$J$4:$J$200&gt;0)*1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>reactor has a calibration row?</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>has_cal</t>
+        </is>
+      </c>
+      <c r="D121" s="80">
+        <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$J$4:$J$200&gt;0)*1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>calibration source</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>cal_warning</t>
+        </is>
+      </c>
+      <c r="D122" s="80">
+        <f>IF(has_cal&gt;0,"calibrated: "&amp;Reactor,"NO CALIBRATION for "&amp;Reactor&amp;" - add a row in CO2 flows with nominal flowrate + minimum sparge")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Sparge duration per pulse</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>spg_dur</t>
+        </is>
+      </c>
+      <c r="D123" s="80">
+        <f>IF(sched_mode="Optimal",spg_dur_opt,IF(sched_mode="Manual",spg_dur_man,NA()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Sparge interval</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>spg_int</t>
+        </is>
+      </c>
+      <c r="D124" s="80">
+        <f>IF(sched_mode="Optimal",spg_int_opt,IF(sched_mode="Manual",spg_int_man,NA()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CO₂ per pulse</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CO2_pulse</t>
+        </is>
+      </c>
+      <c r="D125" s="80">
+        <f>nCO2_rate*spg_dur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Pulses per hour</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>pulses_h</t>
+        </is>
+      </c>
+      <c r="D126" s="80">
+        <f>60/spg_int</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Pulses per day</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>pulses_d</t>
+        </is>
+      </c>
+      <c r="D127" s="80">
+        <f>pulses_h*24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>CO₂ supply : carbon demand</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CO2_sd_ratio</t>
+        </is>
+      </c>
+      <c r="D128" s="80">
+        <f>IF(CO2_cons&gt;0,CO2_supply/CO2_cons,NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>O₂ accumulated per interval</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>O2_accum</t>
+        </is>
+      </c>
+      <c r="D129" s="80">
+        <f>O2_excess/60*spg_int</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>O₂ removable per pulse</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>O2_strip_pulse</t>
+        </is>
+      </c>
+      <c r="D130" s="80">
+        <f>strip_sparge/3600*spg_dur</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Per-pulse balance</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>sched_bal</t>
+        </is>
+      </c>
+      <c r="D131" s="80">
+        <f>IF(O2_accum&gt;0,O2_strip_pulse/O2_accum,NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Duration floor check</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>dur_ok</t>
+        </is>
+      </c>
+      <c r="D132" s="80">
+        <f>IF(spg_dur&gt;=pulse_floor,"OK","LOW")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -9045,974 +9292,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="57" t="inlineStr">
-        <is>
-          <t>CO₂ DOSING &amp; SCHEDULE</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="58" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B2" s="58" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C2" s="58" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D2" s="58" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="E2" s="58" t="inlineStr">
-        <is>
-          <t>Source / assumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>CO₂ volumetric flow rate</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Q_CO2</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>mL/min</t>
-        </is>
-      </c>
-      <c r="D3" s="31">
-        <f>flowrate_cal*60</f>
-        <v/>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>Needle-valve setting at ~atmospheric surface. Input.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Sparge duration per pulse</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>spg_dur</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="D4" s="32">
-        <f>IF(sched_mode="Optimal",spg_dur_opt,IF(sched_mode="Manual",spg_dur_man,NA()))</f>
-        <v/>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Pulse duration ACTUALLY USED. Driven by §14: Manual→spg_dur_man, Optimal→computed optimum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Sparge interval</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>spg_int</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D5" s="32">
-        <f>IF(sched_mode="Optimal",spg_int_opt,IF(sched_mode="Manual",spg_int_man,NA()))</f>
-        <v/>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>Sparge interval ACTUALLY USED. Driven by §14: Manual→spg_int_man, Optimal→computed optimum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Min reliable pulse (solenoid floor)</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>pulse_floor</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="D6" s="24">
-        <f>min_sparge_cal</f>
-        <v/>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>Smallest dependable actuation. Provisional - characterise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Ideal gas constant</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>R_gas</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>J/mol/K</t>
-        </is>
-      </c>
-      <c r="D7" s="47" t="n">
-        <v>8.314462618</v>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>NIST CODATA (exact, SI 2019).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Molar mass CO₂</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>M_CO2</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>g/mol</t>
-        </is>
-      </c>
-      <c r="D8" s="48" t="n">
-        <v>44.0095</v>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>NIST WebBook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>CO₂ molar flow during sparge</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>nCO2_rate</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>mol/s</t>
-        </is>
-      </c>
-      <c r="D9" s="49">
-        <f>P_atm*(Q_CO2/1000000/60)/(R_gas*T_K)</f>
-        <v/>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Ideal gas n=PV/RT at surface conditions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>CO₂ per pulse</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>CO2_pulse</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>mol</t>
-        </is>
-      </c>
-      <c r="D10" s="46">
-        <f>nCO2_rate*spg_dur</f>
-        <v/>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Molar flow x duration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Pulses per hour</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>pulses_h</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>1/h</t>
-        </is>
-      </c>
-      <c r="D11" s="32">
-        <f>60/spg_int</f>
-        <v/>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>60 / interval(min).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Pulses per day</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>pulses_d</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>1/d</t>
-        </is>
-      </c>
-      <c r="D12" s="33">
-        <f>pulses_h*24</f>
-        <v/>
-      </c>
-      <c r="E12" s="14" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Average CO₂ supply rate</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>CO2_supply</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>mol/h</t>
-        </is>
-      </c>
-      <c r="D13" s="22">
-        <f>CO2_pulse*pulses_h</f>
-        <v/>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Time-averaged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>CO₂ supply : carbon demand</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>CO2_sd_ratio</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="D14" s="32">
-        <f>IF(CO2_cons&gt;0,CO2_supply/CO2_cons,NA())</f>
-        <v/>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>Carbon supply : demand (~20× = over-dosed, non-limiting). CO₂ mostly bursts at the surface → §11 headspace sweep active from pulse 1. High pCO₂ extends lag (Amer &amp; Kim 2023).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Sparge duty cycle</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>duty</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="37">
-        <f>spg_dur/(spg_int*60)</f>
-        <v/>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Fraction of time sparging.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>O₂ accumulated per interval</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>O2_accum</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>mol</t>
-        </is>
-      </c>
-      <c r="D16" s="46">
-        <f>O2_excess/60*spg_int</f>
-        <v/>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Excess O₂ generated between pulses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>O₂ removable per pulse</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>O2_strip_pulse</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>mol</t>
-        </is>
-      </c>
-      <c r="D17" s="46">
-        <f>strip_sparge/3600*spg_dur</f>
-        <v/>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>O₂ a pulse strips (at ceiling).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>Per-pulse balance</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>sched_bal</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="D18" s="36">
-        <f>IF(O2_accum&gt;0,O2_strip_pulse/O2_accum,NA())</f>
-        <v/>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>&gt;=1 = each pulse clears the interval's O₂ by stripping alone. Bubble path only — the dominant O₂ route is the §11 surface/headspace path; see §14 optimiser.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Duration floor check</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>dur_ok</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" s="45">
-        <f>IF(spg_dur&gt;=pulse_floor,"OK","LOW")</f>
-        <v/>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>Pulse must exceed reliable actuation time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="64" t="inlineStr">
-        <is>
-          <t>IMPORTS (from other tabs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>(import) EXCESS O₂ to remove</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>O2_excess</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>mol/h</t>
-        </is>
-      </c>
-      <c r="D22" s="61">
-        <f>Biology!$D$9</f>
-        <v/>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>(import) Temperature (absolute)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>T_K</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D23" s="61">
-        <f>Biology!$D$11</f>
-        <v/>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>(import) Surface pressure</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>P_atm</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D24" s="61">
-        <f>Biology!$D$12</f>
-        <v/>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>(import) CO₂ consumed (carbon fixation)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CO2_cons</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>mol/h</t>
-        </is>
-      </c>
-      <c r="D25" s="61">
-        <f>Biology!$D$8</f>
-        <v/>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>(import) Manual sparge interval</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>spg_int_man</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D26" s="60">
-        <f>'Mass Transfer'!$D$60</f>
-        <v/>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>(import) Schedule mode</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>sched_mode</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="60">
-        <f>'Mass Transfer'!$D$58</f>
-        <v/>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>(import) ► OPTIMAL pulse duration</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>spg_dur_opt</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="D28" s="60">
-        <f>'Mass Transfer'!$D$67</f>
-        <v/>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>(import) O₂ strip rate at ceiling (sparge on)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>strip_sparge</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>mol/h</t>
-        </is>
-      </c>
-      <c r="D29" s="60">
-        <f>'Mass Transfer'!$D$30</f>
-        <v/>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>(import) Manual pulse duration</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>spg_dur_man</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="D30" s="60">
-        <f>'Mass Transfer'!$D$59</f>
-        <v/>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>(import) ► OPTIMAL sparge interval</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>spg_int_opt</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D31" s="60">
-        <f>'Mass Transfer'!$D$68</f>
-        <v/>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>From Mass Transfer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="69" t="inlineStr">
-        <is>
-          <t>REACTOR CALIBRATION (latest date, from CO2 flows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Reactor (calibration key)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Reactor</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="79">
-        <f>Summary!$D$33</f>
-        <v/>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Selects which CO2 flows calibration to use.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>CO2 per pulse (headspace volumes)</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>flush_factor</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Headspace volumes of CO₂ per pulse. 1.0 = exactly one headspace flush (the minimum that fully sweeps it). Raise for margin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>latest calibration date</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>latest_date</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="80">
-        <f>SUMPRODUCT(MAX(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$J$4:$J$200&gt;0)*'CO2 flows'!$B$4:$B$200))</f>
-        <v/>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Latest date for this reactor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>flowrate (calibrated)</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>flowrate_cal</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ml/s</t>
-        </is>
-      </c>
-      <c r="D37" s="80">
-        <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*'CO2 flows'!$J$4:$J$200)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*('CO2 flows'!$J$4:$J$200&gt;0)*1))</f>
-        <v/>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Pulled from CO2 flows (latest date for reactor).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>min sparge (calibrated)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>min_sparge_cal</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="D38" s="80">
-        <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*'CO2 flows'!$I$4:$I$200)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*('CO2 flows'!$J$4:$J$200&gt;0)*1))</f>
-        <v/>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Pulled from CO2 flows (latest date for reactor).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>reactor has a calibration row?</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>has_cal</t>
-        </is>
-      </c>
-      <c r="D39" s="80">
-        <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$J$4:$J$200&gt;0)*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="D40" s="80" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>calibration source</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>cal_warning</t>
-        </is>
-      </c>
-      <c r="D41" s="80">
-        <f>IF(has_cal&gt;0,"calibrated: "&amp;Reactor,"NO CALIBRATION for "&amp;Reactor&amp;" - add a row in CO2 flows with nominal flowrate + minimum sparge")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="D14">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="num" val="1"/>
-        <cfvo type="num" val="5"/>
-        <cfvo type="num" val="20"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
-      <formula>"LOW"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="11">
-      <formula>OR(ISNUMBER(SEARCH("RISK",D19)),ISNUMBER(SEARCH("OVER",D19)),ISNUMBER(SEARCH("BELOW",D19)),ISNUMBER(SEARCH("EXCEED",D19)),ISNUMBER(SEARCH("NO CALIB",D19)),ISNUMBER(SEARCH("NEAREST",D19)),ISNUMBER(SEARCH("EXPLOSIVE",D19)),ISNUMBER(SEARCH("LOW",D19)),ISNUMBER(SEARCH("TIGHT",D19)),ISNUMBER(SEARCH("insufficient",D19)))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="12">
-      <formula>OR(ISNUMBER(SEARCH("OK",D19)),ISNUMBER(SEARCH("calibrated",D19)),ISNUMBER(SEARCH("under optimum",D19)),ISNUMBER(SEARCH("above min",D19)),ISNUMBER(SEARCH("exact",D19)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D41">
-    <cfRule type="expression" priority="6" dxfId="11">
-      <formula>OR(ISNUMBER(SEARCH("RISK",D41)),ISNUMBER(SEARCH("OVER",D41)),ISNUMBER(SEARCH("BELOW",D41)),ISNUMBER(SEARCH("EXCEED",D41)),ISNUMBER(SEARCH("NO CALIB",D41)),ISNUMBER(SEARCH("NEAREST",D41)),ISNUMBER(SEARCH("EXPLOSIVE",D41)),ISNUMBER(SEARCH("LOW",D41)),ISNUMBER(SEARCH("TIGHT",D41)),ISNUMBER(SEARCH("insufficient",D41)))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" dxfId="12">
-      <formula>OR(ISNUMBER(SEARCH("OK",D41)),ISNUMBER(SEARCH("calibrated",D41)),ISNUMBER(SEARCH("under optimum",D41)),ISNUMBER(SEARCH("above min",D41)),ISNUMBER(SEARCH("exact",D41)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="D58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
-      <formula1>"Manual,Optimal"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor theme="9"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -14,14 +14,16 @@
     <sheet name="CO2 flows" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="por_grade" localSheetId="0">Summary!$D$5</definedName>
-    <definedName name="rx_ver" localSheetId="0">Summary!$D$3</definedName>
-    <definedName name="sparger" localSheetId="0">Summary!$D$4</definedName>
     <definedName name="led_intensity" localSheetId="0">Summary!$D$37</definedName>
     <definedName name="stir_rpm_set" localSheetId="0">Summary!$D$38</definedName>
     <definedName name="media_volume" localSheetId="0">Summary!$D$39</definedName>
     <definedName name="temp_C" localSheetId="0">Summary!$D$40</definedName>
     <definedName name="P_atm_set" localSheetId="0">Summary!$D$41</definedName>
+    <definedName name="Reactor_sel" localSheetId="0">Summary!$D$3</definedName>
+    <definedName name="electrode_sel" localSheetId="0">Summary!$D$4</definedName>
+    <definedName name="organism_sel" localSheetId="0">Summary!$D$5</definedName>
+    <definedName name="media_sel" localSheetId="0">Summary!$D$6</definedName>
+    <definedName name="por_grade" localSheetId="0">Summary!$D$42</definedName>
     <definedName name="A_x" localSheetId="1">Geometry!$D$21</definedName>
     <definedName name="D_int" localSheetId="1">Geometry!$D$22</definedName>
     <definedName name="D_int_1" localSheetId="1">Geometry!$D$12</definedName>
@@ -712,7 +714,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -845,6 +847,9 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1209,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T65"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1255,12 +1260,12 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Reactor version (resolved from reactor)</t>
+          <t>Reactor (select)</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>rx_ver</t>
+          <t>Reactor_sel</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -1268,9 +1273,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D3" s="75">
-        <f>Geometry!$D$51</f>
-        <v/>
+      <c r="D3" s="98" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
@@ -1281,12 +1287,12 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Sparger type (resolved from electrode)</t>
+          <t>Electrode (select)</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>sparger</t>
+          <t>electrode_sel</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -1294,9 +1300,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D4" s="82">
-        <f>Electrochemistry!$D$31</f>
-        <v/>
+      <c r="D4" s="99" t="inlineStr">
+        <is>
+          <t>MMO tube</t>
+        </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
@@ -1307,12 +1314,12 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Sinter porosity grade (if Sintered)</t>
+          <t>HOB organism (select)</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>por_grade</t>
+          <t>organism_sel</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -1320,8 +1327,10 @@
           <t>0-5</t>
         </is>
       </c>
-      <c r="D5" s="30" t="n">
-        <v>5</v>
+      <c r="D5" s="100" t="inlineStr">
+        <is>
+          <t>Cupriavidus necator</t>
+        </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -1329,7 +1338,23 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Media (select)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>media_sel</t>
+        </is>
+      </c>
+      <c r="D6" s="88" t="inlineStr">
+        <is>
+          <t>Sydow 2017 minimal</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="59" t="inlineStr">
         <is>
@@ -1623,7 +1648,6 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="29" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="73" t="inlineStr">
         <is>
@@ -1631,74 +1655,6 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Reactor</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Reactor_sel</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Electrode</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>electrode_sel</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>MMO tube</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>HOB organism</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>organism_sel</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Cupriavidus necator</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>media_sel</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Sydow 2017 minimal</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
@@ -1792,7 +1748,21 @@
         <v>101325</v>
       </c>
     </row>
-    <row r="42"/>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sinter porosity grade (only if sparger = Sintered)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>por_grade</t>
+        </is>
+      </c>
+      <c r="D42" s="88" t="n">
+        <v>5</v>
+      </c>
+    </row>
     <row r="43">
       <c r="A43" s="69" t="inlineStr">
         <is>
@@ -1917,7 +1887,6 @@
         <v/>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="69" t="inlineStr">
         <is>
@@ -2094,7 +2063,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="69" t="inlineStr">
         <is>
@@ -2151,6 +2119,12 @@
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="12">
       <formula>OR(ISNUMBER(SEARCH("OK",D7)),ISNUMBER(SEARCH("calibrated",D7)),ISNUMBER(SEARCH("under optimum",D7)),ISNUMBER(SEARCH("above min",D7)),ISNUMBER(SEARCH("exact",D7)))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="11" stopIfTrue="0">
+      <formula>OR(ISNUMBER(SEARCH("RISK",D7)),ISNUMBER(SEARCH("OVER",D7)),ISNUMBER(SEARCH("BELOW",D7)),ISNUMBER(SEARCH("EXCEED",D7)),ISNUMBER(SEARCH("NO CALIB",D7)),ISNUMBER(SEARCH("NEAREST",D7)),ISNUMBER(SEARCH("EXPLOSIVE",D7)),ISNUMBER(SEARCH("TIGHT",D7)),ISNUMBER(SEARCH("insufficient",D7)),EXACT(D7,"LOW"))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="12" stopIfTrue="0">
+      <formula>OR(EXACT(D7,"OK"),ISNUMBER(SEARCH("calibrated",D7)),ISNUMBER(SEARCH("under optimum",D7)),ISNUMBER(SEARCH("above min",D7)),ISNUMBER(SEARCH("exact",D7)),ISNUMBER(SEARCH("CARBON-limited",D7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D44:D51">
@@ -2160,22 +2134,36 @@
     <cfRule type="expression" priority="4" dxfId="12">
       <formula>OR(ISNUMBER(SEARCH("OK",D44)),ISNUMBER(SEARCH("calibrated",D44)),ISNUMBER(SEARCH("under optimum",D44)),ISNUMBER(SEARCH("above min",D44)),ISNUMBER(SEARCH("exact",D44)))</formula>
     </cfRule>
+    <cfRule type="expression" priority="7" dxfId="11" stopIfTrue="0">
+      <formula>OR(ISNUMBER(SEARCH("RISK",D44)),ISNUMBER(SEARCH("OVER",D44)),ISNUMBER(SEARCH("BELOW",D44)),ISNUMBER(SEARCH("EXCEED",D44)),ISNUMBER(SEARCH("NO CALIB",D44)),ISNUMBER(SEARCH("NEAREST",D44)),ISNUMBER(SEARCH("EXPLOSIVE",D44)),ISNUMBER(SEARCH("TIGHT",D44)),ISNUMBER(SEARCH("insufficient",D44)),EXACT(D44,"LOW"))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="12" stopIfTrue="0">
+      <formula>OR(EXACT(D44,"OK"),ISNUMBER(SEARCH("calibrated",D44)),ISNUMBER(SEARCH("under optimum",D44)),ISNUMBER(SEARCH("above min",D44)),ISNUMBER(SEARCH("exact",D44)),ISNUMBER(SEARCH("CARBON-limited",D44)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D63:D65">
+    <cfRule type="expression" priority="9" dxfId="11" stopIfTrue="0">
+      <formula>OR(ISNUMBER(SEARCH("RISK",D63)),ISNUMBER(SEARCH("OVER",D63)),ISNUMBER(SEARCH("BELOW",D63)),ISNUMBER(SEARCH("EXCEED",D63)),ISNUMBER(SEARCH("NO CALIB",D63)),ISNUMBER(SEARCH("NEAREST",D63)),ISNUMBER(SEARCH("EXPLOSIVE",D63)),ISNUMBER(SEARCH("TIGHT",D63)),ISNUMBER(SEARCH("insufficient",D63)),EXACT(D63,"LOW"))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="12" stopIfTrue="0">
+      <formula>OR(EXACT(D63,"OK"),ISNUMBER(SEARCH("calibrated",D63)),ISNUMBER(SEARCH("under optimum",D63)),ISNUMBER(SEARCH("above min",D63)),ISNUMBER(SEARCH("exact",D63)),ISNUMBER(SEARCH("CARBON-limited",D63)))</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
-      <formula1>"0,1,2,3,4,5"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Geometry!$A$59:$A$88</formula1>
     </dataValidation>
-    <dataValidation sqref="D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Electrochemistry!$A$35:$A$43</formula1>
     </dataValidation>
-    <dataValidation sqref="D35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Biology!$A$52:$A$65</formula1>
     </dataValidation>
-    <dataValidation sqref="D36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Biology!$A$61:$A$69</formula1>
+    </dataValidation>
+    <dataValidation sqref="D42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"0,1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2190,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T87"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2267,7 +2255,7 @@
         </is>
       </c>
       <c r="D5" s="79">
-        <f>Summary!$D$33</f>
+        <f>Summary!$D$3</f>
         <v/>
       </c>
       <c r="E5" t="inlineStr">
@@ -3472,7 +3460,6 @@
         <v/>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="73" t="inlineStr">
         <is>
@@ -3756,7 +3743,6 @@
         </is>
       </c>
     </row>
-    <row r="81"/>
     <row r="82">
       <c r="A82" s="73" t="inlineStr">
         <is>
@@ -3963,7 +3949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4113,7 +4099,7 @@
         </is>
       </c>
       <c r="D8" s="79">
-        <f>Summary!$D$34</f>
+        <f>Summary!$D$4</f>
         <v/>
       </c>
     </row>
@@ -4864,7 +4850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T61"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5014,7 +5000,7 @@
         </is>
       </c>
       <c r="D8" s="79">
-        <f>Summary!$D$35</f>
+        <f>Summary!$D$5</f>
         <v/>
       </c>
     </row>
@@ -6307,7 +6293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T132"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6775,7 +6761,7 @@
         </is>
       </c>
       <c r="D20" s="94">
-        <f>Summary!$D$5</f>
+        <f>Summary!$D$42</f>
         <v/>
       </c>
       <c r="E20" t="inlineStr">
@@ -9440,7 +9426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T75"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="9"/>
@@ -10739,7 +10725,6 @@
     <row r="47">
       <c r="B47" s="66" t="n"/>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="73" t="n"/>
     </row>
@@ -10756,34 +10741,15 @@
     <row r="52">
       <c r="A52" s="72" t="n"/>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="73" t="n"/>
     </row>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="72" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="72" t="n"/>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="73" t="n"/>
     </row>

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -1648,6 +1648,7 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="29" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="73" t="inlineStr">
         <is>
@@ -1655,6 +1656,10 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
@@ -1887,6 +1892,7 @@
         <v/>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="69" t="inlineStr">
         <is>
@@ -2063,6 +2069,7 @@
         </is>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="69" t="inlineStr">
         <is>
@@ -3460,6 +3467,7 @@
         <v/>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="73" t="inlineStr">
         <is>
@@ -3743,6 +3751,7 @@
         </is>
       </c>
     </row>
+    <row r="81"/>
     <row r="82">
       <c r="A82" s="73" t="inlineStr">
         <is>
@@ -9057,7 +9066,7 @@
         </is>
       </c>
       <c r="D115" s="79">
-        <f>Summary!$D$33</f>
+        <f>Summary!$D$3</f>
         <v/>
       </c>
     </row>
@@ -10725,6 +10734,7 @@
     <row r="47">
       <c r="B47" s="66" t="n"/>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="73" t="n"/>
     </row>
@@ -10741,15 +10751,34 @@
     <row r="52">
       <c r="A52" s="72" t="n"/>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="73" t="n"/>
     </row>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="72" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="72" t="n"/>
     </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="73" t="n"/>
     </row>

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -73,6 +73,7 @@
     <definedName name="media_volume" localSheetId="1">Geometry!$D$6</definedName>
     <definedName name="media_vol_warn" localSheetId="1">Geometry!$D$54</definedName>
     <definedName name="depth_warn" localSheetId="1">Geometry!$D$55</definedName>
+    <definedName name="geom_check" localSheetId="1">Geometry!$D$90</definedName>
     <definedName name="etaF" localSheetId="2">Electrochemistry!$D$18</definedName>
     <definedName name="etaF_OER" localSheetId="2">Electrochemistry!$D$26</definedName>
     <definedName name="F_const" localSheetId="2">Electrochemistry!$D$15</definedName>
@@ -714,7 +715,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -850,11 +851,18 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -954,6 +962,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1322,21 +1337,13 @@
           <t>organism_sel</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>0-5</t>
-        </is>
-      </c>
+      <c r="C5" s="9" t="n"/>
       <c r="D5" s="100" t="inlineStr">
         <is>
           <t>Cupriavidus necator</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>ISO 4793 / DURAN class; 0 = coarsest. Dropdown.</t>
-        </is>
-      </c>
+      <c r="E5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1374,7 +1381,7 @@
         </is>
       </c>
       <c r="D8" s="60">
-        <f>'Mass Transfer'!$D$90</f>
+        <f>IFERROR('Mass Transfer'!$D$90,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
       <c r="E8" s="87">
@@ -1385,7 +1392,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>► Optimal interval</t>
+          <t>Optimal interval (conservative, O2-limited) — see SCHEDULE REGIME below</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1394,7 +1401,7 @@
         </is>
       </c>
       <c r="D9" s="60">
-        <f>'Mass Transfer'!$D$91</f>
+        <f>IFERROR('Mass Transfer'!$D$91,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
       <c r="E9" s="87">
@@ -1409,7 +1416,7 @@
         </is>
       </c>
       <c r="D10" s="60">
-        <f>'Mass Transfer'!$D$78</f>
+        <f>IFERROR('Mass Transfer'!$D$78,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
       <c r="E10" s="87">
@@ -1459,7 +1466,7 @@
         </is>
       </c>
       <c r="D13" s="79">
-        <f>'Mass Transfer'!$D$126</f>
+        <f>IFERROR('Mass Transfer'!$D$126,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
       <c r="E13" s="87">
@@ -1519,7 +1526,7 @@
         </is>
       </c>
       <c r="D17" s="79">
-        <f>'Mass Transfer'!$D$130</f>
+        <f>IFERROR('Mass Transfer'!$D$130,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
       <c r="E17" s="87">
@@ -1534,7 +1541,7 @@
         </is>
       </c>
       <c r="D18" s="60">
-        <f>'Mass Transfer'!$D$95</f>
+        <f>IFERROR('Mass Transfer'!$D$95,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
       <c r="E18" s="87">
@@ -1575,14 +1582,18 @@
     <row r="21">
       <c r="A21" s="59" t="inlineStr">
         <is>
-          <t>KEY</t>
-        </is>
+          <t>Vial geometry check</t>
+        </is>
+      </c>
+      <c r="D21">
+        <f>Geometry!$D$90</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Verified / handbook / defined / standard</t>
+      <c r="A22" s="101" t="inlineStr">
+        <is>
+          <t>NOTE: O₂ figures assume etaF=1 (no cathodic O₂ loss) and 100% H₂ uptake — upper bounds until measured</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1659,6 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="29" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="73" t="inlineStr">
         <is>
@@ -1656,10 +1666,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
@@ -1892,7 +1898,6 @@
         <v/>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="69" t="inlineStr">
         <is>
@@ -2069,7 +2074,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="69" t="inlineStr">
         <is>
@@ -2084,7 +2088,7 @@
         </is>
       </c>
       <c r="D63" s="80">
-        <f>'Mass Transfer'!$D$91</f>
+        <f>IFERROR('Mass Transfer'!$D$91,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
     </row>
@@ -2100,7 +2104,7 @@
         </is>
       </c>
       <c r="D64" s="80">
-        <f>'Mass Transfer'!$D$112</f>
+        <f>IFERROR('Mass Transfer'!$D$112,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
     </row>
@@ -2121,53 +2125,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D7:D20">
-    <cfRule type="expression" priority="1" dxfId="11">
-      <formula>OR(ISNUMBER(SEARCH("RISK",D7)),ISNUMBER(SEARCH("OVER",D7)),ISNUMBER(SEARCH("BELOW",D7)),ISNUMBER(SEARCH("EXCEED",D7)),ISNUMBER(SEARCH("NO CALIB",D7)),ISNUMBER(SEARCH("NEAREST",D7)),ISNUMBER(SEARCH("EXPLOSIVE",D7)),ISNUMBER(SEARCH("LOW",D7)),ISNUMBER(SEARCH("TIGHT",D7)),ISNUMBER(SEARCH("insufficient",D7)))</formula>
+    <cfRule type="expression" priority="11" dxfId="11" stopIfTrue="0">
+      <formula>OR(ISNUMBER(SEARCH("RISK",D7)),ISNUMBER(SEARCH("OVER",D7)),ISNUMBER(SEARCH("BELOW",D7)),ISNUMBER(SEARCH("EXCEED",D7)),ISNUMBER(SEARCH("NO CALIB",D7)),ISNUMBER(SEARCH("NEAREST",D7)),ISNUMBER(SEARCH("EXPLOSIVE",D7)),ISNUMBER(SEARCH("TIGHT",D7)),ISNUMBER(SEARCH("insufficient",D7)),ISNUMBER(SEARCH("OOR",D7)),ISNUMBER(SEARCH("calibrate",D7)),ISNUMBER(SEARCH("INCONSISTENT",D7)),EXACT(D7,"OUT"),EXACT(D7,"LOW"))</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="12">
-      <formula>OR(ISNUMBER(SEARCH("OK",D7)),ISNUMBER(SEARCH("calibrated",D7)),ISNUMBER(SEARCH("under optimum",D7)),ISNUMBER(SEARCH("above min",D7)),ISNUMBER(SEARCH("exact",D7)))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="11" stopIfTrue="0">
-      <formula>OR(ISNUMBER(SEARCH("RISK",D7)),ISNUMBER(SEARCH("OVER",D7)),ISNUMBER(SEARCH("BELOW",D7)),ISNUMBER(SEARCH("EXCEED",D7)),ISNUMBER(SEARCH("NO CALIB",D7)),ISNUMBER(SEARCH("NEAREST",D7)),ISNUMBER(SEARCH("EXPLOSIVE",D7)),ISNUMBER(SEARCH("TIGHT",D7)),ISNUMBER(SEARCH("insufficient",D7)),EXACT(D7,"LOW"))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="6" dxfId="12" stopIfTrue="0">
-      <formula>OR(EXACT(D7,"OK"),ISNUMBER(SEARCH("calibrated",D7)),ISNUMBER(SEARCH("under optimum",D7)),ISNUMBER(SEARCH("above min",D7)),ISNUMBER(SEARCH("exact",D7)),ISNUMBER(SEARCH("CARBON-limited",D7)))</formula>
+    <cfRule type="expression" priority="12" dxfId="12" stopIfTrue="0">
+      <formula>OR(EXACT(D7,"OK"),ISNUMBER(SEARCH("calibrated:",D7)),ISNUMBER(SEARCH("under optimum",D7)),ISNUMBER(SEARCH("above min",D7)),ISNUMBER(SEARCH("exact",D7)),ISNUMBER(SEARCH("CARBON-limited",D7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D44:D51">
-    <cfRule type="expression" priority="3" dxfId="11">
-      <formula>OR(ISNUMBER(SEARCH("RISK",D44)),ISNUMBER(SEARCH("OVER",D44)),ISNUMBER(SEARCH("BELOW",D44)),ISNUMBER(SEARCH("EXCEED",D44)),ISNUMBER(SEARCH("NO CALIB",D44)),ISNUMBER(SEARCH("NEAREST",D44)),ISNUMBER(SEARCH("EXPLOSIVE",D44)),ISNUMBER(SEARCH("LOW",D44)),ISNUMBER(SEARCH("TIGHT",D44)),ISNUMBER(SEARCH("insufficient",D44)))</formula>
+    <cfRule type="expression" priority="13" dxfId="11" stopIfTrue="0">
+      <formula>OR(ISNUMBER(SEARCH("RISK",D44)),ISNUMBER(SEARCH("OVER",D44)),ISNUMBER(SEARCH("BELOW",D44)),ISNUMBER(SEARCH("EXCEED",D44)),ISNUMBER(SEARCH("NO CALIB",D44)),ISNUMBER(SEARCH("NEAREST",D44)),ISNUMBER(SEARCH("EXPLOSIVE",D44)),ISNUMBER(SEARCH("TIGHT",D44)),ISNUMBER(SEARCH("insufficient",D44)),ISNUMBER(SEARCH("OOR",D44)),ISNUMBER(SEARCH("calibrate",D44)),ISNUMBER(SEARCH("INCONSISTENT",D44)),EXACT(D44,"OUT"),EXACT(D44,"LOW"))</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="12">
-      <formula>OR(ISNUMBER(SEARCH("OK",D44)),ISNUMBER(SEARCH("calibrated",D44)),ISNUMBER(SEARCH("under optimum",D44)),ISNUMBER(SEARCH("above min",D44)),ISNUMBER(SEARCH("exact",D44)))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" dxfId="11" stopIfTrue="0">
-      <formula>OR(ISNUMBER(SEARCH("RISK",D44)),ISNUMBER(SEARCH("OVER",D44)),ISNUMBER(SEARCH("BELOW",D44)),ISNUMBER(SEARCH("EXCEED",D44)),ISNUMBER(SEARCH("NO CALIB",D44)),ISNUMBER(SEARCH("NEAREST",D44)),ISNUMBER(SEARCH("EXPLOSIVE",D44)),ISNUMBER(SEARCH("TIGHT",D44)),ISNUMBER(SEARCH("insufficient",D44)),EXACT(D44,"LOW"))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" dxfId="12" stopIfTrue="0">
-      <formula>OR(EXACT(D44,"OK"),ISNUMBER(SEARCH("calibrated",D44)),ISNUMBER(SEARCH("under optimum",D44)),ISNUMBER(SEARCH("above min",D44)),ISNUMBER(SEARCH("exact",D44)),ISNUMBER(SEARCH("CARBON-limited",D44)))</formula>
+    <cfRule type="expression" priority="14" dxfId="12" stopIfTrue="0">
+      <formula>OR(EXACT(D44,"OK"),ISNUMBER(SEARCH("calibrated:",D44)),ISNUMBER(SEARCH("under optimum",D44)),ISNUMBER(SEARCH("above min",D44)),ISNUMBER(SEARCH("exact",D44)),ISNUMBER(SEARCH("CARBON-limited",D44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:D65">
-    <cfRule type="expression" priority="9" dxfId="11" stopIfTrue="0">
-      <formula>OR(ISNUMBER(SEARCH("RISK",D63)),ISNUMBER(SEARCH("OVER",D63)),ISNUMBER(SEARCH("BELOW",D63)),ISNUMBER(SEARCH("EXCEED",D63)),ISNUMBER(SEARCH("NO CALIB",D63)),ISNUMBER(SEARCH("NEAREST",D63)),ISNUMBER(SEARCH("EXPLOSIVE",D63)),ISNUMBER(SEARCH("TIGHT",D63)),ISNUMBER(SEARCH("insufficient",D63)),EXACT(D63,"LOW"))</formula>
+    <cfRule type="expression" priority="15" dxfId="11" stopIfTrue="0">
+      <formula>OR(ISNUMBER(SEARCH("RISK",D63)),ISNUMBER(SEARCH("OVER",D63)),ISNUMBER(SEARCH("BELOW",D63)),ISNUMBER(SEARCH("EXCEED",D63)),ISNUMBER(SEARCH("NO CALIB",D63)),ISNUMBER(SEARCH("NEAREST",D63)),ISNUMBER(SEARCH("EXPLOSIVE",D63)),ISNUMBER(SEARCH("TIGHT",D63)),ISNUMBER(SEARCH("insufficient",D63)),ISNUMBER(SEARCH("OOR",D63)),ISNUMBER(SEARCH("calibrate",D63)),ISNUMBER(SEARCH("INCONSISTENT",D63)),EXACT(D63,"OUT"),EXACT(D63,"LOW"))</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="12" stopIfTrue="0">
-      <formula>OR(EXACT(D63,"OK"),ISNUMBER(SEARCH("calibrated",D63)),ISNUMBER(SEARCH("under optimum",D63)),ISNUMBER(SEARCH("above min",D63)),ISNUMBER(SEARCH("exact",D63)),ISNUMBER(SEARCH("CARBON-limited",D63)))</formula>
+    <cfRule type="expression" priority="16" dxfId="12" stopIfTrue="0">
+      <formula>OR(EXACT(D63,"OK"),ISNUMBER(SEARCH("calibrated:",D63)),ISNUMBER(SEARCH("under optimum",D63)),ISNUMBER(SEARCH("above min",D63)),ISNUMBER(SEARCH("exact",D63)),ISNUMBER(SEARCH("CARBON-limited",D63)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="cellIs" priority="17" operator="lessThan" dxfId="11">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D12">
+    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="13">
+      <formula>2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21">
+    <cfRule type="expression" priority="19" dxfId="11" stopIfTrue="0">
+      <formula>ISNUMBER(SEARCH("INCONSISTENT",D21))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="20" dxfId="12" stopIfTrue="0">
+      <formula>EXACT(D21,"OK")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation sqref="D3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Geometry!$A$59:$A$88</formula1>
+      <formula1>=Geometry!$A$59:$A$80</formula1>
     </dataValidation>
     <dataValidation sqref="D4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Electrochemistry!$A$35:$A$43</formula1>
+      <formula1>=Electrochemistry!$A$35:$A$37</formula1>
     </dataValidation>
     <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Biology!$A$52:$A$65</formula1>
+      <formula1>=Biology!$A$52:$A$57</formula1>
     </dataValidation>
     <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Biology!$A$61:$A$69</formula1>
+      <formula1>=Biology!$A$61:$A$61</formula1>
     </dataValidation>
     <dataValidation sqref="D42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0,1,2,3,4,5"</formula1>
@@ -2185,7 +2195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3467,7 +3477,6 @@
         <v/>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="73" t="inlineStr">
         <is>
@@ -3751,7 +3760,6 @@
         </is>
       </c>
     </row>
-    <row r="81"/>
     <row r="82">
       <c r="A82" s="73" t="inlineStr">
         <is>
@@ -3936,6 +3944,22 @@
       </c>
       <c r="I87" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Vial geometry consistency check</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>geom_check</t>
+        </is>
+      </c>
+      <c r="D90">
+        <f>IF(ABS(A_x*D_int/1000-V_vial_total)&gt;3,"VIAL GEOMETRY INCONSISTENT - measure true fill volume &amp; bore depth","OK")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -5141,9 +5165,9 @@
         <f>H2_cons*bio_O2/bio_H2</f>
         <v/>
       </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>H₂ consumed × O₂:H₂. Steady growth only; ~0 during lag.</t>
+      <c r="E14" s="102" t="inlineStr">
+        <is>
+          <t>Assumes 100% H₂ uptake (upper bound); true limit is gas-liquid H₂ transfer — see H2_turnover</t>
         </is>
       </c>
     </row>
@@ -5193,9 +5217,9 @@
         <f>O2_net_gen-O2_cons</f>
         <v/>
       </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Net O₂ (after cathode) minus biological uptake — the surplus to strip.</t>
+      <c r="E16" s="103" t="inlineStr">
+        <is>
+          <t>Upper bound: rests on full-uptake O2_cons above</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8847,7 @@
         </is>
       </c>
       <c r="D102" s="96">
-        <f>flowrate_cal*60</f>
+        <f>IF(has_cal&gt;0,flowrate_cal*60,NA())</f>
         <v/>
       </c>
       <c r="E102" t="inlineStr">
@@ -8952,6 +8976,11 @@
           <t>DO_ss</t>
         </is>
       </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
       <c r="D108" s="80">
         <f>O2_excess/(kLa_surf_used*3600*(V_charge/1000000))*32</f>
         <v/>
@@ -9021,6 +9050,11 @@
           <t>spg_int_carbon</t>
         </is>
       </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
       <c r="D112" s="80">
         <f>spg_dur_opt/(60*duty_carbon)</f>
         <v/>
@@ -9097,6 +9131,11 @@
           <t>flowrate_cal</t>
         </is>
       </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ml/s</t>
+        </is>
+      </c>
       <c r="D117" s="80">
         <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*'CO2 flows'!$J$4:$J$200)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*('CO2 flows'!$J$4:$J$200&gt;0)*1))</f>
         <v/>
@@ -9113,6 +9152,11 @@
           <t>min_sparge_cal</t>
         </is>
       </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="D118" s="80">
         <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*'CO2 flows'!$I$4:$I$200)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$B$4:$B$200=latest_date)*('CO2 flows'!$J$4:$J$200&gt;0)*1))</f>
         <v/>
@@ -9129,6 +9173,11 @@
           <t>has_cal</t>
         </is>
       </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
       <c r="D119" s="80">
         <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$200=Reactor)*('CO2 flows'!$J$4:$J$200&gt;0)*1)</f>
         <v/>
@@ -9161,6 +9210,11 @@
           <t>spg_dur</t>
         </is>
       </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="D121" s="80">
         <f>IF(sched_mode="Optimal",spg_dur_opt,IF(sched_mode="Manual",spg_dur_man,NA()))</f>
         <v/>
@@ -9177,6 +9231,11 @@
           <t>spg_int</t>
         </is>
       </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
       <c r="D122" s="80">
         <f>IF(sched_mode="Optimal",spg_int_opt,IF(sched_mode="Manual",spg_int_man,NA()))</f>
         <v/>
@@ -9193,6 +9252,11 @@
           <t>CO2_pulse</t>
         </is>
       </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>mol</t>
+        </is>
+      </c>
       <c r="D123" s="80">
         <f>nCO2_rate*spg_dur</f>
         <v/>
@@ -9209,6 +9273,11 @@
           <t>pulses_h</t>
         </is>
       </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>/h</t>
+        </is>
+      </c>
       <c r="D124" s="80">
         <f>60/spg_int</f>
         <v/>
@@ -9225,6 +9294,11 @@
           <t>pulses_d</t>
         </is>
       </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>/d</t>
+        </is>
+      </c>
       <c r="D125" s="80">
         <f>pulses_h*24</f>
         <v/>
@@ -9241,6 +9315,11 @@
           <t>CO2_sd_ratio</t>
         </is>
       </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
       <c r="D126" s="80">
         <f>IF(CO2_cons&gt;0,CO2_supply/CO2_cons,NA())</f>
         <v/>
@@ -9257,6 +9336,11 @@
           <t>O2_accum</t>
         </is>
       </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>mol</t>
+        </is>
+      </c>
       <c r="D127" s="80">
         <f>O2_excess/60*spg_int</f>
         <v/>
@@ -9273,6 +9357,11 @@
           <t>O2_strip_pulse</t>
         </is>
       </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>mol</t>
+        </is>
+      </c>
       <c r="D128" s="80">
         <f>strip_sparge/3600*spg_dur</f>
         <v/>
@@ -9287,6 +9376,11 @@
       <c r="B129" t="inlineStr">
         <is>
           <t>sched_bal</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ratio</t>
         </is>
       </c>
       <c r="D129" s="80">
@@ -9347,17 +9441,6 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D40">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
-      <formula>"Static"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2">
-      <formula>"Dynamic"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
-      <formula>"Sinter OOR – add fine-bubble model"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
@@ -9424,6 +9507,11 @@
       <formula>OR(ISNUMBER(SEARCH("OK",D110)),ISNUMBER(SEARCH("calibrated",D110)),ISNUMBER(SEARCH("under optimum",D110)),ISNUMBER(SEARCH("above min",D110)),ISNUMBER(SEARCH("exact",D110)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D64">
+    <cfRule type="expression" priority="15" dxfId="11" stopIfTrue="0">
+      <formula>ISNUMBER(SEARCH("OOR",D64))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10734,7 +10822,6 @@
     <row r="47">
       <c r="B47" s="66" t="n"/>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="73" t="n"/>
     </row>
@@ -10751,34 +10838,15 @@
     <row r="52">
       <c r="A52" s="72" t="n"/>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="73" t="n"/>
     </row>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="72" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="72" t="n"/>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="73" t="n"/>
     </row>

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -715,7 +715,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -858,6 +858,7 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1598,9 +1599,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Literature-supported (~90%)</t>
+      <c r="A23" s="104" t="inlineStr">
+        <is>
+          <t>NOTE: headspace &amp; optimal pulse are PROVISIONAL pending a fill-to-septum vial measurement (see Geometry consistency check)</t>
         </is>
       </c>
     </row>
@@ -5343,11 +5344,11 @@
         </is>
       </c>
       <c r="D21" s="44" t="n">
-        <v>1.3e-05</v>
+        <v>1.2e-05</v>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Sander (2023) compilation (supersedes 2015), value from Burkholder et al. 2019.</t>
+          <t>Sander (2023) recommended H^cp O2; reproduces ~7.5 mg/L air-saturation at 30 degC</t>
         </is>
       </c>
     </row>

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -265,6 +265,7 @@
     <definedName name="O2_strip_pulse" localSheetId="4">'Mass Transfer'!$D$128</definedName>
     <definedName name="sched_bal" localSheetId="4">'Mass Transfer'!$D$129</definedName>
     <definedName name="dur_ok" localSheetId="4">'Mass Transfer'!$D$130</definedName>
+    <definedName name="kL_surf_crit" localSheetId="4">'Mass Transfer'!$D$131</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -715,7 +716,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -859,6 +860,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1678,6 +1695,11 @@
           <t>led_intensity</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="D37" s="88" t="n">
         <v>3</v>
       </c>
@@ -2326,9 +2348,9 @@
           <t>AEP0.1.1</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>Current build (20 mL Pioreactor vial, assumed).</t>
+      <c r="E8" s="102" t="inlineStr">
+        <is>
+          <t>Per-version inputs SUPERSEDED by the reactor-type lookup (below) - retained for reference only, not read by formulas</t>
         </is>
       </c>
     </row>
@@ -4189,9 +4211,9 @@
       <c r="D11" s="40" t="n">
         <v>1.03</v>
       </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Empirical current-vs-intensity fit (constant-current; electrolyte/volume-independent).</t>
+      <c r="E11" s="105" t="inlineStr">
+        <is>
+          <t>Gerrit's Law fit (slope) - from LED-current calibration; see protocol gerrit-current.md</t>
         </is>
       </c>
     </row>
@@ -4214,9 +4236,9 @@
       <c r="D12" s="41" t="n">
         <v>2.6</v>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Intercept of the same fit.</t>
+      <c r="E12" s="105" t="inlineStr">
+        <is>
+          <t>Gerrit's Law fit (intercept); calibration-derived constant</t>
         </is>
       </c>
     </row>
@@ -4571,9 +4593,9 @@
       <c r="D26" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="25" t="inlineStr">
-        <is>
-          <t>OER at the anode assumed ~100% faradaic; the cell's inefficiency is cathodic (O₂ reduction competing with H₂), not anodic. Design assumption.</t>
+      <c r="E26" s="106" t="inlineStr">
+        <is>
+          <t>Assumes chloride-free medium (no competing Cl2 evolution at the anode)</t>
         </is>
       </c>
     </row>
@@ -6070,9 +6092,9 @@
       <c r="E52" t="n">
         <v>11.5</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Amer &amp; Kim 2023; Wilde &amp; Schlegel 1982</t>
+      <c r="F52" s="72" t="inlineStr">
+        <is>
+          <t>11.5 = Wilde &amp; Schlegel 1982 literature datum; model's operative O2 ceiling is computed via Henry (~10.7 mg/L at 30C) - the two differ slightly</t>
         </is>
       </c>
     </row>
@@ -7583,9 +7605,9 @@
         <f>kLa_sparge*duty</f>
         <v/>
       </c>
-      <c r="E53" s="20" t="inlineStr">
-        <is>
-          <t>x duty cycle.</t>
+      <c r="E53" s="107" t="inlineStr">
+        <is>
+          <t>Sparge-on regime only; not meaningful in the surface-strip-dominated default</t>
         </is>
       </c>
     </row>
@@ -7815,9 +7837,9 @@
         <f>(Q_CO2/1000000/60)/(n_pores_active*(PI()/4*d_orifice^2))</f>
         <v/>
       </c>
-      <c r="E62" s="23" t="inlineStr">
-        <is>
-          <t>Per-orifice superficial gas velocity during a sparge pulse.</t>
+      <c r="E62" s="108" t="inlineStr">
+        <is>
+          <t>Sparge-on regime only; not meaningful in the surface-strip-dominated default</t>
         </is>
       </c>
     </row>
@@ -7841,9 +7863,9 @@
         <f>rho_CO2*v_orifice^2*d_orifice/sigma</f>
         <v/>
       </c>
-      <c r="E63" s="23" t="inlineStr">
-        <is>
-          <t>Gas inertia vs surface tension at the orifice. Sets whether bubble detachment is quasi-static.</t>
+      <c r="E63" s="108" t="inlineStr">
+        <is>
+          <t>Sparge-on regime only; not meaningful in the surface-strip-dominated default</t>
         </is>
       </c>
     </row>
@@ -8231,9 +8253,9 @@
         <f>IF(O2_excess&gt;0,(strip_avg+surf_strip)/O2_excess,NA())</f>
         <v/>
       </c>
-      <c r="E78" s="53" t="inlineStr">
-        <is>
-          <t>Gas removal (bubble + surface) vs the steady-growth surplus O2_excess (which already nets the cathodic sink and biological uptake). &gt;=1 = ceiling held at steady growth.</t>
+      <c r="E78" s="109" t="inlineStr">
+        <is>
+          <t>Upper bound: surface + sparge O2 sinks are in series (liquid-&gt;headspace-&gt;vent), not strictly additive</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9428,30 @@
       </c>
     </row>
     <row r="131">
-      <c r="D131" s="80" t="n"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Critical surface kL_surf (DO_ss = impairment DO)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>kL_surf_crit</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D131" s="80">
+        <f>O2_excess*32/(DO_impair*3600*(V_charge/1000000)*a_surf)</f>
+        <v/>
+      </c>
+      <c r="E131" s="72" t="inlineStr">
+        <is>
+          <t>Measured kL_surf must EXCEED this or DO_ss breaches impairment; current model kL_surf vs this = the safety margin. See protocol surface-kla.md</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="D132" s="80" t="n"/>
@@ -9664,10 +9709,10 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="110" t="n">
         <v>0.25</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="110" t="n">
         <v>3.33</v>
       </c>
       <c r="L4" s="67" t="inlineStr">
@@ -10130,6 +10175,11 @@
         <f>E20/F20</f>
         <v/>
       </c>
+      <c r="L20" s="69" t="inlineStr">
+        <is>
+          <t>HOW TO ADD A CALIBRATION</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10157,6 +10207,11 @@
         <f>E21/F21</f>
         <v/>
       </c>
+      <c r="L21" s="72" t="inlineStr">
+        <is>
+          <t>1. Add a row: reactor ID (col A), date (col B), then the burst measurements (vol/time).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10184,6 +10239,11 @@
         <f>E22/F22</f>
         <v/>
       </c>
+      <c r="L22" s="72" t="inlineStr">
+        <is>
+          <t>2. Enter the chosen nominal flowrate (col J, ml/s) and minimum reliable sparge (col I, s) for that reactor+date.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10211,6 +10271,11 @@
         <f>E23/F23</f>
         <v/>
       </c>
+      <c r="L23" s="72" t="inlineStr">
+        <is>
+          <t>3. The model reads the LATEST dated J/I for the selected reactor automatically.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10227,6 +10292,11 @@
       <c r="D24" t="n">
         <v>31</v>
       </c>
+      <c r="L24" s="72" t="inlineStr">
+        <is>
+          <t>Derivation (ed04): nominal 3.33 ml/s = inspection-set max (no bubbles into the neck), confirmed by long-pulse slope;</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10258,6 +10328,11 @@
         <f>AVERAGE(G25:G29)</f>
         <v/>
       </c>
+      <c r="L25" s="72" t="inlineStr">
+        <is>
+          <t>min sparge 0.25 s = shortest repeatable shot (1 ml); at &lt;=0.2 s per-pulse flow is erratic (open/close bolus dominates). See protocol: flow-calibration.md</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10520,10 +10595,6 @@
       </c>
       <c r="D35" t="n">
         <v>0</v>
-      </c>
-      <c r="E35">
-        <f>D35-D34</f>
-        <v/>
       </c>
     </row>
     <row r="36">

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -284,7 +284,7 @@
     <numFmt numFmtId="171" formatCode="0.0000000"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -436,6 +436,11 @@
     </font>
     <font>
       <color rgb="FF7030A0"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
+      <sz val="9"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="17">
@@ -716,7 +721,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -876,6 +881,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1607,6 +1613,10 @@
         <f>Geometry!$D$90</f>
         <v/>
       </c>
+      <c r="E21" s="111">
+        <f>HYPERLINK("protocols/vial-geometry.md","→ vial-geometry.md")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="101" t="inlineStr">
@@ -1937,6 +1947,10 @@
           <t>Effort</t>
         </is>
       </c>
+      <c r="D53" s="111">
+        <f>HYPERLINK("protocols/README.md","all protocols →")</f>
+        <v/>
+      </c>
       <c r="E53" s="69" t="inlineStr">
         <is>
           <t>Why it matters</t>
@@ -1959,6 +1973,10 @@
           <t>med</t>
         </is>
       </c>
+      <c r="D54" s="111">
+        <f>HYPERLINK("protocols/surface-kla.md","protocol →")</f>
+        <v/>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>375% sensitivity; decides whether DO stays in the organism band</t>
@@ -1981,6 +1999,10 @@
           <t>med</t>
         </is>
       </c>
+      <c r="D55" s="111">
+        <f>HYPERLINK("protocols/faradaic-efficiency.md","protocol →")</f>
+        <v/>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>sets the H2/O2 split and net O2; currently assumed 1.0</t>
@@ -2003,6 +2025,10 @@
           <t>low</t>
         </is>
       </c>
+      <c r="D56" s="111">
+        <f>HYPERLINK("protocols/dissolved-oxygen.md","protocol →")</f>
+        <v/>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>lower DO guardrail; currently a gap for every organism</t>
@@ -2025,6 +2051,10 @@
           <t>low</t>
         </is>
       </c>
+      <c r="D57" s="111">
+        <f>HYPERLINK("protocols/flow-calibration.md","protocol →")</f>
+        <v/>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>each experiment; only ed04 calibrated so far</t>
@@ -2047,6 +2077,10 @@
           <t>high</t>
         </is>
       </c>
+      <c r="D58" s="111">
+        <f>HYPERLINK("protocols/knallgas-stoichiometry.md","protocol →")</f>
+        <v/>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>carbon/O2 balance; needs a growing culture</t>
@@ -2069,6 +2103,10 @@
           <t>low</t>
         </is>
       </c>
+      <c r="D59" s="111">
+        <f>HYPERLINK("protocols/sinter-porosity.md","protocol →")</f>
+        <v/>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>bubble size when sparger = sintered</t>
@@ -2090,6 +2128,10 @@
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="D60" s="111">
+        <f>HYPERLINK("protocols/README.md","protocol →")</f>
+        <v/>
       </c>
       <c r="E60" t="inlineStr">
         <is>

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -283,7 +283,7 @@
     <numFmt numFmtId="170" formatCode="0.0000000"/>
     <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -455,6 +455,10 @@
     <font>
       <b val="1"/>
       <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="17">
@@ -732,7 +736,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -890,6 +894,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1401,7 +1406,7 @@
       </c>
       <c r="D4" s="104" t="inlineStr">
         <is>
-          <t>MMO tube 5</t>
+          <t>MMO Tubular</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -2287,7 +2292,7 @@
       <formula1>=Geometry!$A$59:$A$80</formula1>
     </dataValidation>
     <dataValidation sqref="D4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Electrochemistry!$A$35:$A$42</formula1>
+      <formula1>=Electrochemistry!$A$35:$A$37</formula1>
     </dataValidation>
     <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Biology!$A$52:$A$57</formula1>
@@ -4706,7 +4711,7 @@
         </is>
       </c>
       <c r="D27" s="69">
-        <f>VLOOKUP(electrode_sel,$A$35:$I$42,9,FALSE)</f>
+        <f>VLOOKUP(electrode_sel,$A$35:$I$37,9,FALSE)</f>
         <v/>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -4786,7 +4791,7 @@
         </is>
       </c>
       <c r="D31" s="72">
-        <f>VLOOKUP(electrode_sel,$A$35:$I$42,4,FALSE)</f>
+        <f>VLOOKUP(electrode_sel,$A$35:$I$37,4,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -4802,8 +4807,13 @@
         </is>
       </c>
       <c r="D32" s="105">
-        <f>IF(ISNUMBER(VLOOKUP(electrode_sel,$A$35:$I$42,5,FALSE)),VLOOKUP(electrode_sel,$A$35:$I$42,5,FALSE),0)</f>
-        <v/>
+        <f>IF(ISNUMBER(VLOOKUP(electrode_sel,$A$35:$I$37,5,FALSE)),VLOOKUP(electrode_sel,$A$35:$I$37,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="E32" s="109" t="inlineStr">
+        <is>
+          <t>Porosity 0 = Gerrit's sourced sintered disc (SD8/0/P 8mm, fallback SD10/0/P 10mm; Scientific Glass Labs, 2026-05)</t>
+        </is>
       </c>
       <c r="H32" s="68" t="n"/>
     </row>
@@ -4946,7 +4956,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MMO tube 0</t>
+          <t>MMO Tubular</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4983,200 +4993,14 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>MMO tube 1</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>MMO</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>6</v>
-      </c>
-      <c r="D38" s="71" t="inlineStr">
-        <is>
-          <t>Sintered</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>SS rod</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>6</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>2</v>
-      </c>
+      <c r="D38" s="71" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>MMO tube 2</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>MMO</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>6</v>
-      </c>
-      <c r="D39" s="72" t="inlineStr">
-        <is>
-          <t>Sintered</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>SS rod</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>6</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>MMO tube 3</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>MMO</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>6</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Sintered</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>SS rod</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>6</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>MMO tube 4</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>MMO</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>6</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Sintered</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>SS rod</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>6</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>MMO tube 5</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>MMO</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>6</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Sintered</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>SS rod</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>6</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>2</v>
-      </c>
-    </row>
+      <c r="D39" s="72" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
   </sheetData>
   <conditionalFormatting sqref="D13">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -283,7 +283,7 @@
     <numFmt numFmtId="170" formatCode="0.0000000"/>
     <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -460,8 +460,22 @@
       <i val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <color rgb="FF7030A0"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -551,8 +565,23 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -732,11 +761,81 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="6"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="thin">
+        <color theme="6"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF0000FF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF0000FF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF0000FF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF0000FF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="7"/>
+      </left>
+      <right style="thin">
+        <color theme="7"/>
+      </right>
+      <top style="thin">
+        <color theme="7"/>
+      </top>
+      <bottom style="thin">
+        <color theme="7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
+      <right style="thin">
+        <color theme="5"/>
+      </right>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="8"/>
+      </left>
+      <right style="thin">
+        <color theme="8"/>
+      </right>
+      <top style="thin">
+        <color theme="8"/>
+      </top>
+      <bottom style="thin">
+        <color theme="8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -895,6 +994,25 @@
     <xf numFmtId="170" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1318,13 +1436,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="37.5" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1357,7 +1477,12 @@
       </c>
       <c r="E2" s="53" t="inlineStr">
         <is>
-          <t>Source / assumption</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Comment</t>
         </is>
       </c>
     </row>
@@ -1553,16 +1678,16 @@
       <c r="D12" s="103" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1" thickBot="1">
-      <c r="A13" s="54" t="inlineStr">
-        <is>
-          <t>RESULTS (imported — border = source tab)</t>
+      <c r="A13" s="110" t="inlineStr">
+        <is>
+          <t>KEY RESULTS  — enter these two into the plugin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>► Optimal pulse</t>
+      <c r="A14" s="110" t="inlineStr">
+        <is>
+          <t>CO₂ pulse duration</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1570,19 +1695,24 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="111">
         <f>IFERROR('Mass Transfer'!$D$90,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
-      <c r="E14" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D90","From Mass Transfer")</f>
-        <v/>
+      <c r="E14" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D90","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F14" s="109" t="inlineStr">
+        <is>
+          <t>How long to open the CO2 solenoid each dose.</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Optimal interval (conservative, O2-limited) — see SCHEDULE REGIME below</t>
+      <c r="A15" s="110" t="inlineStr">
+        <is>
+          <t>CO₂ sparge interval</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1590,433 +1720,609 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="111">
         <f>IFERROR('Mass Transfer'!$D$91,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
-      <c r="E15" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D91","From Mass Transfer")</f>
-        <v/>
+      <c r="E15" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D91","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F15" s="109" t="inlineStr">
+        <is>
+          <t>Time between doses (conservative, O2-safe). The 'interval can be relaxed?' check below says if you can dose less often.</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>O₂ removal : surplus</t>
-        </is>
-      </c>
-      <c r="D16" s="55">
-        <f>IFERROR('Mass Transfer'!$D$78,"calibrate this reactor first (see CO2 flows)")</f>
-        <v/>
-      </c>
-      <c r="E16" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D78","From Mass Transfer")</f>
-        <v/>
-      </c>
+      <c r="D16" s="55" t="n"/>
+      <c r="E16" s="78" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>O₂ time-to-ceiling lag</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D17" s="55">
-        <f>'Mass Transfer'!$D$79</f>
-        <v/>
-      </c>
-      <c r="E17" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D79","From Mass Transfer")</f>
-        <v/>
-      </c>
+      <c r="A17" s="110" t="inlineStr">
+        <is>
+          <t>CHECKS  — if every one is GREEN, trust the two results above and enter them</t>
+        </is>
+      </c>
+      <c r="D17" s="55" t="n"/>
+      <c r="E17" s="78" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Carbon margin</t>
-        </is>
-      </c>
-      <c r="D18" s="56">
-        <f>Biology!$D$35</f>
-        <v/>
-      </c>
-      <c r="E18" s="78">
-        <f>HYPERLINK("#Biology!D35","From Biology")</f>
-        <v/>
+          <t>Vial geometry consistent?</t>
+        </is>
+      </c>
+      <c r="D18" s="113">
+        <f>Geometry!$D$90</f>
+        <v/>
+      </c>
+      <c r="E18" s="112">
+        <f>HYPERLINK("#Geometry!D90","→ Geometry")</f>
+        <v/>
+      </c>
+      <c r="F18" s="109" t="inlineStr">
+        <is>
+          <t>Red until the vial headspace is measured (vial-geometry.md). While red, the pulse above is provisional (~4x uncertain).</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CO₂ supply:demand</t>
-        </is>
-      </c>
-      <c r="D19" s="71">
-        <f>IFERROR('Mass Transfer'!$D$126,"calibrate this reactor first (see CO2 flows)")</f>
-        <v/>
-      </c>
-      <c r="E19" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D126","From Mass Transfer")</f>
-        <v/>
+          <t>Reactor calibrated?</t>
+        </is>
+      </c>
+      <c r="D19" s="114">
+        <f>'Mass Transfer'!$D$120</f>
+        <v/>
+      </c>
+      <c r="E19" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D120","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F19" s="109" t="inlineStr">
+        <is>
+          <t>Red = no CO2-flow calibration for this reactor; results read 'calibrate first' (flow-calibration.md).</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Current-law</t>
-        </is>
-      </c>
-      <c r="D20" s="58">
-        <f>Electrochemistry!$D$20</f>
-        <v/>
-      </c>
-      <c r="E20" s="78">
-        <f>HYPERLINK("#Electrochemistry!D20","From Electrochemistry")</f>
-        <v/>
+          <t>O₂ at/under organism optimum?</t>
+        </is>
+      </c>
+      <c r="D20" s="115">
+        <f>'Mass Transfer'!$D$109</f>
+        <v/>
+      </c>
+      <c r="E20" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D109","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F20" s="109" t="inlineStr">
+        <is>
+          <t>Green = dissolved O2 sits at/under the organism optimum; red = surface stripping insufficient, O2 may breach impairment.</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Carryover</t>
-        </is>
-      </c>
-      <c r="D21" s="55">
-        <f>'Mass Transfer'!$D$59</f>
-        <v/>
-      </c>
-      <c r="E21" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D59","From Mass Transfer")</f>
-        <v/>
+          <t>O₂ above organism minimum?</t>
+        </is>
+      </c>
+      <c r="D21" s="115">
+        <f>'Mass Transfer'!$D$110</f>
+        <v/>
+      </c>
+      <c r="E21" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D110","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F21" s="109" t="inlineStr">
+        <is>
+          <t>Minimum DO is a data gap for most organisms (dissolved-oxygen.md).</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bubble regime</t>
-        </is>
-      </c>
-      <c r="D22" s="55">
-        <f>'Mass Transfer'!$D$64</f>
-        <v/>
-      </c>
-      <c r="E22" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D64","From Mass Transfer")</f>
-        <v/>
+          <t>Interval can be relaxed (carbon-limited)?</t>
+        </is>
+      </c>
+      <c r="D22" s="115">
+        <f>'Mass Transfer'!$D$113</f>
+        <v/>
+      </c>
+      <c r="E22" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D113","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F22" s="109" t="inlineStr">
+        <is>
+          <t>If surface stripping handles O2 you may dose far less often (the carbon-limited interval, in Supporting figures). The interval above is the safe fallback until kL_surf is measured.</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pulse≥floor</t>
-        </is>
-      </c>
-      <c r="D23" s="71">
-        <f>IFERROR('Mass Transfer'!$D$130,"calibrate this reactor first (see CO2 flows)")</f>
-        <v/>
-      </c>
-      <c r="E23" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D130","From Mass Transfer")</f>
-        <v/>
+          <t>H₂ headspace safe?</t>
+        </is>
+      </c>
+      <c r="D23" s="116">
+        <f>Biology!$D$44</f>
+        <v/>
+      </c>
+      <c r="E23" s="112">
+        <f>HYPERLINK("#Biology!D44","→ Biology")</f>
+        <v/>
+      </c>
+      <c r="F23" s="109" t="inlineStr">
+        <is>
+          <t>EXPLOSIVE = H2 evolves faster than it dissolves; ensure headspace venting and no ignition source.</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OD window</t>
-        </is>
-      </c>
-      <c r="D24" s="55">
-        <f>IFERROR('Mass Transfer'!$D$95,"calibrate this reactor first (see CO2 flows)")</f>
-        <v/>
-      </c>
-      <c r="E24" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D95","From Mass Transfer")</f>
-        <v/>
+          <t>Bubble model valid?</t>
+        </is>
+      </c>
+      <c r="D24" s="115">
+        <f>'Mass Transfer'!$D$64</f>
+        <v/>
+      </c>
+      <c r="E24" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D64","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F24" s="109" t="inlineStr">
+        <is>
+          <t>'Sinter OOR' = sinter pore size out of the validated bubble range; sparge mass-transfer is approximate (expected for the porosity-0 disc).</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>H₂ headspace</t>
-        </is>
-      </c>
-      <c r="D25" s="56">
-        <f>Biology!$D$44</f>
-        <v/>
-      </c>
-      <c r="E25" s="78">
-        <f>HYPERLINK("#Biology!D44","From Biology")</f>
-        <v/>
+          <t>CO₂ supply meets demand?</t>
+        </is>
+      </c>
+      <c r="D25" s="115">
+        <f>IFERROR('Mass Transfer'!$D$126,"calibrate this reactor first (see CO2 flows)")</f>
+        <v/>
+      </c>
+      <c r="E25" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D126","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F25" s="109" t="inlineStr">
+        <is>
+          <t>Ratio of CO2 supplied to carbon demand; should be &gt;= 1.</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Calibration source</t>
-        </is>
-      </c>
-      <c r="D26" s="71">
-        <f>'Mass Transfer'!$D$120</f>
-        <v/>
-      </c>
-      <c r="E26" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D120","From Mass Transfer")</f>
-        <v/>
+          <t>Pulse ≥ solenoid floor?</t>
+        </is>
+      </c>
+      <c r="D26" s="114">
+        <f>IFERROR('Mass Transfer'!$D$130,"calibrate this reactor first (see CO2 flows)")</f>
+        <v/>
+      </c>
+      <c r="E26" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D130","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F26" s="109" t="inlineStr">
+        <is>
+          <t>The optimal pulse must exceed the shortest reliable sparge.</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="54" t="inlineStr">
         <is>
-          <t>Vial geometry check</t>
-        </is>
-      </c>
-      <c r="D27">
-        <f>Geometry!$D$90</f>
-        <v/>
-      </c>
-      <c r="E27" s="102">
-        <f>HYPERLINK("protocols/vial-geometry.md","→ vial-geometry.md")</f>
-        <v/>
+          <t>Dosing window OK?</t>
+        </is>
+      </c>
+      <c r="D27" s="115">
+        <f>IFERROR('Mass Transfer'!$D$95,"calibrate this reactor first (see CO2 flows)")</f>
+        <v/>
+      </c>
+      <c r="E27" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D95","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F27" s="109" t="inlineStr">
+        <is>
+          <t>Enough gap between doses to read OD without sparging.</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="92" t="inlineStr">
         <is>
-          <t>NOTE: O₂ figures assume etaF=1 (no cathodic O₂ loss) and 100% H₂ uptake — upper bounds until measured</t>
+          <t>Carryover risk?</t>
+        </is>
+      </c>
+      <c r="D28" s="115">
+        <f>'Mass Transfer'!$D$59</f>
+        <v/>
+      </c>
+      <c r="E28" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D59","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F28" s="109" t="inlineStr">
+        <is>
+          <t>Gas velocity below the entrainment limit (no liquid carried out).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="95" t="inlineStr">
         <is>
-          <t>NOTE: headspace &amp; optimal pulse are PROVISIONAL pending a fill-to-septum vial measurement (see Geometry consistency check)</t>
+          <t>Tip-speed shear OK?</t>
+        </is>
+      </c>
+      <c r="D29" s="115">
+        <f>'Mass Transfer'!$D$111</f>
+        <v/>
+      </c>
+      <c r="E29" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D111","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F29" s="109" t="inlineStr">
+        <is>
+          <t>Stirrer tip speed under the conservative 1.5 m/s shear limit.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Design assumption (~70%)</t>
+          <t>Media volume fits vial?</t>
+        </is>
+      </c>
+      <c r="D30" s="113">
+        <f>Geometry!$D$54</f>
+        <v/>
+      </c>
+      <c r="E30" s="112">
+        <f>HYPERLINK("#Geometry!D54","→ Geometry")</f>
+        <v/>
+      </c>
+      <c r="F30" s="109" t="inlineStr">
+        <is>
+          <t>Media volume not exceeding the max working volume.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Weak / coarse estimate (~50%)</t>
+          <t>Liquid level OK?</t>
+        </is>
+      </c>
+      <c r="D31" s="113">
+        <f>Geometry!$D$55</f>
+        <v/>
+      </c>
+      <c r="E31" s="112">
+        <f>HYPERLINK("#Geometry!D55","→ Geometry")</f>
+        <v/>
+      </c>
+      <c r="F31" s="109" t="inlineStr">
+        <is>
+          <t>Liquid not above the usable vial depth.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Guess - replace when known</t>
+          <t>LED current-law in range?</t>
+        </is>
+      </c>
+      <c r="D32" s="117">
+        <f>Electrochemistry!$D$20</f>
+        <v/>
+      </c>
+      <c r="E32" s="112">
+        <f>HYPERLINK("#Electrochemistry!D20","→ Electrochemistry")</f>
+        <v/>
+      </c>
+      <c r="F32" s="109" t="inlineStr">
+        <is>
+          <t>LED intensity within Gerrit's-Law validated band 3-25% (gerrit-current.md).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>DATA GAP - need to measure</t>
-        </is>
-      </c>
+      <c r="A33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>variable (set/measure)</t>
+      <c r="A34" s="110" t="inlineStr">
+        <is>
+          <t>SUPPORTING FIGURES  (context, not pass/fail)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>fixed data / constant</t>
+          <t>Steady-state DO (surface)</t>
         </is>
       </c>
       <c r="B35" s="25" t="n"/>
-      <c r="C35" s="26" t="n"/>
-      <c r="D35" s="27" t="n"/>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="D35" s="118">
+        <f>'Mass Transfer'!$D$108</f>
+        <v/>
+      </c>
+      <c r="E35" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D108","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F35" s="109" t="inlineStr">
+        <is>
+          <t>Predicted dissolved O2 the surface stripping settles at; compare to the organism band.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="27" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>Sparge interval if O₂ handled</t>
         </is>
       </c>
       <c r="B36" s="25" t="n"/>
-      <c r="C36" s="26" t="n"/>
-      <c r="D36" s="27" t="n"/>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D36" s="118">
+        <f>'Mass Transfer'!$D$112</f>
+        <v/>
+      </c>
+      <c r="E36" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D112","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F36" s="109" t="inlineStr">
+        <is>
+          <t>The longer (carbon-limited) interval usable if the 'relaxed' check is green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Stir-bar tip speed</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D37" s="115">
+        <f>'Mass Transfer'!$D$68</f>
+        <v/>
+      </c>
+      <c r="E37" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D68","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F37" s="109" t="inlineStr">
+        <is>
+          <t>Checked against 1.5 m/s above.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="67" t="inlineStr">
         <is>
-          <t>EXPERIMENT SELECTORS  (dropdowns auto-extend from the lookup tables; wired to calcs next stage)</t>
-        </is>
-      </c>
+          <t>Carbon margin</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D38" s="119">
+        <f>Biology!$D$35</f>
+        <v/>
+      </c>
+      <c r="E38" s="112">
+        <f>HYPERLINK("#Biology!D35","→ Biology")</f>
+        <v/>
+      </c>
+      <c r="F38" s="109" t="inlineStr">
+        <is>
+          <t>Dissolved CO2 vs RuBisCO Km at in-sparge peak; large = ample carbon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="110" t="inlineStr">
+        <is>
+          <t>KEY  (whole workbook)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Verified / handbook / defined / standard</t>
+        </is>
+      </c>
+      <c r="D41" s="120" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Literature-supported (~90%)</t>
+        </is>
+      </c>
+      <c r="D42" s="121" t="n"/>
     </row>
     <row r="43">
-      <c r="D43" s="79" t="n"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Design assumption (~70%)</t>
+        </is>
+      </c>
+      <c r="D43" s="122" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="63" t="inlineStr">
         <is>
-          <t>DO BAND (organism)</t>
-        </is>
-      </c>
+          <t>Weak / coarse estimate (~50%)</t>
+        </is>
+      </c>
+      <c r="D44" s="123" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Steady-state DO (surface, mg/L)</t>
-        </is>
-      </c>
-      <c r="D45" s="72">
-        <f>'Mass Transfer'!$D$108</f>
-        <v/>
-      </c>
-      <c r="E45" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D108","From Mass Transfer")</f>
-        <v/>
-      </c>
+          <t>Guess - replace when known</t>
+        </is>
+      </c>
+      <c r="D45" s="124" t="n"/>
+      <c r="E45" s="78" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DO vs organism optimum</t>
-        </is>
-      </c>
-      <c r="D46" s="72">
-        <f>'Mass Transfer'!$D$109</f>
-        <v/>
-      </c>
-      <c r="E46" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D109","From Mass Transfer")</f>
-        <v/>
-      </c>
+          <t>DATA GAP - measure, do not invent</t>
+        </is>
+      </c>
+      <c r="D46" s="75" t="n"/>
+      <c r="E46" s="78" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>DO vs organism minimum</t>
-        </is>
-      </c>
-      <c r="D47" s="72">
-        <f>'Mass Transfer'!$D$110</f>
-        <v/>
-      </c>
-      <c r="E47" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D110","From Mass Transfer")</f>
-        <v/>
-      </c>
+      <c r="A47" s="125" t="inlineStr">
+        <is>
+          <t>Value font: blue = input you set/measure</t>
+        </is>
+      </c>
+      <c r="D47" s="72" t="n"/>
+      <c r="E47" s="78" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="63" t="inlineStr">
-        <is>
-          <t>Media-volume / depth / tip warnings</t>
+      <c r="A48" s="105" t="inlineStr">
+        <is>
+          <t>black = formula / derived</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Media vs max working</t>
-        </is>
-      </c>
-      <c r="D49" s="71">
-        <f>Geometry!$D$54</f>
-        <v/>
-      </c>
-      <c r="E49" s="78">
-        <f>HYPERLINK("#Geometry!D54","From Geometry")</f>
-        <v/>
-      </c>
+      <c r="A49" s="126" t="inlineStr">
+        <is>
+          <t>purple = fixed data / constant</t>
+        </is>
+      </c>
+      <c r="D49" s="71" t="n"/>
+      <c r="E49" s="78" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Liquid vs usable depth</t>
-        </is>
-      </c>
-      <c r="D50" s="71">
-        <f>Geometry!$D$55</f>
-        <v/>
-      </c>
-      <c r="E50" s="78">
-        <f>HYPERLINK("#Geometry!D55","From Geometry")</f>
-        <v/>
-      </c>
+          <t>CHECK fills: green = OK · amber = caution · red = problem</t>
+        </is>
+      </c>
+      <c r="D50" s="127" t="n"/>
+      <c r="E50" s="128" t="n"/>
+      <c r="F50" s="68" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Tip speed</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>m/s</t>
-        </is>
-      </c>
-      <c r="D51" s="72">
-        <f>'Mass Transfer'!$D$68</f>
-        <v/>
-      </c>
-      <c r="E51" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D68","From Mass Transfer")</f>
-        <v/>
-      </c>
+      <c r="D51" s="72" t="n"/>
+      <c r="E51" s="78" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Tip-speed shear</t>
-        </is>
-      </c>
-      <c r="D52" s="72">
-        <f>'Mass Transfer'!$D$111</f>
-        <v/>
-      </c>
-      <c r="E52" s="78">
-        <f>HYPERLINK("#'Mass Transfer'!D111","From Mass Transfer")</f>
-        <v/>
+      <c r="A52" s="110" t="inlineStr">
+        <is>
+          <t>RANKED IMPROVEMENTS</t>
+        </is>
+      </c>
+      <c r="D52" s="72" t="n"/>
+      <c r="E52" s="78" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="110" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B53" s="110" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C53" s="110" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="D53" s="110" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="F53" s="110" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="54" t="inlineStr">
         <is>
-          <t>RANKED IMPROVEMENTS (by impact, with effort)</t>
+          <t>Measure surface kLa (kL_surf)</t>
         </is>
       </c>
       <c r="B54" s="63" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="C54" s="63" t="inlineStr">
         <is>
-          <t>Effort</t>
-        </is>
-      </c>
-      <c r="D54" s="102">
-        <f>HYPERLINK("protocols/README.md","all protocols →")</f>
-        <v/>
-      </c>
-      <c r="E54" s="63" t="inlineStr">
-        <is>
-          <t>Why it matters</t>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="D54" s="112">
+        <f>HYPERLINK("protocols/surface-kla.md","surface-kla.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="E54" s="63" t="n"/>
+      <c r="F54" s="109" t="inlineStr">
+        <is>
+          <t>375% sensitivity; decides the safe sparge interval</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1 Measure surface kLa (kL_surf)</t>
+          <t>Measure cathodic Faradaic efficiency</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2029,46 +2335,46 @@
           <t>med</t>
         </is>
       </c>
-      <c r="D55" s="102">
-        <f>HYPERLINK("protocols/surface-kla.md","protocol →")</f>
-        <v/>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>375% sensitivity; decides whether DO stays in the organism band</t>
+      <c r="D55" s="112">
+        <f>HYPERLINK("protocols/faradaic-efficiency.md","faradaic-efficiency.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="F55" s="109" t="inlineStr">
+        <is>
+          <t>sets the H2/O2 split; O2 figures are an upper bound at etaF=1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2 Measure cathodic Faradaic efficiency (etaF)</t>
+          <t>Determine organism minimum DO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="D56" s="102">
-        <f>HYPERLINK("protocols/faradaic-efficiency.md","protocol →")</f>
-        <v/>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>sets the H2/O2 split and net O2; currently assumed 1.0</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D56" s="112">
+        <f>HYPERLINK("protocols/dissolved-oxygen.md","dissolved-oxygen.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="F56" s="109" t="inlineStr">
+        <is>
+          <t>lower DO guardrail; a gap for every organism</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3 Determine organism minimum DO</t>
+          <t>Calibrate flow for each reactor</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2081,20 +2387,20 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D57" s="102">
-        <f>HYPERLINK("protocols/dissolved-oxygen.md","protocol →")</f>
-        <v/>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>lower DO guardrail; currently a gap for every organism</t>
+      <c r="D57" s="112">
+        <f>HYPERLINK("protocols/flow-calibration.md","flow-calibration.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="F57" s="109" t="inlineStr">
+        <is>
+          <t>each experiment; only ed04 done</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4 Calibrate flow for each reactor used</t>
+          <t>Confirm knallgas uptake ratio (H2:O2:CO2)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2104,49 +2410,49 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D58" s="102">
-        <f>HYPERLINK("protocols/flow-calibration.md","protocol →")</f>
-        <v/>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>each experiment; only ed04 calibrated so far</t>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D58" s="112">
+        <f>HYPERLINK("protocols/knallgas-stoichiometry.md","knallgas-stoichiometry.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="F58" s="109" t="inlineStr">
+        <is>
+          <t>sets O2 surplus + carbon demand; needs a growing culture</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5 Confirm knallgas uptake ratio (H2:O2:CO2)</t>
+          <t>Measure / confirm sinter porosity</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D59" s="102">
-        <f>HYPERLINK("protocols/knallgas-stoichiometry.md","protocol →")</f>
-        <v/>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>carbon/O2 balance; needs a growing culture</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D59" s="112">
+        <f>HYPERLINK("protocols/sinter-porosity.md","sinter-porosity.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="F59" s="109" t="inlineStr">
+        <is>
+          <t>bubble size; currently grade 0 from Gerrit's disc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6 Measure sinter porosity grade</t>
+          <t>Record lab ambient pressure</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2159,132 +2465,73 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D60" s="102">
-        <f>HYPERLINK("protocols/sinter-porosity.md","protocol →")</f>
-        <v/>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>bubble size when sparger = sintered</t>
+      <c r="D60" s="112">
+        <f>HYPERLINK("protocols/README.md","README.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="F60" s="109" t="inlineStr">
+        <is>
+          <t>Henry solubilities + gas volumes</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>7 Record lab ambient pressure</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D61" s="102">
-        <f>HYPERLINK("protocols/README.md","protocol →")</f>
-        <v/>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Henry solubilities + gas volumes</t>
-        </is>
-      </c>
-    </row>
+      <c r="D61" s="102" t="n"/>
+    </row>
+    <row r="62"/>
     <row r="63">
-      <c r="A63" s="63" t="inlineStr">
-        <is>
-          <t>SCHEDULE REGIME</t>
-        </is>
-      </c>
+      <c r="A63" s="63" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Interval - O2-limited (conservative, model optimum, min)</t>
-        </is>
-      </c>
-      <c r="D64" s="72">
-        <f>IFERROR('Mass Transfer'!$D$91,"calibrate this reactor first (see CO2 flows)")</f>
-        <v/>
-      </c>
+      <c r="D64" s="72" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Interval - carbon-limited if O2 handled by surface</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D65" s="72">
-        <f>IFERROR('Mass Transfer'!$D$112,"calibrate this reactor first (see CO2 flows)")</f>
-        <v/>
-      </c>
+      <c r="D65" s="72" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Which regime</t>
-        </is>
-      </c>
-      <c r="D66" s="72">
-        <f>'Mass Transfer'!$D$113</f>
-        <v/>
-      </c>
-      <c r="E66">
-        <f>'Mass Transfer'!$E$113</f>
-        <v/>
-      </c>
-    </row>
+      <c r="D66" s="72" t="n"/>
+    </row>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
   </sheetData>
-  <conditionalFormatting sqref="D13:D26">
-    <cfRule type="expression" priority="11" dxfId="1">
-      <formula>OR(ISNUMBER(SEARCH("RISK",D13)),ISNUMBER(SEARCH("OVER",D13)),ISNUMBER(SEARCH("BELOW",D13)),ISNUMBER(SEARCH("EXCEED",D13)),ISNUMBER(SEARCH("NO CALIB",D13)),ISNUMBER(SEARCH("NEAREST",D13)),ISNUMBER(SEARCH("EXPLOSIVE",D13)),ISNUMBER(SEARCH("TIGHT",D13)),ISNUMBER(SEARCH("insufficient",D13)),ISNUMBER(SEARCH("OOR",D13)),ISNUMBER(SEARCH("calibrate",D13)),ISNUMBER(SEARCH("INCONSISTENT",D13)),EXACT(D13,"OUT"),EXACT(D13,"LOW"))</formula>
+  <conditionalFormatting sqref="D18:D32">
+    <cfRule type="expression" priority="11" dxfId="1" stopIfTrue="1">
+      <formula>OR(ISNUMBER(SEARCH("INCONSISTENT",D18)),ISNUMBER(SEARCH("OVER",D18)),ISNUMBER(SEARCH("BELOW",D18)),ISNUMBER(SEARCH("EXCEED",D18)),ISNUMBER(SEARCH("NO CALIB",D18)),ISNUMBER(SEARCH("calibrate",D18)),ISNUMBER(SEARCH("RISK",D18)),ISNUMBER(SEARCH("EXPLOSIVE",D18)),ISNUMBER(SEARCH("OOR",D18)),ISNUMBER(SEARCH("insufficient",D18)),EXACT(D18,"OUT"),EXACT(D18,"LOW"))</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" dxfId="0">
-      <formula>OR(EXACT(D13,"OK"),ISNUMBER(SEARCH("calibrated:",D13)),ISNUMBER(SEARCH("under optimum",D13)),ISNUMBER(SEARCH("above min",D13)),ISNUMBER(SEARCH("exact",D13)),ISNUMBER(SEARCH("CARBON-limited",D13)))</formula>
+    <cfRule type="expression" priority="12" dxfId="19" stopIfTrue="1">
+      <formula>OR(ISNUMBER(SEARCH("above optimum",D18)),ISNUMBER(SEARCH("watch",D18)),ISNUMBER(SEARCH("NEAREST",D18)),ISNUMBER(SEARCH("unknown",D18)),ISNUMBER(SEARCH("TIGHT",D18)))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" dxfId="0" stopIfTrue="1">
+      <formula>OR(EXACT(D18,"OK"),ISNUMBER(SEARCH("calibrated:",D18)),ISNUMBER(SEARCH("under optimum",D18)),ISNUMBER(SEARCH("above min",D18)),ISNUMBER(SEARCH("CARBON-limited",D18)),ISNUMBER(SEARCH("Static",D18)),ISNUMBER(SEARCH("Dynamic",D18)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18">
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="19">
-      <formula>2</formula>
+  <conditionalFormatting sqref="D14:D15">
+    <cfRule type="expression" priority="14" dxfId="1" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("calibrate",D14))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D19">
-    <cfRule type="cellIs" priority="17" operator="lessThan" dxfId="1">
-      <formula>1</formula>
+  <conditionalFormatting sqref="B54:B60">
+    <cfRule type="expression" priority="15" dxfId="0" stopIfTrue="1">
+      <formula>EXACT(B54,"HIGH")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="19" stopIfTrue="1">
+      <formula>EXACT(B54,"MED")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="17" dxfId="1" stopIfTrue="1">
+      <formula>EXACT(B54,"LOW")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D27">
-    <cfRule type="expression" priority="19" dxfId="1">
-      <formula>ISNUMBER(SEARCH("INCONSISTENT",D27))</formula>
+  <conditionalFormatting sqref="C54:C60">
+    <cfRule type="expression" priority="18" dxfId="0" stopIfTrue="1">
+      <formula>EXACT(C54,"low")</formula>
     </cfRule>
-    <cfRule type="expression" priority="20" dxfId="0">
-      <formula>EXACT(D27,"OK")</formula>
+    <cfRule type="expression" priority="19" dxfId="19" stopIfTrue="1">
+      <formula>EXACT(C54,"med")</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D45:D52">
-    <cfRule type="expression" priority="13" dxfId="1">
-      <formula>OR(ISNUMBER(SEARCH("RISK",D45)),ISNUMBER(SEARCH("OVER",D45)),ISNUMBER(SEARCH("BELOW",D45)),ISNUMBER(SEARCH("EXCEED",D45)),ISNUMBER(SEARCH("NO CALIB",D45)),ISNUMBER(SEARCH("NEAREST",D45)),ISNUMBER(SEARCH("EXPLOSIVE",D45)),ISNUMBER(SEARCH("TIGHT",D45)),ISNUMBER(SEARCH("insufficient",D45)),ISNUMBER(SEARCH("OOR",D45)),ISNUMBER(SEARCH("calibrate",D45)),ISNUMBER(SEARCH("INCONSISTENT",D45)),EXACT(D45,"OUT"),EXACT(D45,"LOW"))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="14" dxfId="0">
-      <formula>OR(EXACT(D45,"OK"),ISNUMBER(SEARCH("calibrated:",D45)),ISNUMBER(SEARCH("under optimum",D45)),ISNUMBER(SEARCH("above min",D45)),ISNUMBER(SEARCH("exact",D45)),ISNUMBER(SEARCH("CARBON-limited",D45)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D64:D66">
-    <cfRule type="expression" priority="15" dxfId="1">
-      <formula>OR(ISNUMBER(SEARCH("RISK",D64)),ISNUMBER(SEARCH("OVER",D64)),ISNUMBER(SEARCH("BELOW",D64)),ISNUMBER(SEARCH("EXCEED",D64)),ISNUMBER(SEARCH("NO CALIB",D64)),ISNUMBER(SEARCH("NEAREST",D64)),ISNUMBER(SEARCH("EXPLOSIVE",D64)),ISNUMBER(SEARCH("TIGHT",D64)),ISNUMBER(SEARCH("insufficient",D64)),ISNUMBER(SEARCH("OOR",D64)),ISNUMBER(SEARCH("calibrate",D64)),ISNUMBER(SEARCH("INCONSISTENT",D64)),EXACT(D64,"OUT"),EXACT(D64,"LOW"))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="16" dxfId="0">
-      <formula>OR(EXACT(D64,"OK"),ISNUMBER(SEARCH("calibrated:",D64)),ISNUMBER(SEARCH("under optimum",D64)),ISNUMBER(SEARCH("above min",D64)),ISNUMBER(SEARCH("exact",D64)),ISNUMBER(SEARCH("CARBON-limited",D64)))</formula>
+    <cfRule type="expression" priority="20" dxfId="1" stopIfTrue="1">
+      <formula>EXACT(C54,"high")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -4100,7 +4347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4998,9 +5245,6 @@
     <row r="39">
       <c r="D39" s="72" t="n"/>
     </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <conditionalFormatting sqref="D13">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -581,7 +581,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -831,11 +831,25 @@
         <color theme="8"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1013,6 +1027,31 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1436,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1557,7 +1596,16 @@
           <t>Cupriavidus necator</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n"/>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Input (you set it)</t>
+        </is>
+      </c>
+      <c r="F5" s="109" t="inlineStr">
+        <is>
+          <t>The HOB strain; sets the DO band the schedule targets.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1575,6 +1623,16 @@
           <t>Sydow 2017 minimal</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Input (you set it)</t>
+        </is>
+      </c>
+      <c r="F6" s="109" t="inlineStr">
+        <is>
+          <t>Growth medium.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1595,6 +1653,16 @@
       <c r="D7" s="79" t="n">
         <v>3</v>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Input - Pioreactor LED channel</t>
+        </is>
+      </c>
+      <c r="F7" s="109" t="inlineStr">
+        <is>
+          <t>% driving electrolysis current (Gerrit's Law, valid 3-25%).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1615,11 +1683,21 @@
       <c r="D8" s="79" t="n">
         <v>500</v>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Input - Pioreactor</t>
+        </is>
+      </c>
+      <c r="F8" s="109" t="inlineStr">
+        <is>
+          <t>Stir rate; sets tip speed and surface O2 transfer.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Media volume - blank = recommended max</t>
+          <t>Media volume</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1633,6 +1711,16 @@
         </is>
       </c>
       <c r="D9" s="80" t="n"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Input (you set it)</t>
+        </is>
+      </c>
+      <c r="F9" s="109" t="inlineStr">
+        <is>
+          <t>Liquid charged; leave blank to use the reactor's recommended max working volume.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1653,6 +1741,16 @@
       <c r="D10" s="80" t="n">
         <v>30</v>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Input - Pioreactor</t>
+        </is>
+      </c>
+      <c r="F10" s="109" t="inlineStr">
+        <is>
+          <t>Temperature setpoint; sets Henry solubilities and rates.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1" thickBot="1">
       <c r="A11" t="inlineStr">
@@ -1672,6 +1770,16 @@
       </c>
       <c r="D11" s="80" t="n">
         <v>101325</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Input (record on the day)</t>
+        </is>
+      </c>
+      <c r="F11" s="109" t="inlineStr">
+        <is>
+          <t>Lab pressure; default 101325 Pa is fine for design (low sensitivity).</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2159,7 +2267,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="110" t="inlineStr">
         <is>
@@ -2478,7 +2585,6 @@
     <row r="61">
       <c r="D61" s="102" t="n"/>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="63" t="n"/>
     </row>
@@ -2491,10 +2597,6 @@
     <row r="66">
       <c r="D66" s="72" t="n"/>
     </row>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
   </sheetData>
   <conditionalFormatting sqref="D18:D32">
     <cfRule type="expression" priority="11" dxfId="1" stopIfTrue="1">
@@ -2636,14 +2738,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D5" s="71">
+      <c r="D5" s="129">
         <f>Summary!$D$3</f>
         <v/>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>From Summary.</t>
-        </is>
+      <c r="E5" s="112">
+        <f>HYPERLINK("#Summary!D3","→ Summary")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -2657,8 +2758,17 @@
           <t>media_volume</t>
         </is>
       </c>
-      <c r="D6" s="71">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D6" s="129">
         <f>Summary!$D$9</f>
+        <v/>
+      </c>
+      <c r="E6" s="112">
+        <f>HYPERLINK("#Summary!D9","→ Summary")</f>
         <v/>
       </c>
     </row>
@@ -2690,9 +2800,9 @@
           <t>AEP0.1.1</t>
         </is>
       </c>
-      <c r="E8" s="93" t="inlineStr">
-        <is>
-          <t>Per-version inputs SUPERSEDED by the reactor-type lookup (below) - retained for reference only, not read by formulas</t>
+      <c r="E8" s="130" t="inlineStr">
+        <is>
+          <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
       </c>
     </row>
@@ -2717,9 +2827,9 @@
           <t>AEP0.2</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Planned build (40 mL Pioreactor vial).</t>
+      <c r="E9" s="130" t="inlineStr">
+        <is>
+          <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
       </c>
     </row>
@@ -2742,9 +2852,9 @@
       <c r="D10" s="22" t="n">
         <v>27.48</v>
       </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Pioreactor 20 mL vial, measured OD.</t>
+      <c r="E10" s="131" t="inlineStr">
+        <is>
+          <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
       </c>
     </row>
@@ -2767,9 +2877,9 @@
       <c r="D11" s="22" t="n">
         <v>27.48</v>
       </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>40 mL vial — same diameter as 20 mL (Pioreactor source). Using 27.48 mm until measured.</t>
+      <c r="E11" s="132" t="inlineStr">
+        <is>
+          <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
       </c>
     </row>
@@ -2792,9 +2902,9 @@
       <c r="D12" s="29" t="n">
         <v>55</v>
       </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>20 mL vial total height 57.4 mm; usable depth est. Measure.</t>
+      <c r="E12" s="133" t="inlineStr">
+        <is>
+          <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
       </c>
     </row>
@@ -2817,9 +2927,9 @@
       <c r="D13" s="29" t="n">
         <v>95</v>
       </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>40 mL internal depth — measure. ~double the 20 mL (same diameter, double volume).</t>
+      <c r="E13" s="133" t="inlineStr">
+        <is>
+          <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
       </c>
     </row>
@@ -2842,9 +2952,9 @@
       <c r="D14" s="29" t="n">
         <v>16</v>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Pioreactor docs: 8-16 mL for 20 mL vial; using max as level datum.</t>
+      <c r="E14" s="131" t="inlineStr">
+        <is>
+          <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
       </c>
     </row>
@@ -2867,9 +2977,9 @@
       <c r="D15" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Pioreactor docs recommend 10–30 mL working volume for the 40 mL vial; using the top of that range as level datum.</t>
+      <c r="E15" s="131" t="inlineStr">
+        <is>
+          <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
       </c>
     </row>
@@ -2892,9 +3002,9 @@
       <c r="D16" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>To cap underside (&gt; nominal). Placeholder - measure (water to fill).</t>
+      <c r="E16" s="134" t="inlineStr">
+        <is>
+          <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
       </c>
     </row>
@@ -2915,11 +3025,11 @@
         </is>
       </c>
       <c r="D17" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder - measure.</t>
+        <v>42</v>
+      </c>
+      <c r="E17" s="134" t="inlineStr">
+        <is>
+          <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
       </c>
     </row>
@@ -3842,6 +3952,7 @@
         <v/>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="67" t="inlineStr">
         <is>
@@ -4125,6 +4236,7 @@
         </is>
       </c>
     </row>
+    <row r="81"/>
     <row r="82">
       <c r="A82" s="67" t="inlineStr">
         <is>
@@ -4311,6 +4423,14 @@
         <v>6</v>
       </c>
     </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="110" t="inlineStr">
+        <is>
+          <t>VIAL GEOMETRY CONSISTENCY CHECK</t>
+        </is>
+      </c>
+    </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -4325,6 +4445,11 @@
       <c r="D90">
         <f>IF(ABS(A_x*D_int/1000-V_vial_total)&gt;3,"VIAL GEOMETRY INCONSISTENT - measure true fill volume &amp; bore depth","OK")</f>
         <v/>
+      </c>
+      <c r="F90" s="109" t="inlineStr">
+        <is>
+          <t>Fires INCONSISTENT for the 20 mL vial because the bare cylinder (A_x x usable depth ~28 mL) overestimates the true 20 mL vial (it tapers/necks, not a full cylinder to 55 mm). Expected tolerance artifact, not a data error - resolved by measuring true bore depth (protocols/vial-geometry.md).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4423,14 +4548,13 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D5" s="56">
+      <c r="D5" s="119">
         <f>Biology!$D$18</f>
         <v/>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
+      <c r="E5" s="112">
+        <f>HYPERLINK("#Biology!D18","→ Biology")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -4449,14 +4573,13 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D6" s="56">
+      <c r="D6" s="119">
         <f>Biology!$D$19</f>
         <v/>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
+      <c r="E6" s="112">
+        <f>HYPERLINK("#Biology!D19","→ Biology")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -4475,14 +4598,13 @@
           <t>J/mol/K</t>
         </is>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="115">
         <f>'Mass Transfer'!$D$101</f>
         <v/>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>From Dosing.</t>
-        </is>
+      <c r="E7" s="112">
+        <f>HYPERLINK("#'Mass Transfer'!D101","→ Mass Transfer")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -4496,8 +4618,12 @@
           <t>electrode_sel</t>
         </is>
       </c>
-      <c r="D8" s="71">
+      <c r="D8" s="129">
         <f>Summary!$D$4</f>
+        <v/>
+      </c>
+      <c r="E8" s="112">
+        <f>HYPERLINK("#Summary!D4","→ Summary")</f>
         <v/>
       </c>
     </row>
@@ -4961,9 +5087,9 @@
         <f>VLOOKUP(electrode_sel,$A$35:$I$37,9,FALSE)</f>
         <v/>
       </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>Electrons per cathodic O₂. 4 = to water; 2 = peroxide (favoured on non-Pt, neutral pH) — consumes 2× the O₂/amp, and H₂O₂ is biocidal. Inert while etaF=1.</t>
+      <c r="E27" s="135" t="inlineStr">
+        <is>
+          <t>Electrode lookup fixes ORR at 2 e- (peroxide pathway, SS cathode, neutral pH) for every current electrode; a 4 e- (to-water) electrode would need its own table row.</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5278,7 @@
       </c>
       <c r="H35" s="68" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>?</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -5193,7 +5319,7 @@
       </c>
       <c r="H36" s="68" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>?</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -5232,7 +5358,7 @@
       </c>
       <c r="H37" s="68" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>?</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -5341,14 +5467,13 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D5" s="58">
+      <c r="D5" s="117">
         <f>Electrochemistry!$D$21</f>
         <v/>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>From Electrochemistry.</t>
-        </is>
+      <c r="E5" s="112">
+        <f>HYPERLINK("#Electrochemistry!D21","→ Electrochemistry")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -5367,14 +5492,13 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D6" s="58">
+      <c r="D6" s="117">
         <f>Electrochemistry!$D$29</f>
         <v/>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>From Electrochemistry.</t>
-        </is>
+      <c r="E6" s="112">
+        <f>HYPERLINK("#Electrochemistry!D29","→ Electrochemistry")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -5393,14 +5517,13 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="113">
         <f>Geometry!$D$41</f>
         <v/>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>From Geometry.</t>
-        </is>
+      <c r="E7" s="112">
+        <f>HYPERLINK("#Geometry!D41","→ Geometry")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -5414,8 +5537,12 @@
           <t>organism_sel</t>
         </is>
       </c>
-      <c r="D8" s="71">
+      <c r="D8" s="129">
         <f>Summary!$D$5</f>
+        <v/>
+      </c>
+      <c r="E8" s="112">
+        <f>HYPERLINK("#Summary!D5","→ Summary")</f>
         <v/>
       </c>
     </row>
@@ -6321,6 +6448,11 @@
           <t>On when H₂ escapes faster than it dissolves (H2_turnover&gt;1) → explosive H₂+O₂ headspace (4–94% in O₂). On at any useful current — headspace venting is mandatory.</t>
         </is>
       </c>
+      <c r="F44" s="109" t="inlineStr">
+        <is>
+          <t>Pink no longer used here - red fill = hazard (H2 evolving faster than it dissolves), not a data gap.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6333,6 +6465,11 @@
           <t>DO_min</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
       <c r="D45" s="75">
         <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,2,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,2,FALSE),NA())</f>
         <v/>
@@ -6349,6 +6486,11 @@
           <t>DO_opt</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
       <c r="D46" s="72">
         <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE),NA())</f>
         <v/>
@@ -6365,6 +6507,11 @@
           <t>DO_impair</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
       <c r="D47" s="72">
         <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE),NA())</f>
         <v/>
@@ -6379,6 +6526,11 @@
       <c r="B48" t="inlineStr">
         <is>
           <t>DO_toxic</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="D48" s="72">
@@ -6697,6 +6849,11 @@
       <formula>"EXPLOSIVE"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D44">
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("EXPLOSIVE",D44))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6708,7 +6865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6785,11 +6942,15 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D5" s="73">
+      <c r="D5" s="136">
         <f>Geometry!$D$52</f>
         <v/>
       </c>
-      <c r="E5" s="48" t="inlineStr">
+      <c r="E5" s="137">
+        <f>HYPERLINK("#Geometry!D52","→ Geometry")</f>
+        <v/>
+      </c>
+      <c r="F5" s="109" t="inlineStr">
         <is>
           <t>Magnetic stir bar. Pioreactor max 20 mm; confirm the supplied bar's length. Input.</t>
         </is>
@@ -6811,14 +6972,13 @@
           <t>mol/m³</t>
         </is>
       </c>
-      <c r="D6" s="56">
+      <c r="D6" s="119">
         <f>Biology!$D$27</f>
         <v/>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
+      <c r="E6" s="112">
+        <f>HYPERLINK("#Biology!D27","→ Biology")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -6837,14 +6997,13 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D7" s="56">
+      <c r="D7" s="119">
         <f>Biology!$D$26</f>
         <v/>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
+      <c r="E7" s="112">
+        <f>HYPERLINK("#Biology!D26","→ Biology")</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
@@ -6863,14 +7022,13 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D8" s="56">
+      <c r="D8" s="119">
         <f>Biology!$D$18</f>
         <v/>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
+      <c r="E8" s="112">
+        <f>HYPERLINK("#Biology!D18","→ Biology")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -6889,14 +7047,13 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D9" s="56">
+      <c r="D9" s="119">
         <f>Biology!$D$19</f>
         <v/>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
+      <c r="E9" s="112">
+        <f>HYPERLINK("#Biology!D19","→ Biology")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -6915,14 +7072,13 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="119">
         <f>Biology!$D$15</f>
         <v/>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
+      <c r="E10" s="112">
+        <f>HYPERLINK("#Biology!D15","→ Biology")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -6941,14 +7097,13 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D11" s="56">
+      <c r="D11" s="119">
         <f>Biology!$D$16</f>
         <v/>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
+      <c r="E11" s="112">
+        <f>HYPERLINK("#Biology!D16","→ Biology")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -6967,14 +7122,13 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D12" s="56">
+      <c r="D12" s="119">
         <f>Biology!$D$24</f>
         <v/>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>From Biology.</t>
-        </is>
+      <c r="E12" s="112">
+        <f>HYPERLINK("#Biology!D24","→ Biology")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -6993,14 +7147,13 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D13" s="58">
+      <c r="D13" s="117">
         <f>Electrochemistry!$D$29</f>
         <v/>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>From Electrochemistry.</t>
-        </is>
+      <c r="E13" s="112">
+        <f>HYPERLINK("#Electrochemistry!D29","→ Electrochemistry")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -7019,14 +7172,13 @@
           <t>mm²</t>
         </is>
       </c>
-      <c r="D14" s="59">
+      <c r="D14" s="113">
         <f>Geometry!$D$44</f>
         <v/>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>From Geometry.</t>
-        </is>
+      <c r="E14" s="112">
+        <f>HYPERLINK("#Geometry!D44","→ Geometry")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -7045,14 +7197,13 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="113">
         <f>Geometry!$D$20</f>
         <v/>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>From Geometry.</t>
-        </is>
+      <c r="E15" s="112">
+        <f>HYPERLINK("#Geometry!D20","→ Geometry")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -7071,14 +7222,13 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D16" s="59">
+      <c r="D16" s="113">
         <f>Geometry!$D$41</f>
         <v/>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>From Geometry.</t>
-        </is>
+      <c r="E16" s="112">
+        <f>HYPERLINK("#Geometry!D41","→ Geometry")</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -7097,14 +7247,13 @@
           <t>mm²</t>
         </is>
       </c>
-      <c r="D17" s="59">
+      <c r="D17" s="113">
         <f>Geometry!$D$21</f>
         <v/>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>From Geometry.</t>
-        </is>
+      <c r="E17" s="112">
+        <f>HYPERLINK("#Geometry!D21","→ Geometry")</f>
+        <v/>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
@@ -7123,14 +7272,13 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D18" s="59">
+      <c r="D18" s="113">
         <f>Geometry!$D$31</f>
         <v/>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>From Geometry.</t>
-        </is>
+      <c r="E18" s="112">
+        <f>HYPERLINK("#Geometry!D31","→ Geometry")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -7149,14 +7297,13 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D19" s="59">
+      <c r="D19" s="113">
         <f>Geometry!$D$49</f>
         <v/>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>From Geometry.</t>
-        </is>
+      <c r="E19" s="112">
+        <f>HYPERLINK("#Geometry!D49","→ Geometry")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -7175,14 +7322,13 @@
           <t>0-5</t>
         </is>
       </c>
-      <c r="D20" s="106">
+      <c r="D20" s="138">
         <f>Electrochemistry!$D$32</f>
         <v/>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>From Summary.</t>
-        </is>
+      <c r="E20" s="112">
+        <f>HYPERLINK("#Electrochemistry!D32","→ Electrochemistry")</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -7201,14 +7347,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D21" s="74">
+      <c r="D21" s="139">
         <f>Electrochemistry!$D$31</f>
         <v/>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>From Summary.</t>
-        </is>
+      <c r="E21" s="112">
+        <f>HYPERLINK("#Electrochemistry!D31","→ Electrochemistry")</f>
+        <v/>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
@@ -7222,8 +7367,12 @@
           <t>DO_opt</t>
         </is>
       </c>
-      <c r="D22" s="77">
+      <c r="D22" s="116">
         <f>Biology!$D$46</f>
+        <v/>
+      </c>
+      <c r="E22" s="112">
+        <f>HYPERLINK("#Biology!D46","→ Biology")</f>
         <v/>
       </c>
     </row>
@@ -7238,8 +7387,12 @@
           <t>DO_impair</t>
         </is>
       </c>
-      <c r="D23" s="77">
+      <c r="D23" s="116">
         <f>Biology!$D$47</f>
+        <v/>
+      </c>
+      <c r="E23" s="112">
+        <f>HYPERLINK("#Biology!D47","→ Biology")</f>
         <v/>
       </c>
     </row>
@@ -7254,8 +7407,12 @@
           <t>DO_toxic</t>
         </is>
       </c>
-      <c r="D24" s="77">
+      <c r="D24" s="116">
         <f>Biology!$D$48</f>
+        <v/>
+      </c>
+      <c r="E24" s="112">
+        <f>HYPERLINK("#Biology!D48","→ Biology")</f>
         <v/>
       </c>
     </row>
@@ -7270,8 +7427,12 @@
           <t>DO_min</t>
         </is>
       </c>
-      <c r="D25" s="77">
+      <c r="D25" s="116">
         <f>Biology!$D$45</f>
+        <v/>
+      </c>
+      <c r="E25" s="112">
+        <f>HYPERLINK("#Biology!D45","→ Biology")</f>
         <v/>
       </c>
     </row>
@@ -9699,7 +9860,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>×</t>
         </is>
       </c>
       <c r="D126" s="72">
@@ -9762,7 +9923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>×</t>
         </is>
       </c>
       <c r="D129" s="72">
@@ -9966,7 +10127,7 @@
       </c>
       <c r="E2" s="53" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>volume (Δ)</t>
         </is>
       </c>
       <c r="F2" s="53" t="inlineStr">
@@ -9986,7 +10147,7 @@
       </c>
       <c r="I2" s="53" t="inlineStr">
         <is>
-          <t>minimum sparge</t>
+          <t>minimum sparge time</t>
         </is>
       </c>
       <c r="J2" s="53" t="inlineStr">
@@ -10110,7 +10271,7 @@
         <v/>
       </c>
       <c r="H5">
-        <f>AVERAGE(G5)</f>
+        <f>G5</f>
         <v/>
       </c>
       <c r="N5" s="66" t="n"/>
@@ -10313,7 +10474,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CO2 collected in measuring cyclinder over CO2-saturated water</t>
+          <t>CO2 collected in measuring cylinder over CO2-saturated water</t>
         </is>
       </c>
       <c r="N13" s="63" t="n"/>
@@ -10384,7 +10545,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Collected over saturated NaHCO3 soln, as Martin  innovated without thinking</t>
+          <t>Collected over saturated NaHCO3 soln, as Martin innovated without thinking</t>
         </is>
       </c>
     </row>
@@ -10433,6 +10594,12 @@
       <c r="H17">
         <f>AVERAGE(G17:G22)</f>
         <v/>
+      </c>
+      <c r="K17" s="121" t="n"/>
+      <c r="L17" s="109" t="inlineStr">
+        <is>
+          <t>Light blue = calibration input the model reads (latest date per reactor)</t>
+        </is>
       </c>
     </row>
     <row r="18">

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="580" windowWidth="18400" windowHeight="18060" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="580" windowWidth="18400" windowHeight="18060" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,15 +14,15 @@
     <sheet name="CO2 flows" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="electrode_sel" localSheetId="0">Summary!$D$4</definedName>
-    <definedName name="led_intensity" localSheetId="0">Summary!$D$7</definedName>
-    <definedName name="media_sel" localSheetId="0">Summary!$D$6</definedName>
-    <definedName name="media_volume" localSheetId="0">Summary!$D$9</definedName>
-    <definedName name="organism_sel" localSheetId="0">Summary!$D$5</definedName>
-    <definedName name="P_atm_set" localSheetId="0">Summary!$D$11</definedName>
-    <definedName name="Reactor_sel" localSheetId="0">Summary!$D$3</definedName>
-    <definedName name="stir_rpm_set" localSheetId="0">Summary!$D$8</definedName>
-    <definedName name="temp_C" localSheetId="0">Summary!$D$10</definedName>
+    <definedName name="electrode_sel" localSheetId="0">Summary!$D$3</definedName>
+    <definedName name="led_intensity" localSheetId="0">Summary!$D$6</definedName>
+    <definedName name="media_sel" localSheetId="0">Summary!$D$5</definedName>
+    <definedName name="media_volume" localSheetId="0">Summary!$D$8</definedName>
+    <definedName name="organism_sel" localSheetId="0">Summary!$D$4</definedName>
+    <definedName name="P_atm_set" localSheetId="0">Summary!$D$10</definedName>
+    <definedName name="Reactor_sel" localSheetId="0">Summary!$D$2</definedName>
+    <definedName name="stir_rpm_set" localSheetId="0">Summary!$D$7</definedName>
+    <definedName name="temp_C" localSheetId="0">Summary!$D$9</definedName>
     <definedName name="A_x" localSheetId="1">Geometry!$D$21</definedName>
     <definedName name="D_int" localSheetId="1">Geometry!$D$22</definedName>
     <definedName name="D_int_1" localSheetId="1">Geometry!$D$12</definedName>
@@ -87,6 +87,7 @@
     <definedName name="O2_cathode_ORR" localSheetId="2">Electrochemistry!$D$28</definedName>
     <definedName name="O2_net_gen" localSheetId="2">Electrochemistry!$D$29</definedName>
     <definedName name="P_atm" localSheetId="2">Electrochemistry!$D$6</definedName>
+    <definedName name="por_grade_e" localSheetId="2">Electrochemistry!$D$32</definedName>
     <definedName name="R_gas" localSheetId="2">Electrochemistry!$D$7</definedName>
     <definedName name="rH2_gen" localSheetId="2">Electrochemistry!$D$21</definedName>
     <definedName name="rO2_gen" localSheetId="2">Electrochemistry!$D$22</definedName>
@@ -98,7 +99,6 @@
     <definedName name="z_e_H2" localSheetId="2">Electrochemistry!$D$16</definedName>
     <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$17</definedName>
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$27</definedName>
-    <definedName name="por_grade_e" localSheetId="2">Electrochemistry!$D$32</definedName>
     <definedName name="bio_CO2" localSheetId="3">Biology!$D$12</definedName>
     <definedName name="bio_H2" localSheetId="3">Biology!$D$10</definedName>
     <definedName name="bio_O2" localSheetId="3">Biology!$D$11</definedName>
@@ -273,7 +273,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
@@ -282,8 +282,9 @@
     <numFmt numFmtId="169" formatCode="0.00000000"/>
     <numFmt numFmtId="170" formatCode="0.0000000"/>
     <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="46">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -450,11 +451,74 @@
       <u val="single"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0000FF"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF7030A0"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="3"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="FF0000FF"/>
     </font>
     <font>
       <i val="1"/>
@@ -462,6 +526,10 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <color rgb="FF0000FF"/>
@@ -469,10 +537,21 @@
       <u val="single"/>
     </font>
     <font>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
-      <color rgb="FF7030A0"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0000FF"/>
     </font>
   </fonts>
   <fills count="20">
@@ -577,11 +656,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -606,31 +686,16 @@
     </border>
     <border>
       <left style="medium">
-        <color theme="5"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color theme="5"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color theme="5"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color theme="5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="9"/>
-      </left>
-      <right style="medium">
-        <color theme="9"/>
-      </right>
-      <top style="medium">
-        <color theme="9"/>
-      </top>
-      <bottom style="medium">
-        <color theme="9"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -646,96 +711,6 @@
       </top>
       <bottom style="medium">
         <color theme="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="7"/>
-      </left>
-      <right style="medium">
-        <color theme="7"/>
-      </right>
-      <top style="medium">
-        <color theme="7"/>
-      </top>
-      <bottom style="medium">
-        <color theme="7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="6"/>
-      </left>
-      <right style="medium">
-        <color theme="6"/>
-      </right>
-      <top style="medium">
-        <color theme="6"/>
-      </top>
-      <bottom style="medium">
-        <color theme="6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="7"/>
-      </left>
-      <right style="medium">
-        <color theme="7"/>
-      </right>
-      <top style="medium">
-        <color theme="7"/>
-      </top>
-      <bottom style="medium">
-        <color theme="7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="8"/>
-      </left>
-      <right style="medium">
-        <color theme="8"/>
-      </right>
-      <top style="medium">
-        <color theme="8"/>
-      </top>
-      <bottom style="medium">
-        <color theme="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="5"/>
-      </left>
-      <right style="medium">
-        <color theme="5"/>
-      </right>
-      <top style="medium">
-        <color theme="5"/>
-      </top>
-      <bottom style="medium">
-        <color theme="5"/>
       </bottom>
       <diagonal/>
     </border>
@@ -774,6 +749,7 @@
       <bottom style="thin">
         <color theme="6"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -788,6 +764,7 @@
       <bottom style="medium">
         <color rgb="FF0000FF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -802,6 +779,7 @@
       <bottom style="thin">
         <color theme="7"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -816,6 +794,7 @@
       <bottom style="thin">
         <color theme="5"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -829,6 +808,36 @@
       </top>
       <bottom style="thin">
         <color theme="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
@@ -845,11 +854,12 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -887,9 +897,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -939,11 +946,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -955,26 +957,20 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="21" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1001,33 +997,27 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1046,17 +1036,91 @@
     <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="42" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="43" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="42" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="43" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="43" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="42" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="42" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="42" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="43" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="43" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="29">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1113,6 +1177,13 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF8696B"/>
           <bgColor rgb="FFF8696B"/>
         </patternFill>
@@ -1158,14 +1229,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
+          <fgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1173,13 +1237,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1215,6 +1272,44 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1481,59 +1576,84 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="24.6640625" customWidth="1" min="4" max="4"/>
+    <col width="13.1640625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="110.5" bestFit="1" customWidth="1" style="122" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1">
+    <row r="1">
       <c r="A1" s="52" t="inlineStr">
         <is>
-          <t>SUMMARY / CONTROL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="53" t="inlineStr">
-        <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B2" s="53" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C2" s="53" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D2" s="53" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E2" s="53" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="2" ht="16" customHeight="1" thickBot="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Reactor</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Reactor_sel</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" s="132" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="F2" s="123" t="inlineStr">
+        <is>
+          <t>Active build. Choose from the values below. Dropdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1" thickBot="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Reactor (select)</t>
+          <t>Electrode</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Reactor_sel</t>
+          <t>electrode_sel</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -1541,284 +1661,301 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D3" s="89" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Active build. Choose from the values below. Dropdown.</t>
+      <c r="D3" s="132" t="inlineStr">
+        <is>
+          <t>MMO tube</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="F3" s="123" t="inlineStr">
+        <is>
+          <t>CO₂ delivery route. Choose from the values below. Dropdown.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Electrode (select)</t>
+          <t>HOB organism</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>electrode_sel</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="104" t="inlineStr">
-        <is>
-          <t>MMO Tubular</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>CO₂ delivery route. Choose from the values below. Dropdown.</t>
+          <t>organism_sel</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="132" t="inlineStr">
+        <is>
+          <t>Cupriavidus necator</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="F4" s="123" t="inlineStr">
+        <is>
+          <t>The HOB strain; sets the DO band the schedule targets.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>HOB organism (select)</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>organism_sel</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="91" t="inlineStr">
-        <is>
-          <t>Cupriavidus necator</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>Input (you set it)</t>
-        </is>
-      </c>
-      <c r="F5" s="109" t="inlineStr">
-        <is>
-          <t>The HOB strain; sets the DO band the schedule targets.</t>
+          <t>media_sel</t>
+        </is>
+      </c>
+      <c r="D5" s="132" t="inlineStr">
+        <is>
+          <t>Sydow 2017 minimal</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="F5" s="123" t="inlineStr">
+        <is>
+          <t>Growth medium.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Media (select)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>media_sel</t>
-        </is>
-      </c>
-      <c r="D6" s="79" t="inlineStr">
-        <is>
-          <t>Sydow 2017 minimal</t>
-        </is>
+          <t>LED intensity setpoint</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>led_intensity</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D6" s="133" t="n">
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Input (you set it)</t>
-        </is>
-      </c>
-      <c r="F6" s="109" t="inlineStr">
-        <is>
-          <t>Growth medium.</t>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="F6" s="123" t="inlineStr">
+        <is>
+          <t>Pioreactor LED channel % driving electrolysis current (Gerrit's Law, valid 3-25%).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LED intensity setpoint</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>led_intensity</t>
+          <t>Stirrer rate</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>stir_rpm_set</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D7" s="79" t="n">
-        <v>3</v>
+          <t>rpm</t>
+        </is>
+      </c>
+      <c r="D7" s="133" t="n">
+        <v>500</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Input - Pioreactor LED channel</t>
-        </is>
-      </c>
-      <c r="F7" s="109" t="inlineStr">
-        <is>
-          <t>% driving electrolysis current (Gerrit's Law, valid 3-25%).</t>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="F7" s="123" t="inlineStr">
+        <is>
+          <t>Stir rate; sets tip speed and surface O2 transfer.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Stirrer rate</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>stir_rpm_set</t>
+          <t>Media volume</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>media_volume</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rpm</t>
-        </is>
-      </c>
-      <c r="D8" s="79" t="n">
-        <v>500</v>
-      </c>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D8" s="133" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Input - Pioreactor</t>
-        </is>
-      </c>
-      <c r="F8" s="109" t="inlineStr">
-        <is>
-          <t>Stir rate; sets tip speed and surface O2 transfer.</t>
+          <t>input/blank</t>
+        </is>
+      </c>
+      <c r="F8" s="123" t="inlineStr">
+        <is>
+          <t>Liquid charged; leave blank to use the reactor's recommended max working volume.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Media volume</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>media_volume</t>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>temp_C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="D9" s="80" t="n"/>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="D9" s="133" t="n"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Input (you set it)</t>
-        </is>
-      </c>
-      <c r="F9" s="109" t="inlineStr">
-        <is>
-          <t>Liquid charged; leave blank to use the reactor's recommended max working volume.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>input</t>
+        </is>
+      </c>
+      <c r="F9" s="123" t="inlineStr">
+        <is>
+          <t>Temperature setpoint; sets Henry solubilities and rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1" thickBot="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>temp_C</t>
+          <t>Ambient pressure</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>P_atm_set</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>degC</t>
-        </is>
-      </c>
-      <c r="D10" s="80" t="n">
-        <v>30</v>
-      </c>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D10" s="133" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Input - Pioreactor</t>
-        </is>
-      </c>
-      <c r="F10" s="109" t="inlineStr">
-        <is>
-          <t>Temperature setpoint; sets Henry solubilities and rates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1" thickBot="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Ambient pressure</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>P_atm_set</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D11" s="80" t="n">
-        <v>101325</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Input (record on the day)</t>
-        </is>
-      </c>
-      <c r="F11" s="109" t="inlineStr">
-        <is>
-          <t>Lab pressure; default 101325 Pa is fine for design (low sensitivity).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="D12" s="103" t="n"/>
+          <t>input/blank</t>
+        </is>
+      </c>
+      <c r="F10" s="134" t="inlineStr">
+        <is>
+          <t>blank = default 101325 Pa</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" s="91" t="n"/>
+      <c r="F11" s="123" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1" thickBot="1">
+      <c r="A12" s="52" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C12" s="52" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D12" s="52" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F12" s="52" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="16" customHeight="1" thickBot="1">
-      <c r="A13" s="110" t="inlineStr">
-        <is>
-          <t>KEY RESULTS  — enter these two into the plugin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="110" t="inlineStr">
+      <c r="A13" s="126" t="inlineStr">
         <is>
           <t>CO₂ pulse duration</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="D14" s="111">
+      <c r="D13" s="135">
         <f>IFERROR('Mass Transfer'!$D$90,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
-      <c r="E14" s="112">
+      <c r="E13" s="97">
         <f>HYPERLINK("#'Mass Transfer'!D90","→ Mass")</f>
         <v/>
       </c>
-      <c r="F14" s="109" t="inlineStr">
+      <c r="F13" s="123" t="inlineStr">
         <is>
           <t>How long to open the CO2 solenoid each dose.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="110" t="inlineStr">
+    <row r="14" ht="16" customFormat="1" customHeight="1" s="124" thickBot="1">
+      <c r="A14" s="126" t="inlineStr">
+        <is>
+          <t>CO₂ pulse duration (rounded)</t>
+        </is>
+      </c>
+      <c r="C14" s="124" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D14" s="135">
+        <f>IF(D13&gt;0.5,ROUND(D13,0),ROUND(D13,1-(1+INT(LOG10(ABS(D13))))))</f>
+        <v/>
+      </c>
+      <c r="F14" s="125" t="n"/>
+    </row>
+    <row r="15" ht="16" customHeight="1" thickBot="1">
+      <c r="A15" s="126" t="inlineStr">
         <is>
           <t>CO₂ sparge interval</t>
         </is>
@@ -1828,599 +1965,629 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D15" s="111">
+      <c r="D15" s="135">
         <f>IFERROR('Mass Transfer'!$D$91,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
-      <c r="E15" s="112">
+      <c r="E15" s="97">
         <f>HYPERLINK("#'Mass Transfer'!D91","→ Mass")</f>
         <v/>
       </c>
-      <c r="F15" s="109" t="inlineStr">
+      <c r="F15" s="123" t="inlineStr">
         <is>
           <t>Time between doses (conservative, O2-safe). The 'interval can be relaxed?' check below says if you can dose less often.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="D16" s="55" t="n"/>
-      <c r="E16" s="78" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="110" t="inlineStr">
-        <is>
-          <t>CHECKS  — if every one is GREEN, trust the two results above and enter them</t>
-        </is>
-      </c>
-      <c r="D17" s="55" t="n"/>
-      <c r="E17" s="78" t="n"/>
+      <c r="A16" s="126" t="inlineStr">
+        <is>
+          <t>CO₂ sparge interval rounded)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D16" s="135">
+        <f>IF(D15&gt;0.5,ROUND(D15,0),ROUND(D15,1-(1+INT(LOG10(ABS(D15))))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="69" t="n"/>
+      <c r="F16" s="123" t="n"/>
+    </row>
+    <row r="17" customFormat="1" s="124">
+      <c r="A17" s="127" t="n"/>
+      <c r="D17" s="128" t="n"/>
+      <c r="E17" s="128" t="n"/>
+      <c r="F17" s="125" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Vial geometry consistent?</t>
-        </is>
-      </c>
-      <c r="D18" s="113">
-        <f>Geometry!$D$90</f>
-        <v/>
-      </c>
-      <c r="E18" s="112">
-        <f>HYPERLINK("#Geometry!D90","→ Geometry")</f>
-        <v/>
-      </c>
-      <c r="F18" s="109" t="inlineStr">
-        <is>
-          <t>Red until the vial headspace is measured (vial-geometry.md). While red, the pulse above is provisional (~4x uncertain).</t>
+      <c r="A18" s="52" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="B18" s="52" t="n"/>
+      <c r="C18" s="52" t="n"/>
+      <c r="D18" s="52" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E18" s="52" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F18" s="52" t="inlineStr">
+        <is>
+          <t>Comment</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Reactor calibrated?</t>
-        </is>
-      </c>
-      <c r="D19" s="114">
-        <f>'Mass Transfer'!$D$120</f>
-        <v/>
-      </c>
-      <c r="E19" s="112">
-        <f>HYPERLINK("#'Mass Transfer'!D120","→ Mass")</f>
-        <v/>
-      </c>
-      <c r="F19" s="109" t="inlineStr">
-        <is>
-          <t>Red = no CO2-flow calibration for this reactor; results read 'calibrate first' (flow-calibration.md).</t>
+          <t>Vial geometry consistent?</t>
+        </is>
+      </c>
+      <c r="D19" s="136">
+        <f>Geometry!$D$90</f>
+        <v/>
+      </c>
+      <c r="E19" s="97">
+        <f>HYPERLINK("#Geometry!D90","→ Geometry")</f>
+        <v/>
+      </c>
+      <c r="F19" s="123" t="inlineStr">
+        <is>
+          <t>Red until the vial headspace is measured (vial-geometry.md). While red, the pulse above is provisional (~4x uncertain).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O₂ at/under organism optimum?</t>
-        </is>
-      </c>
-      <c r="D20" s="115">
-        <f>'Mass Transfer'!$D$109</f>
-        <v/>
-      </c>
-      <c r="E20" s="112">
-        <f>HYPERLINK("#'Mass Transfer'!D109","→ Mass")</f>
-        <v/>
-      </c>
-      <c r="F20" s="109" t="inlineStr">
-        <is>
-          <t>Green = dissolved O2 sits at/under the organism optimum; red = surface stripping insufficient, O2 may breach impairment.</t>
+          <t>Reactor calibrated?</t>
+        </is>
+      </c>
+      <c r="D20" s="137">
+        <f>'Mass Transfer'!$D$120</f>
+        <v/>
+      </c>
+      <c r="E20" s="97">
+        <f>HYPERLINK("#'Mass Transfer'!D120","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F20" s="123" t="inlineStr">
+        <is>
+          <t>Red = no CO2-flow calibration for this reactor; results read 'calibrate first' (flow-calibration.md).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O₂ above organism minimum?</t>
-        </is>
-      </c>
-      <c r="D21" s="115">
-        <f>'Mass Transfer'!$D$110</f>
-        <v/>
-      </c>
-      <c r="E21" s="112">
-        <f>HYPERLINK("#'Mass Transfer'!D110","→ Mass")</f>
-        <v/>
-      </c>
-      <c r="F21" s="109" t="inlineStr">
-        <is>
-          <t>Minimum DO is a data gap for most organisms (dissolved-oxygen.md).</t>
+          <t>O₂ at/under organism optimum?</t>
+        </is>
+      </c>
+      <c r="D21" s="137">
+        <f>'Mass Transfer'!$D$109</f>
+        <v/>
+      </c>
+      <c r="E21" s="97">
+        <f>HYPERLINK("#'Mass Transfer'!D109","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F21" s="123" t="inlineStr">
+        <is>
+          <t>Green = dissolved O2 sits at/under the organism optimum; red = surface stripping insufficient, O2 may breach impairment.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Interval can be relaxed (carbon-limited)?</t>
-        </is>
-      </c>
-      <c r="D22" s="115">
-        <f>'Mass Transfer'!$D$113</f>
-        <v/>
-      </c>
-      <c r="E22" s="112">
-        <f>HYPERLINK("#'Mass Transfer'!D113","→ Mass")</f>
-        <v/>
-      </c>
-      <c r="F22" s="109" t="inlineStr">
-        <is>
-          <t>If surface stripping handles O2 you may dose far less often (the carbon-limited interval, in Supporting figures). The interval above is the safe fallback until kL_surf is measured.</t>
+          <t>O₂ above organism minimum?</t>
+        </is>
+      </c>
+      <c r="D22" s="137">
+        <f>'Mass Transfer'!$D$110</f>
+        <v/>
+      </c>
+      <c r="E22" s="97">
+        <f>HYPERLINK("#'Mass Transfer'!D110","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F22" s="123" t="inlineStr">
+        <is>
+          <t>Minimum DO is a data gap for most organisms (dissolved-oxygen.md).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H₂ headspace safe?</t>
-        </is>
-      </c>
-      <c r="D23" s="116">
-        <f>Biology!$D$44</f>
-        <v/>
-      </c>
-      <c r="E23" s="112">
-        <f>HYPERLINK("#Biology!D44","→ Biology")</f>
-        <v/>
-      </c>
-      <c r="F23" s="109" t="inlineStr">
-        <is>
-          <t>EXPLOSIVE = H2 evolves faster than it dissolves; ensure headspace venting and no ignition source.</t>
+          <t>Interval can be relaxed (carbon-limited)?</t>
+        </is>
+      </c>
+      <c r="D23" s="137">
+        <f>'Mass Transfer'!$D$113</f>
+        <v/>
+      </c>
+      <c r="E23" s="97">
+        <f>HYPERLINK("#'Mass Transfer'!D113","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F23" s="123" t="inlineStr">
+        <is>
+          <t>If surface stripping handles O2 you may dose far less often (the carbon-limited interval, in Supporting figures). The interval above is the safe fallback until kL_surf is measured.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bubble model valid?</t>
-        </is>
-      </c>
-      <c r="D24" s="115">
-        <f>'Mass Transfer'!$D$64</f>
-        <v/>
-      </c>
-      <c r="E24" s="112">
-        <f>HYPERLINK("#'Mass Transfer'!D64","→ Mass")</f>
-        <v/>
-      </c>
-      <c r="F24" s="109" t="inlineStr">
-        <is>
-          <t>'Sinter OOR' = sinter pore size out of the validated bubble range; sparge mass-transfer is approximate (expected for the porosity-0 disc).</t>
+          <t>H₂ headspace safe?</t>
+        </is>
+      </c>
+      <c r="D24" s="138">
+        <f>Biology!$D$44</f>
+        <v/>
+      </c>
+      <c r="E24" s="97">
+        <f>HYPERLINK("#Biology!D44","→ Biology")</f>
+        <v/>
+      </c>
+      <c r="F24" s="123" t="inlineStr">
+        <is>
+          <t>EXPLOSIVE = H2 evolves faster than it dissolves; ensure headspace venting and no ignition source.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CO₂ supply meets demand?</t>
-        </is>
-      </c>
-      <c r="D25" s="115">
-        <f>IFERROR('Mass Transfer'!$D$126,"calibrate this reactor first (see CO2 flows)")</f>
-        <v/>
-      </c>
-      <c r="E25" s="112">
-        <f>HYPERLINK("#'Mass Transfer'!D126","→ Mass")</f>
-        <v/>
-      </c>
-      <c r="F25" s="109" t="inlineStr">
-        <is>
-          <t>Ratio of CO2 supplied to carbon demand; should be &gt;= 1.</t>
+          <t>Bubble model valid?</t>
+        </is>
+      </c>
+      <c r="D25" s="137">
+        <f>'Mass Transfer'!$D$64</f>
+        <v/>
+      </c>
+      <c r="E25" s="97">
+        <f>HYPERLINK("#'Mass Transfer'!D64","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F25" s="123" t="inlineStr">
+        <is>
+          <t>'Sinter OOR' = sinter pore size out of the validated bubble range; sparge mass-transfer is approximate (expected for the porosity-0 disc).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>CO₂ supply meets demand?</t>
+        </is>
+      </c>
+      <c r="D26" s="137">
+        <f>IFERROR('Mass Transfer'!$D$126,"calibrate this reactor first (see CO2 flows)")</f>
+        <v/>
+      </c>
+      <c r="E26" s="97">
+        <f>HYPERLINK("#'Mass Transfer'!D126","→ Mass")</f>
+        <v/>
+      </c>
+      <c r="F26" s="123" t="inlineStr">
+        <is>
+          <t>Ratio of CO2 supplied to carbon demand; should be &gt;= 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Pulse ≥ solenoid floor?</t>
         </is>
       </c>
-      <c r="D26" s="114">
+      <c r="D27" s="137">
         <f>IFERROR('Mass Transfer'!$D$130,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
-      <c r="E26" s="112">
+      <c r="E27" s="97">
         <f>HYPERLINK("#'Mass Transfer'!D130","→ Mass")</f>
         <v/>
       </c>
-      <c r="F26" s="109" t="inlineStr">
+      <c r="F27" s="123" t="inlineStr">
         <is>
           <t>The optimal pulse must exceed the shortest reliable sparge.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="54" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="53" t="inlineStr">
         <is>
           <t>Dosing window OK?</t>
         </is>
       </c>
-      <c r="D27" s="115">
+      <c r="D28" s="137">
         <f>IFERROR('Mass Transfer'!$D$95,"calibrate this reactor first (see CO2 flows)")</f>
         <v/>
       </c>
-      <c r="E27" s="112">
+      <c r="E28" s="97">
         <f>HYPERLINK("#'Mass Transfer'!D95","→ Mass")</f>
         <v/>
       </c>
-      <c r="F27" s="109" t="inlineStr">
+      <c r="F28" s="123" t="inlineStr">
         <is>
           <t>Enough gap between doses to read OD without sparging.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="92" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="80" t="inlineStr">
         <is>
           <t>Carryover risk?</t>
         </is>
       </c>
-      <c r="D28" s="115">
+      <c r="D29" s="137">
         <f>'Mass Transfer'!$D$59</f>
         <v/>
       </c>
-      <c r="E28" s="112">
+      <c r="E29" s="97">
         <f>HYPERLINK("#'Mass Transfer'!D59","→ Mass")</f>
         <v/>
       </c>
-      <c r="F28" s="109" t="inlineStr">
+      <c r="F29" s="123" t="inlineStr">
         <is>
           <t>Gas velocity below the entrainment limit (no liquid carried out).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="95" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="83" t="inlineStr">
         <is>
           <t>Tip-speed shear OK?</t>
         </is>
       </c>
-      <c r="D29" s="115">
+      <c r="D30" s="137">
         <f>'Mass Transfer'!$D$111</f>
         <v/>
       </c>
-      <c r="E29" s="112">
+      <c r="E30" s="97">
         <f>HYPERLINK("#'Mass Transfer'!D111","→ Mass")</f>
         <v/>
       </c>
-      <c r="F29" s="109" t="inlineStr">
+      <c r="F30" s="123" t="inlineStr">
         <is>
           <t>Stirrer tip speed under the conservative 1.5 m/s shear limit.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>Media volume fits vial?</t>
         </is>
       </c>
-      <c r="D30" s="113">
+      <c r="D31" s="136">
         <f>Geometry!$D$54</f>
         <v/>
       </c>
-      <c r="E30" s="112">
+      <c r="E31" s="97">
         <f>HYPERLINK("#Geometry!D54","→ Geometry")</f>
         <v/>
       </c>
-      <c r="F30" s="109" t="inlineStr">
+      <c r="F31" s="123" t="inlineStr">
         <is>
           <t>Media volume not exceeding the max working volume.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Liquid level OK?</t>
         </is>
       </c>
-      <c r="D31" s="113">
+      <c r="D32" s="136">
         <f>Geometry!$D$55</f>
         <v/>
       </c>
-      <c r="E31" s="112">
+      <c r="E32" s="97">
         <f>HYPERLINK("#Geometry!D55","→ Geometry")</f>
         <v/>
       </c>
-      <c r="F31" s="109" t="inlineStr">
+      <c r="F32" s="123" t="inlineStr">
         <is>
           <t>Liquid not above the usable vial depth.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>LED current-law in range?</t>
         </is>
       </c>
-      <c r="D32" s="117">
+      <c r="D33" s="139">
         <f>Electrochemistry!$D$20</f>
         <v/>
       </c>
-      <c r="E32" s="112">
+      <c r="E33" s="97">
         <f>HYPERLINK("#Electrochemistry!D20","→ Electrochemistry")</f>
         <v/>
       </c>
-      <c r="F32" s="109" t="inlineStr">
+      <c r="F33" s="123" t="inlineStr">
         <is>
           <t>LED intensity within Gerrit's-Law validated band 3-25% (gerrit-current.md).</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="n"/>
-    </row>
     <row r="34">
-      <c r="A34" s="110" t="inlineStr">
+      <c r="A34" s="4" t="n"/>
+      <c r="F34" s="123" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="95" t="inlineStr">
         <is>
           <t>SUPPORTING FIGURES  (context, not pass/fail)</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="F35" s="123" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>Steady-state DO (surface)</t>
         </is>
       </c>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="25" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="D35" s="118">
+      <c r="D36" s="137">
         <f>'Mass Transfer'!$D$108</f>
         <v/>
       </c>
-      <c r="E35" s="112">
+      <c r="E36" s="97">
         <f>HYPERLINK("#'Mass Transfer'!D108","→ Mass")</f>
         <v/>
       </c>
-      <c r="F35" s="109" t="inlineStr">
+      <c r="F36" s="123" t="inlineStr">
         <is>
           <t>Predicted dissolved O2 the surface stripping settles at; compare to the organism band.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="27" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
         <is>
           <t>Sparge interval if O₂ handled</t>
         </is>
       </c>
-      <c r="B36" s="25" t="n"/>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="B37" s="24" t="n"/>
+      <c r="C37" s="25" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="D36" s="118">
+      <c r="D37" s="137">
         <f>'Mass Transfer'!$D$112</f>
         <v/>
       </c>
-      <c r="E36" s="112">
+      <c r="E37" s="97">
         <f>HYPERLINK("#'Mass Transfer'!D112","→ Mass")</f>
         <v/>
       </c>
-      <c r="F36" s="109" t="inlineStr">
+      <c r="F37" s="123" t="inlineStr">
         <is>
           <t>The longer (carbon-limited) interval usable if the 'relaxed' check is green.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Stir-bar tip speed</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
       </c>
-      <c r="D37" s="115">
+      <c r="D38" s="137">
         <f>'Mass Transfer'!$D$68</f>
         <v/>
       </c>
-      <c r="E37" s="112">
+      <c r="E38" s="97">
         <f>HYPERLINK("#'Mass Transfer'!D68","→ Mass")</f>
         <v/>
       </c>
-      <c r="F37" s="109" t="inlineStr">
+      <c r="F38" s="123" t="inlineStr">
         <is>
           <t>Checked against 1.5 m/s above.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="67" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="61" t="inlineStr">
         <is>
           <t>Carbon margin</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="D38" s="119">
+      <c r="D39" s="138">
         <f>Biology!$D$35</f>
         <v/>
       </c>
-      <c r="E38" s="112">
+      <c r="E39" s="97">
         <f>HYPERLINK("#Biology!D35","→ Biology")</f>
         <v/>
       </c>
-      <c r="F38" s="109" t="inlineStr">
+      <c r="F39" s="123" t="inlineStr">
         <is>
           <t>Dissolved CO2 vs RuBisCO Km at in-sparge peak; large = ample carbon.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="110" t="inlineStr">
-        <is>
-          <t>KEY  (whole workbook)</t>
-        </is>
-      </c>
-    </row>
+    <row r="40"/>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="52" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+      <c r="E41" s="52" t="n"/>
+      <c r="F41" s="52" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="105" t="inlineStr">
         <is>
           <t>Verified / handbook / defined / standard</t>
         </is>
       </c>
-      <c r="D41" s="120" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="D42" s="66" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="106" t="inlineStr">
         <is>
           <t>Literature-supported (~90%)</t>
         </is>
       </c>
-      <c r="D42" s="121" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="D43" s="66" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="130" t="inlineStr">
         <is>
           <t>Design assumption (~70%)</t>
         </is>
       </c>
-      <c r="D43" s="122" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="63" t="inlineStr">
+      <c r="D44" s="66" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="107" t="inlineStr">
         <is>
           <t>Weak / coarse estimate (~50%)</t>
         </is>
       </c>
-      <c r="D44" s="123" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="D45" s="66" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="108" t="inlineStr">
         <is>
           <t>Guess - replace when known</t>
         </is>
       </c>
-      <c r="D45" s="124" t="n"/>
-      <c r="E45" s="78" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="D46" s="66" t="n"/>
+      <c r="E46" s="69" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="67" t="inlineStr">
         <is>
           <t>DATA GAP - measure, do not invent</t>
         </is>
       </c>
-      <c r="D46" s="75" t="n"/>
-      <c r="E46" s="78" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="125" t="inlineStr">
+      <c r="D47" s="66" t="n"/>
+      <c r="E47" s="69" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="109" t="inlineStr">
         <is>
           <t>Value font: blue = input you set/measure</t>
         </is>
       </c>
-      <c r="D47" s="72" t="n"/>
-      <c r="E47" s="78" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="105" t="inlineStr">
+      <c r="D48" s="66" t="n"/>
+      <c r="E48" s="69" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="93" t="inlineStr">
         <is>
           <t>black = formula / derived</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="126" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="110" t="inlineStr">
         <is>
           <t>purple = fixed data / constant</t>
         </is>
       </c>
-      <c r="D49" s="71" t="n"/>
-      <c r="E49" s="78" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>CHECK fills: green = OK · amber = caution · red = problem</t>
         </is>
       </c>
-      <c r="D50" s="127" t="n"/>
-      <c r="E50" s="128" t="n"/>
-      <c r="F50" s="68" t="n"/>
-    </row>
-    <row r="51">
-      <c r="D51" s="72" t="n"/>
-      <c r="E51" s="78" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="110" t="inlineStr">
-        <is>
-          <t>RANKED IMPROVEMENTS</t>
-        </is>
-      </c>
-      <c r="D52" s="72" t="n"/>
-      <c r="E52" s="78" t="n"/>
+      <c r="D52" s="66" t="n"/>
+      <c r="E52" s="69" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="110" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B53" s="110" t="inlineStr">
+      <c r="A53" s="129" t="inlineStr">
+        <is>
+          <t>Improvements</t>
+        </is>
+      </c>
+      <c r="B53" s="129" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="C53" s="110" t="inlineStr">
+      <c r="C53" s="129" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
-      <c r="D53" s="110" t="inlineStr">
+      <c r="D53" s="129" t="inlineStr">
         <is>
           <t>Protocol</t>
         </is>
       </c>
-      <c r="F53" s="110" t="inlineStr">
+      <c r="E53" s="129" t="n"/>
+      <c r="F53" s="129" t="inlineStr">
         <is>
           <t>Why it matters</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="54" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Measure surface kLa (kL_surf)</t>
         </is>
       </c>
-      <c r="B54" s="63" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="C54" s="63" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="D54" s="112">
-        <f>HYPERLINK("protocols/surface-kla.md","surface-kla.md protocol →")</f>
-        <v/>
-      </c>
-      <c r="E54" s="63" t="n"/>
-      <c r="F54" s="109" t="inlineStr">
+      <c r="D54" s="140">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/surface-kla.md","surface-kla.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="E54" s="57" t="n"/>
+      <c r="F54" s="123" t="inlineStr">
         <is>
           <t>375% sensitivity; decides the safe sparge interval</t>
         </is>
@@ -2442,11 +2609,11 @@
           <t>med</t>
         </is>
       </c>
-      <c r="D55" s="112">
-        <f>HYPERLINK("protocols/faradaic-efficiency.md","faradaic-efficiency.md protocol →")</f>
-        <v/>
-      </c>
-      <c r="F55" s="109" t="inlineStr">
+      <c r="D55" s="140">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/faradaic-efficiency.md","faradaic-efficiency.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="F55" s="123" t="inlineStr">
         <is>
           <t>sets the H2/O2 split; O2 figures are an upper bound at etaF=1</t>
         </is>
@@ -2468,11 +2635,11 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D56" s="112">
-        <f>HYPERLINK("protocols/dissolved-oxygen.md","dissolved-oxygen.md protocol →")</f>
-        <v/>
-      </c>
-      <c r="F56" s="109" t="inlineStr">
+      <c r="D56" s="140">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/dissolved-oxygen.md","dissolved-oxygen.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="F56" s="123" t="inlineStr">
         <is>
           <t>lower DO guardrail; a gap for every organism</t>
         </is>
@@ -2494,11 +2661,11 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D57" s="112">
-        <f>HYPERLINK("protocols/flow-calibration.md","flow-calibration.md protocol →")</f>
-        <v/>
-      </c>
-      <c r="F57" s="109" t="inlineStr">
+      <c r="D57" s="140">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/flow-calibration.md","flow-calibration.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="F57" s="123" t="inlineStr">
         <is>
           <t>each experiment; only ed04 done</t>
         </is>
@@ -2520,11 +2687,11 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D58" s="112">
-        <f>HYPERLINK("protocols/knallgas-stoichiometry.md","knallgas-stoichiometry.md protocol →")</f>
-        <v/>
-      </c>
-      <c r="F58" s="109" t="inlineStr">
+      <c r="D58" s="140">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/knallgas-stoichiometry.md","knallgas-stoichiometry.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="F58" s="123" t="inlineStr">
         <is>
           <t>sets O2 surplus + carbon demand; needs a growing culture</t>
         </is>
@@ -2546,11 +2713,11 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D59" s="112">
-        <f>HYPERLINK("protocols/sinter-porosity.md","sinter-porosity.md protocol →")</f>
-        <v/>
-      </c>
-      <c r="F59" s="109" t="inlineStr">
+      <c r="D59" s="140">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/sinter-porosity.md","sinter-porosity.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="F59" s="123" t="inlineStr">
         <is>
           <t>bubble size; currently grade 0 from Gerrit's disc</t>
         </is>
@@ -2572,81 +2739,82 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D60" s="112">
-        <f>HYPERLINK("protocols/README.md","README.md protocol →")</f>
-        <v/>
-      </c>
-      <c r="F60" s="109" t="inlineStr">
+      <c r="D60" s="140">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/README.md","README.md protocol →")</f>
+        <v/>
+      </c>
+      <c r="F60" s="123" t="inlineStr">
         <is>
           <t>Henry solubilities + gas volumes</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="D61" s="102" t="n"/>
-    </row>
+      <c r="D61" s="90" t="n"/>
+    </row>
+    <row r="62"/>
     <row r="63">
-      <c r="A63" s="63" t="n"/>
+      <c r="A63" s="57" t="n"/>
     </row>
     <row r="64">
-      <c r="D64" s="72" t="n"/>
+      <c r="D64" s="66" t="n"/>
     </row>
     <row r="65">
-      <c r="D65" s="72" t="n"/>
+      <c r="D65" s="66" t="n"/>
     </row>
     <row r="66">
-      <c r="D66" s="72" t="n"/>
+      <c r="D66" s="66" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D18:D32">
-    <cfRule type="expression" priority="11" dxfId="1" stopIfTrue="1">
-      <formula>OR(ISNUMBER(SEARCH("INCONSISTENT",D18)),ISNUMBER(SEARCH("OVER",D18)),ISNUMBER(SEARCH("BELOW",D18)),ISNUMBER(SEARCH("EXCEED",D18)),ISNUMBER(SEARCH("NO CALIB",D18)),ISNUMBER(SEARCH("calibrate",D18)),ISNUMBER(SEARCH("RISK",D18)),ISNUMBER(SEARCH("EXPLOSIVE",D18)),ISNUMBER(SEARCH("OOR",D18)),ISNUMBER(SEARCH("insufficient",D18)),EXACT(D18,"OUT"),EXACT(D18,"LOW"))</formula>
+  <conditionalFormatting sqref="D19:D33">
+    <cfRule type="expression" priority="14" dxfId="26" stopIfTrue="1">
+      <formula>OR(ISNUMBER(SEARCH("INCONSISTENT",D19)),ISNUMBER(SEARCH("OVER",D19)),ISNUMBER(SEARCH("BELOW",D19)),ISNUMBER(SEARCH("EXCEED",D19)),ISNUMBER(SEARCH("NO CALIB",D19)),ISNUMBER(SEARCH("calibrate",D19)),ISNUMBER(SEARCH("RISK",D19)),ISNUMBER(SEARCH("EXPLOSIVE",D19)),ISNUMBER(SEARCH("OOR",D19)),ISNUMBER(SEARCH("insufficient",D19)),EXACT(D19,"OUT"),EXACT(D19,"LOW"))</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" dxfId="19" stopIfTrue="1">
-      <formula>OR(ISNUMBER(SEARCH("above optimum",D18)),ISNUMBER(SEARCH("watch",D18)),ISNUMBER(SEARCH("NEAREST",D18)),ISNUMBER(SEARCH("unknown",D18)),ISNUMBER(SEARCH("TIGHT",D18)))</formula>
+    <cfRule type="expression" priority="15" dxfId="27" stopIfTrue="1">
+      <formula>OR(ISNUMBER(SEARCH("above optimum",D19)),ISNUMBER(SEARCH("watch",D19)),ISNUMBER(SEARCH("NEAREST",D19)),ISNUMBER(SEARCH("unknown",D19)),ISNUMBER(SEARCH("TIGHT",D19)))</formula>
     </cfRule>
-    <cfRule type="expression" priority="13" dxfId="0" stopIfTrue="1">
-      <formula>OR(EXACT(D18,"OK"),ISNUMBER(SEARCH("calibrated:",D18)),ISNUMBER(SEARCH("under optimum",D18)),ISNUMBER(SEARCH("above min",D18)),ISNUMBER(SEARCH("CARBON-limited",D18)),ISNUMBER(SEARCH("Static",D18)),ISNUMBER(SEARCH("Dynamic",D18)))</formula>
+    <cfRule type="expression" priority="16" dxfId="28" stopIfTrue="1">
+      <formula>OR(EXACT(D19,"OK"),ISNUMBER(SEARCH("calibrated:",D19)),ISNUMBER(SEARCH("under optimum",D19)),ISNUMBER(SEARCH("above min",D19)),ISNUMBER(SEARCH("CARBON-limited",D19)),ISNUMBER(SEARCH("Static",D19)),ISNUMBER(SEARCH("Dynamic",D19)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" priority="14" dxfId="1" stopIfTrue="1">
-      <formula>ISNUMBER(SEARCH("calibrate",D14))</formula>
+  <conditionalFormatting sqref="D13:D16">
+    <cfRule type="expression" priority="17" dxfId="26" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("calibrate",D13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:B60">
-    <cfRule type="expression" priority="15" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="18" dxfId="28" stopIfTrue="1">
       <formula>EXACT(B54,"HIGH")</formula>
     </cfRule>
-    <cfRule type="expression" priority="16" dxfId="19" stopIfTrue="1">
+    <cfRule type="expression" priority="19" dxfId="27" stopIfTrue="1">
       <formula>EXACT(B54,"MED")</formula>
     </cfRule>
-    <cfRule type="expression" priority="17" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="20" dxfId="26" stopIfTrue="1">
       <formula>EXACT(B54,"LOW")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54:C60">
-    <cfRule type="expression" priority="18" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="21" dxfId="28" stopIfTrue="1">
       <formula>EXACT(C54,"low")</formula>
     </cfRule>
-    <cfRule type="expression" priority="19" dxfId="19" stopIfTrue="1">
+    <cfRule type="expression" priority="22" dxfId="27" stopIfTrue="1">
       <formula>EXACT(C54,"med")</formula>
     </cfRule>
-    <cfRule type="expression" priority="20" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="23" dxfId="26" stopIfTrue="1">
       <formula>EXACT(C54,"high")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="D3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Geometry!$A$59:$A$80</formula1>
     </dataValidation>
-    <dataValidation sqref="D4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Electrochemistry!$A$35:$A$37</formula1>
     </dataValidation>
-    <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Biology!$A$52:$A$57</formula1>
     </dataValidation>
-    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Biology!$A$61:$A$61</formula1>
     </dataValidation>
   </dataValidations>
@@ -2671,34 +2839,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="52" t="inlineStr">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>GEOMETRY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="53" t="inlineStr">
+      <c r="A2" s="52" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B2" s="53" t="inlineStr">
+      <c r="B2" s="52" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C2" s="53" t="inlineStr">
+      <c r="C2" s="52" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D2" s="53" t="inlineStr">
+      <c r="D2" s="52" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E2" s="53" t="inlineStr">
+      <c r="E2" s="52" t="inlineStr">
         <is>
           <t>Source / assumption</t>
         </is>
@@ -2708,18 +2876,18 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="6" t="n"/>
       <c r="C3" s="7" t="n"/>
-      <c r="D3" s="28" t="n"/>
+      <c r="D3" s="27" t="n"/>
       <c r="E3" s="8" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>IMPORTS (from other tabs)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="7" t="n"/>
-      <c r="D4" s="28" t="n"/>
+      <c r="D4" s="27" t="n"/>
       <c r="E4" s="8" t="n"/>
     </row>
     <row r="5">
@@ -2738,11 +2906,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D5" s="129">
-        <f>Summary!$D$3</f>
-        <v/>
-      </c>
-      <c r="E5" s="112">
+      <c r="D5" s="141">
+        <f>Summary!$D$2</f>
+        <v/>
+      </c>
+      <c r="E5" s="97">
         <f>HYPERLINK("#Summary!D3","→ Summary")</f>
         <v/>
       </c>
@@ -2763,11 +2931,11 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D6" s="129">
-        <f>Summary!$D$9</f>
-        <v/>
-      </c>
-      <c r="E6" s="112">
+      <c r="D6" s="141">
+        <f>Summary!$D$8</f>
+        <v/>
+      </c>
+      <c r="E6" s="97">
         <f>HYPERLINK("#Summary!D9","→ Summary")</f>
         <v/>
       </c>
@@ -2776,7 +2944,7 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="29" t="n"/>
+      <c r="D7" s="28" t="n"/>
       <c r="E7" s="10" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
@@ -2795,12 +2963,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>AEP0.1.1</t>
         </is>
       </c>
-      <c r="E8" s="130" t="inlineStr">
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
@@ -2822,12 +2990,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>AEP0.2</t>
         </is>
       </c>
-      <c r="E9" s="130" t="inlineStr">
+      <c r="E9" s="112" t="inlineStr">
         <is>
           <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
@@ -2849,10 +3017,10 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="21" t="n">
         <v>27.48</v>
       </c>
-      <c r="E10" s="131" t="inlineStr">
+      <c r="E10" s="113" t="inlineStr">
         <is>
           <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
@@ -2874,10 +3042,10 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="21" t="n">
         <v>27.48</v>
       </c>
-      <c r="E11" s="132" t="inlineStr">
+      <c r="E11" s="114" t="inlineStr">
         <is>
           <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
@@ -2899,10 +3067,10 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="28" t="n">
         <v>55</v>
       </c>
-      <c r="E12" s="133" t="inlineStr">
+      <c r="E12" s="115" t="inlineStr">
         <is>
           <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
@@ -2924,10 +3092,10 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="28" t="n">
         <v>95</v>
       </c>
-      <c r="E13" s="133" t="inlineStr">
+      <c r="E13" s="115" t="inlineStr">
         <is>
           <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
@@ -2949,10 +3117,10 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="28" t="n">
         <v>16</v>
       </c>
-      <c r="E14" s="131" t="inlineStr">
+      <c r="E14" s="113" t="inlineStr">
         <is>
           <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
@@ -2974,10 +3142,10 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="E15" s="131" t="inlineStr">
+      <c r="E15" s="113" t="inlineStr">
         <is>
           <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
@@ -2999,10 +3167,10 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="E16" s="134" t="inlineStr">
+      <c r="E16" s="116" t="inlineStr">
         <is>
           <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
@@ -3024,10 +3192,10 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="28" t="n">
         <v>42</v>
       </c>
-      <c r="E17" s="134" t="inlineStr">
+      <c r="E17" s="116" t="inlineStr">
         <is>
           <t>Superseded by the reactor-type lookup below; not read by any formula</t>
         </is>
@@ -3049,7 +3217,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D18" s="69">
+      <c r="D18" s="142">
         <f>VLOOKUP(rx_ver,$A$84:$I$87,7,FALSE)</f>
         <v/>
       </c>
@@ -3075,7 +3243,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="21" t="n">
         <v>1.1</v>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -3100,7 +3268,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="143">
         <f>vial_OD-2*vial_wall</f>
         <v/>
       </c>
@@ -3126,7 +3294,7 @@
           <t>mm²</t>
         </is>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="144">
         <f>PI()/4*vial_ID^2</f>
         <v/>
       </c>
@@ -3152,7 +3320,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D22" s="70">
+      <c r="D22" s="145">
         <f>VLOOKUP(rx_ver,$A$84:$I$87,4,FALSE)</f>
         <v/>
       </c>
@@ -3178,7 +3346,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D23" s="70">
+      <c r="D23" s="145">
         <f>VLOOKUP(rx_ver,$A$84:$I$87,5,FALSE)</f>
         <v/>
       </c>
@@ -3204,7 +3372,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D24" s="70">
+      <c r="D24" s="145">
         <f>VLOOKUP(rx_ver,$A$84:$I$87,6,FALSE)</f>
         <v/>
       </c>
@@ -3230,7 +3398,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="143">
         <f>V_max*1000/A_x</f>
         <v/>
       </c>
@@ -3256,7 +3424,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="28" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -3281,7 +3449,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D27" s="28" t="n">
+      <c r="D27" s="27" t="n">
         <v>2</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -3306,7 +3474,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="28" t="n">
         <v>22</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -3331,7 +3499,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="144">
         <f>D_int-elec_clear</f>
         <v/>
       </c>
@@ -3357,7 +3525,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D30" s="32" t="n">
+      <c r="D30" s="31" t="n">
         <v>3.175</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -3382,7 +3550,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D31" s="33" t="n">
+      <c r="D31" s="32" t="n">
         <v>1.5875</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -3407,7 +3575,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D32" s="31">
+      <c r="D32" s="144">
         <f>elec_clear</f>
         <v/>
       </c>
@@ -3433,7 +3601,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D33" s="32" t="n">
+      <c r="D33" s="31" t="n">
         <v>3.175</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -3458,7 +3626,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D34" s="33" t="n">
+      <c r="D34" s="32" t="n">
         <v>1.5875</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -3483,7 +3651,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="143">
         <f>MAX(0,h_datum-elec_clear)</f>
         <v/>
       </c>
@@ -3509,7 +3677,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="146">
         <f>rod_n*(PI()/4*rod_d^2)*elec_sub_L/1000</f>
         <v/>
       </c>
@@ -3535,7 +3703,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D37" s="34">
+      <c r="D37" s="146">
         <f>(PI()/4*spg_OD^2)*MAX(0,h_datum-spg_tip_h)/1000</f>
         <v/>
       </c>
@@ -3561,7 +3729,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="146">
         <f>(eff_OD+eff_ID)/2</f>
         <v/>
       </c>
@@ -3587,7 +3755,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D39" s="35">
+      <c r="D39" s="147">
         <f>(PI()/4*(eff_OD^2-eff_ID^2))*eff_sub_L/1000</f>
         <v/>
       </c>
@@ -3613,7 +3781,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D40" s="34">
+      <c r="D40" s="146">
         <f>elec_disp+spg_disp+eff_disp</f>
         <v/>
       </c>
@@ -3639,7 +3807,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D41" s="81">
+      <c r="D41" s="148">
         <f>IF(media_volume&gt;0,media_volume,ROUND(V_max-disp_tot,0))</f>
         <v/>
       </c>
@@ -3665,7 +3833,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="143">
         <f>(V_charge+disp_tot)*1000/A_x</f>
         <v/>
       </c>
@@ -3691,7 +3859,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="143">
         <f>MAX(0,h_actual-spg_tip_h)</f>
         <v/>
       </c>
@@ -3717,7 +3885,7 @@
           <t>mm²</t>
         </is>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="144">
         <f>A_x-(rod_n*(PI()/4*rod_d^2)+(PI()/4*spg_OD^2)+(PI()/4*eff_OD^2))</f>
         <v/>
       </c>
@@ -3743,7 +3911,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="146">
         <f>eff_OD</f>
         <v/>
       </c>
@@ -3769,7 +3937,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D46" s="28" t="n">
+      <c r="D46" s="27" t="n">
         <v>3</v>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -3794,7 +3962,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="28" t="n">
         <v>5</v>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -3819,7 +3987,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D48" s="34">
+      <c r="D48" s="146">
         <f>(rod_n*(PI()/4*rod_d^2)*elec_ins+(PI()/4*spg_OD^2)*spg_len+(PI()/4*(eff_OD^2-eff_ID^2))*(D_int-h_actual)+xtube_n*(PI()/4*xtube_OD^2)*xtube_pro)/1000</f>
         <v/>
       </c>
@@ -3845,7 +4013,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D49" s="30">
+      <c r="D49" s="143">
         <f>V_vial_total-V_charge-V_inserts</f>
         <v/>
       </c>
@@ -3871,11 +4039,11 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D50" s="20">
+      <c r="D50" s="149">
         <f>D_int-spg_tip_h</f>
         <v/>
       </c>
-      <c r="E50" s="21" t="inlineStr">
+      <c r="E50" s="20" t="inlineStr">
         <is>
           <t>Cap underside to release point; tracks spg_tip_h.</t>
         </is>
@@ -3892,7 +4060,7 @@
           <t>rx_ver</t>
         </is>
       </c>
-      <c r="D51" s="72">
+      <c r="D51" s="150">
         <f>VLOOKUP(reactor_sel,$A$59:$B$80,2,FALSE)</f>
         <v/>
       </c>
@@ -3908,13 +4076,13 @@
           <t>stir_bar_L</t>
         </is>
       </c>
-      <c r="D52" s="72">
+      <c r="D52" s="150">
         <f>VLOOKUP(rx_ver,$A$84:$I$87,8,FALSE)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="66" t="inlineStr">
+      <c r="A53" s="60" t="inlineStr">
         <is>
           <t>40 mL OD = 20 mL diameter (Pioreactor source); depths/volumes confirm by measurement.</t>
         </is>
@@ -3931,7 +4099,7 @@
           <t>media_vol_warn</t>
         </is>
       </c>
-      <c r="D54" s="72">
+      <c r="D54" s="150">
         <f>IF(V_charge&gt;V_max,"MEDIA &gt; MAX WORKING VOLUME","OK")</f>
         <v/>
       </c>
@@ -3947,26 +4115,26 @@
           <t>depth_warn</t>
         </is>
       </c>
-      <c r="D55" s="72">
+      <c r="D55" s="150">
         <f>IF(h_actual&gt;D_int,"LIQUID OVER USABLE DEPTH","OK")</f>
         <v/>
       </c>
     </row>
     <row r="56"/>
     <row r="57">
-      <c r="A57" s="67" t="inlineStr">
+      <c r="A57" s="61" t="inlineStr">
         <is>
           <t>REACTOR LOOKUP  (reactor ID → type)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="63" t="inlineStr">
+      <c r="A58" s="57" t="inlineStr">
         <is>
           <t>Reactor</t>
         </is>
       </c>
-      <c r="B58" s="63" t="inlineStr">
+      <c r="B58" s="57" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
@@ -4238,54 +4406,54 @@
     </row>
     <row r="81"/>
     <row r="82">
-      <c r="A82" s="67" t="inlineStr">
+      <c r="A82" s="61" t="inlineStr">
         <is>
           <t>REACTOR-TYPE LOOKUP  (geometry &amp; stir bar; pulled by type)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="63" t="inlineStr">
+      <c r="A83" s="57" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B83" s="63" t="inlineStr">
+      <c r="B83" s="57" t="inlineStr">
         <is>
           <t>Pioreactor</t>
         </is>
       </c>
-      <c r="C83" s="63" t="inlineStr">
+      <c r="C83" s="57" t="inlineStr">
         <is>
           <t>vial (mL)</t>
         </is>
       </c>
-      <c r="D83" s="63" t="inlineStr">
+      <c r="D83" s="57" t="inlineStr">
         <is>
           <t>usable depth (mm)</t>
         </is>
       </c>
-      <c r="E83" s="63" t="inlineStr">
+      <c r="E83" s="57" t="inlineStr">
         <is>
           <t>max working (mL)</t>
         </is>
       </c>
-      <c r="F83" s="63" t="inlineStr">
+      <c r="F83" s="57" t="inlineStr">
         <is>
           <t>total vial (mL)</t>
         </is>
       </c>
-      <c r="G83" s="63" t="inlineStr">
+      <c r="G83" s="57" t="inlineStr">
         <is>
           <t>vial OD (mm)</t>
         </is>
       </c>
-      <c r="H83" s="63" t="inlineStr">
+      <c r="H83" s="57" t="inlineStr">
         <is>
           <t>stir bar L (mm)</t>
         </is>
       </c>
-      <c r="I83" s="63" t="inlineStr">
+      <c r="I83" s="57" t="inlineStr">
         <is>
           <t>stir bar dia (mm)</t>
         </is>
@@ -4425,7 +4593,7 @@
     </row>
     <row r="88"/>
     <row r="89">
-      <c r="A89" s="110" t="inlineStr">
+      <c r="A89" s="95" t="inlineStr">
         <is>
           <t>VIAL GEOMETRY CONSISTENCY CHECK</t>
         </is>
@@ -4442,11 +4610,11 @@
           <t>geom_check</t>
         </is>
       </c>
-      <c r="D90">
+      <c r="D90" s="150">
         <f>IF(ABS(A_x*D_int/1000-V_vial_total)&gt;3,"VIAL GEOMETRY INCONSISTENT - measure true fill volume &amp; bore depth","OK")</f>
         <v/>
       </c>
-      <c r="F90" s="109" t="inlineStr">
+      <c r="F90" s="94" t="inlineStr">
         <is>
           <t>Fires INCONSISTENT for the 20 mL vial because the bare cylinder (A_x x usable depth ~28 mL) overestimates the true 20 mL vial (it tapers/necks, not a full cylinder to 55 mm). Expected tolerance artifact, not a data error - resolved by measuring true bore depth (protocols/vial-geometry.md).</t>
         </is>
@@ -4454,7 +4622,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D86:D87">
-    <cfRule type="expression" priority="1" dxfId="1">
+    <cfRule type="expression" priority="1" dxfId="2">
       <formula>OR(ISNUMBER(SEARCH("RISK",D86)),ISNUMBER(SEARCH("OVER",D86)),ISNUMBER(SEARCH("BELOW",D86)),ISNUMBER(SEARCH("EXCEED",D86)),ISNUMBER(SEARCH("NO CALIB",D86)),ISNUMBER(SEARCH("NEAREST",D86)),ISNUMBER(SEARCH("EXPLOSIVE",D86)),ISNUMBER(SEARCH("LOW",D86)),ISNUMBER(SEARCH("TIGHT",D86)),ISNUMBER(SEARCH("insufficient",D86)))</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="0">
@@ -4481,34 +4649,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="52" t="inlineStr">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>ELECTROCHEMISTRY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="53" t="inlineStr">
+      <c r="A2" s="52" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B2" s="53" t="inlineStr">
+      <c r="B2" s="52" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C2" s="53" t="inlineStr">
+      <c r="C2" s="52" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D2" s="53" t="inlineStr">
+      <c r="D2" s="52" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E2" s="53" t="inlineStr">
+      <c r="E2" s="52" t="inlineStr">
         <is>
           <t>Source / assumption</t>
         </is>
@@ -4518,18 +4686,18 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="6" t="n"/>
       <c r="C3" s="7" t="n"/>
-      <c r="D3" s="82" t="n"/>
+      <c r="D3" s="73" t="n"/>
       <c r="E3" s="8" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>IMPORTS (from other tabs)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="7" t="n"/>
-      <c r="D4" s="36" t="n"/>
+      <c r="D4" s="35" t="n"/>
       <c r="E4" s="9" t="n"/>
     </row>
     <row r="5">
@@ -4548,11 +4716,11 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D5" s="119">
+      <c r="D5" s="138">
         <f>Biology!$D$18</f>
         <v/>
       </c>
-      <c r="E5" s="112">
+      <c r="E5" s="97">
         <f>HYPERLINK("#Biology!D18","→ Biology")</f>
         <v/>
       </c>
@@ -4573,11 +4741,11 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D6" s="119">
+      <c r="D6" s="138">
         <f>Biology!$D$19</f>
         <v/>
       </c>
-      <c r="E6" s="112">
+      <c r="E6" s="97">
         <f>HYPERLINK("#Biology!D19","→ Biology")</f>
         <v/>
       </c>
@@ -4598,11 +4766,11 @@
           <t>J/mol/K</t>
         </is>
       </c>
-      <c r="D7" s="115">
+      <c r="D7" s="137">
         <f>'Mass Transfer'!$D$101</f>
         <v/>
       </c>
-      <c r="E7" s="112">
+      <c r="E7" s="97">
         <f>HYPERLINK("#'Mass Transfer'!D101","→ Mass Transfer")</f>
         <v/>
       </c>
@@ -4618,11 +4786,11 @@
           <t>electrode_sel</t>
         </is>
       </c>
-      <c r="D8" s="129">
-        <f>Summary!$D$4</f>
-        <v/>
-      </c>
-      <c r="E8" s="112">
+      <c r="D8" s="141">
+        <f>Summary!$D$3</f>
+        <v/>
+      </c>
+      <c r="E8" s="97">
         <f>HYPERLINK("#Summary!D4","→ Summary")</f>
         <v/>
       </c>
@@ -4631,7 +4799,7 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="40" t="n"/>
+      <c r="D9" s="39" t="n"/>
       <c r="E9" s="12" t="n"/>
     </row>
     <row r="10">
@@ -4650,8 +4818,8 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D10" s="82">
-        <f>Summary!$D$7</f>
+      <c r="D10" s="151">
+        <f>Summary!$D$6</f>
         <v/>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -4676,10 +4844,10 @@
           <t>mA/%</t>
         </is>
       </c>
-      <c r="D11" s="36" t="n">
+      <c r="D11" s="35" t="n">
         <v>1.03</v>
       </c>
-      <c r="E11" s="96" t="inlineStr">
+      <c r="E11" s="84" t="inlineStr">
         <is>
           <t>Gerrit's Law fit (slope) - from LED-current calibration; see protocol gerrit-current.md</t>
         </is>
@@ -4701,10 +4869,10 @@
           <t>mA</t>
         </is>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="36" t="n">
         <v>2.6</v>
       </c>
-      <c r="E12" s="96" t="inlineStr">
+      <c r="E12" s="84" t="inlineStr">
         <is>
           <t>Gerrit's Law fit (intercept); calibration-derived constant</t>
         </is>
@@ -4726,7 +4894,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D13" s="38" t="n">
+      <c r="D13" s="37" t="n">
         <v>3</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -4751,7 +4919,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D14" s="38" t="n">
+      <c r="D14" s="37" t="n">
         <v>25</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -4776,7 +4944,7 @@
           <t>C/mol</t>
         </is>
       </c>
-      <c r="D15" s="39" t="n">
+      <c r="D15" s="38" t="n">
         <v>96485.33212000001</v>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -4801,7 +4969,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D16" s="40" t="n">
+      <c r="D16" s="39" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -4826,7 +4994,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D17" s="40" t="n">
+      <c r="D17" s="39" t="n">
         <v>4</v>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -4851,7 +5019,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="21" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -4876,7 +5044,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="147">
         <f>(gerrit_slope*intensity+gerrit_int)/1000</f>
         <v/>
       </c>
@@ -4902,7 +5070,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D20" s="41">
+      <c r="D20" s="152">
         <f>IF(AND(intensity&gt;=gerrit_min,intensity&lt;=gerrit_max),"OK","OUT")</f>
         <v/>
       </c>
@@ -4928,7 +5096,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="149">
         <f>I_app*etaF/(z_e_H2*F_const)*3600</f>
         <v/>
       </c>
@@ -4954,7 +5122,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="149">
         <f>I_app*etaF_OER/(z_e_O2*F_const)*3600</f>
         <v/>
       </c>
@@ -4980,7 +5148,7 @@
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="149">
         <f>rH2_gen/60*R_gas*T_K/P_atm*1000000</f>
         <v/>
       </c>
@@ -5006,7 +5174,7 @@
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="149">
         <f>rO2_gen/60*R_gas*T_K/P_atm*1000000</f>
         <v/>
       </c>
@@ -5032,7 +5200,7 @@
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="149">
         <f>V_H2_gen+V_O2_gen</f>
         <v/>
       </c>
@@ -5058,10 +5226,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="97" t="inlineStr">
+      <c r="E26" s="85" t="inlineStr">
         <is>
           <t>Assumes chloride-free medium (no competing Cl2 evolution at the anode)</t>
         </is>
@@ -5083,11 +5251,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D27" s="69">
+      <c r="D27" s="142">
         <f>VLOOKUP(electrode_sel,$A$35:$I$37,9,FALSE)</f>
         <v/>
       </c>
-      <c r="E27" s="135" t="inlineStr">
+      <c r="E27" s="117" t="inlineStr">
         <is>
           <t>Electrode lookup fixes ORR at 2 e- (peroxide pathway, SS cathode, neutral pH) for every current electrode; a 4 e- (to-water) electrode would need its own table row.</t>
         </is>
@@ -5109,11 +5277,11 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D28" s="20">
+      <c r="D28" s="149">
         <f>I_app*(1-etaF)/(z_e_ORR*F_const)*3600</f>
         <v/>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>Cathodic current not making H₂ (1−etaF) reduces dissolved O₂. 0 at etaF=1.</t>
         </is>
@@ -5135,18 +5303,18 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="149">
         <f>rO2_gen-O2_cathode_ORR</f>
         <v/>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>Anodic O₂ minus cathodic consumption — the O₂ the dissolved pool receives.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="66" t="inlineStr">
+      <c r="A30" s="60" t="inlineStr">
         <is>
           <t>z_e_ORR=2 assumed (peroxide, non-Pt SS cathode, neutral pH); etaF unmeasured - both live here per electrode.</t>
         </is>
@@ -5163,7 +5331,7 @@
           <t>sparger_e</t>
         </is>
       </c>
-      <c r="D31" s="72">
+      <c r="D31" s="150">
         <f>VLOOKUP(electrode_sel,$A$35:$I$37,4,FALSE)</f>
         <v/>
       </c>
@@ -5179,66 +5347,66 @@
           <t>por_grade_e</t>
         </is>
       </c>
-      <c r="D32" s="105">
+      <c r="D32" s="150">
         <f>IF(ISNUMBER(VLOOKUP(electrode_sel,$A$35:$I$37,5,FALSE)),VLOOKUP(electrode_sel,$A$35:$I$37,5,FALSE),0)</f>
         <v/>
       </c>
-      <c r="E32" s="109" t="inlineStr">
+      <c r="E32" s="94" t="inlineStr">
         <is>
           <t>Porosity 0 = Gerrit's sourced sintered disc (SD8/0/P 8mm, fallback SD10/0/P 10mm; Scientific Glass Labs, 2026-05)</t>
         </is>
       </c>
-      <c r="H32" s="68" t="n"/>
+      <c r="H32" s="62" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="67" t="inlineStr">
+      <c r="A33" s="61" t="inlineStr">
         <is>
           <t>ELECTRODE LOOKUP  (selecting the electrode sets sparger, porosity, cathode)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="63" t="inlineStr">
+      <c r="A34" s="57" t="inlineStr">
         <is>
           <t>Electrode</t>
         </is>
       </c>
-      <c r="B34" s="63" t="inlineStr">
+      <c r="B34" s="57" t="inlineStr">
         <is>
           <t>anode material</t>
         </is>
       </c>
-      <c r="C34" s="63" t="inlineStr">
+      <c r="C34" s="57" t="inlineStr">
         <is>
           <t>anode dia (mm)</t>
         </is>
       </c>
-      <c r="D34" s="63" t="inlineStr">
+      <c r="D34" s="57" t="inlineStr">
         <is>
           <t>sparger</t>
         </is>
       </c>
-      <c r="E34" s="63" t="inlineStr">
+      <c r="E34" s="57" t="inlineStr">
         <is>
           <t>sinter porosity</t>
         </is>
       </c>
-      <c r="F34" s="63" t="inlineStr">
+      <c r="F34" s="57" t="inlineStr">
         <is>
           <t>cathode</t>
         </is>
       </c>
-      <c r="G34" s="63" t="inlineStr">
+      <c r="G34" s="57" t="inlineStr">
         <is>
           <t>cathode dia (mm)</t>
         </is>
       </c>
-      <c r="H34" s="63" t="inlineStr">
+      <c r="H34" s="57" t="inlineStr">
         <is>
           <t>etaF</t>
         </is>
       </c>
-      <c r="I34" s="63" t="inlineStr">
+      <c r="I34" s="57" t="inlineStr">
         <is>
           <t>z_e_ORR</t>
         </is>
@@ -5276,7 +5444,7 @@
       <c r="G35" t="n">
         <v>6</v>
       </c>
-      <c r="H35" s="68" t="inlineStr">
+      <c r="H35" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -5317,7 +5485,7 @@
       <c r="G36" t="n">
         <v>6</v>
       </c>
-      <c r="H36" s="68" t="inlineStr">
+      <c r="H36" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -5329,7 +5497,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MMO Tubular</t>
+          <t>MMO tube</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5345,7 +5513,7 @@
           <t>Sintered</t>
         </is>
       </c>
-      <c r="E37" s="68" t="n">
+      <c r="E37" s="62" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
@@ -5356,7 +5524,7 @@
       <c r="G37" t="n">
         <v>6</v>
       </c>
-      <c r="H37" s="68" t="inlineStr">
+      <c r="H37" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -5366,17 +5534,17 @@
       </c>
     </row>
     <row r="38">
-      <c r="D38" s="71" t="n"/>
+      <c r="D38" s="65" t="n"/>
     </row>
     <row r="39">
-      <c r="D39" s="72" t="n"/>
+      <c r="D39" s="66" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D13">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="6">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="8">
       <formula>"OUT"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5400,34 +5568,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="52" t="inlineStr">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>BIOLOGY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="53" t="inlineStr">
+      <c r="A2" s="52" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B2" s="53" t="inlineStr">
+      <c r="B2" s="52" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C2" s="53" t="inlineStr">
+      <c r="C2" s="52" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D2" s="53" t="inlineStr">
+      <c r="D2" s="52" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E2" s="53" t="inlineStr">
+      <c r="E2" s="52" t="inlineStr">
         <is>
           <t>Source / assumption</t>
         </is>
@@ -5437,18 +5605,18 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="6" t="n"/>
       <c r="C3" s="7" t="n"/>
-      <c r="D3" s="28" t="n"/>
+      <c r="D3" s="27" t="n"/>
       <c r="E3" s="16" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>IMPORTS (from other tabs)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="7" t="n"/>
-      <c r="D4" s="28" t="n"/>
+      <c r="D4" s="27" t="n"/>
       <c r="E4" s="16" t="n"/>
     </row>
     <row r="5">
@@ -5467,11 +5635,11 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D5" s="117">
+      <c r="D5" s="139">
         <f>Electrochemistry!$D$21</f>
         <v/>
       </c>
-      <c r="E5" s="112">
+      <c r="E5" s="97">
         <f>HYPERLINK("#Electrochemistry!D21","→ Electrochemistry")</f>
         <v/>
       </c>
@@ -5492,11 +5660,11 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D6" s="117">
+      <c r="D6" s="139">
         <f>Electrochemistry!$D$29</f>
         <v/>
       </c>
-      <c r="E6" s="112">
+      <c r="E6" s="97">
         <f>HYPERLINK("#Electrochemistry!D29","→ Electrochemistry")</f>
         <v/>
       </c>
@@ -5517,11 +5685,11 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D7" s="113">
+      <c r="D7" s="136">
         <f>Geometry!$D$41</f>
         <v/>
       </c>
-      <c r="E7" s="112">
+      <c r="E7" s="97">
         <f>HYPERLINK("#Geometry!D41","→ Geometry")</f>
         <v/>
       </c>
@@ -5537,11 +5705,11 @@
           <t>organism_sel</t>
         </is>
       </c>
-      <c r="D8" s="129">
-        <f>Summary!$D$5</f>
-        <v/>
-      </c>
-      <c r="E8" s="112">
+      <c r="D8" s="141">
+        <f>Summary!$D$4</f>
+        <v/>
+      </c>
+      <c r="E8" s="97">
         <f>HYPERLINK("#Summary!D5","→ Summary")</f>
         <v/>
       </c>
@@ -5550,7 +5718,7 @@
       <c r="A9" s="14" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="20" t="n"/>
+      <c r="D9" s="19" t="n"/>
       <c r="E9" s="12" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
@@ -5569,7 +5737,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="27" t="n">
         <v>6</v>
       </c>
       <c r="E10" s="16" t="inlineStr">
@@ -5594,7 +5762,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="27" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="16" t="inlineStr">
@@ -5619,7 +5787,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="27" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="16" t="inlineStr">
@@ -5644,7 +5812,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="149">
         <f>rH2_gen</f>
         <v/>
       </c>
@@ -5670,11 +5838,11 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="149">
         <f>H2_cons*bio_O2/bio_H2</f>
         <v/>
       </c>
-      <c r="E14" s="93" t="inlineStr">
+      <c r="E14" s="81" t="inlineStr">
         <is>
           <t>Assumes 100% H₂ uptake (upper bound); true limit is gas-liquid H₂ transfer — see H2_turnover</t>
         </is>
@@ -5696,7 +5864,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="149">
         <f>H2_cons*bio_CO2/bio_H2</f>
         <v/>
       </c>
@@ -5722,11 +5890,11 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="149">
         <f>O2_net_gen-O2_cons</f>
         <v/>
       </c>
-      <c r="E16" s="94" t="inlineStr">
+      <c r="E16" s="82" t="inlineStr">
         <is>
           <t>Upper bound: rests on full-uptake O2_cons above</t>
         </is>
@@ -5748,8 +5916,8 @@
           <t>°C</t>
         </is>
       </c>
-      <c r="D17" s="83">
-        <f>Summary!$D$10</f>
+      <c r="D17" s="153">
+        <f>Summary!$D$9</f>
         <v/>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -5774,7 +5942,7 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="143">
         <f>T_C+273.15</f>
         <v/>
       </c>
@@ -5800,8 +5968,8 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D19" s="71">
-        <f>Summary!$D$11</f>
+      <c r="D19" s="154">
+        <f>IF(P_atm_set&gt;0,P_atm_set,101325)</f>
         <v/>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -5826,7 +5994,7 @@
           <t>Pa/atm</t>
         </is>
       </c>
-      <c r="D20" s="40" t="n">
+      <c r="D20" s="39" t="n">
         <v>101325</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -5851,7 +6019,7 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D21" s="40" t="n">
+      <c r="D21" s="39" t="n">
         <v>1.2e-05</v>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -5876,7 +6044,7 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D22" s="40" t="n">
+      <c r="D22" s="39" t="n">
         <v>1500</v>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -5901,7 +6069,7 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D23" s="40" t="n">
+      <c r="D23" s="39" t="n">
         <v>298.15</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -5926,7 +6094,7 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D24" s="42">
+      <c r="D24" s="155">
         <f>H_O2ref*EXP(H_O2T*(1/T_K-1/T_ref))</f>
         <v/>
       </c>
@@ -5952,7 +6120,7 @@
           <t>atm</t>
         </is>
       </c>
-      <c r="D25" s="40" t="n">
+      <c r="D25" s="39" t="n">
         <v>0.3</v>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -5977,7 +6145,7 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="144">
         <f>O2_ceil_atm*Pa_per_atm</f>
         <v/>
       </c>
@@ -6003,7 +6171,7 @@
           <t>mol/m³</t>
         </is>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="147">
         <f>H_O2_T*O2_ceil_Pa</f>
         <v/>
       </c>
@@ -6029,7 +6197,7 @@
           <t>µM</t>
         </is>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="144">
         <f>O2_ceil_C*1000</f>
         <v/>
       </c>
@@ -6055,10 +6223,10 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D29" s="43" t="n">
+      <c r="D29" s="42" t="n">
         <v>0.00033</v>
       </c>
-      <c r="E29" s="49" t="inlineStr">
+      <c r="E29" s="48" t="inlineStr">
         <is>
           <t>Sander (2023) compilation; CO₂ ~25× more soluble than O₂.</t>
         </is>
@@ -6080,10 +6248,10 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D30" s="43" t="n">
+      <c r="D30" s="42" t="n">
         <v>2400</v>
       </c>
-      <c r="E30" s="49" t="inlineStr">
+      <c r="E30" s="48" t="inlineStr">
         <is>
           <t>Sander (2023): d ln(Hcp)/d(1/T) for CO₂.</t>
         </is>
@@ -6105,11 +6273,11 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="149">
         <f>H_CO2ref*EXP(H_CO2T*(1/T_K-1/T_ref))</f>
         <v/>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>van 't Hoff to reactor T.</t>
         </is>
@@ -6131,11 +6299,11 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="149">
         <f>P_atm</f>
         <v/>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>Pure-CO₂ sparge: p_CO₂ ≈ surface pressure during a pulse. Assumption.</t>
         </is>
@@ -6157,11 +6325,11 @@
           <t>mol/m³</t>
         </is>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="149">
         <f>H_CO2_T*p_CO2_sparge</f>
         <v/>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>Equilibrium dissolved CO₂ while sparging (mol/m³ = mM).</t>
         </is>
@@ -6183,10 +6351,10 @@
           <t>µM</t>
         </is>
       </c>
-      <c r="D34" s="47" t="n">
+      <c r="D34" s="46" t="n">
         <v>50</v>
       </c>
-      <c r="E34" s="48" t="inlineStr">
+      <c r="E34" s="47" t="inlineStr">
         <is>
           <t>RuBisCO Km(CO₂) ~ order 50 µM. Coarse — confirm.</t>
         </is>
@@ -6208,11 +6376,11 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D35" s="20">
+      <c r="D35" s="149">
         <f>CO2_diss*1000/Km_CO2</f>
         <v/>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>Dissolved CO₂ : RuBisCO Km. ≫1 = saturating (duty-averaged lower).</t>
         </is>
@@ -6234,10 +6402,10 @@
           <t>mol/L</t>
         </is>
       </c>
-      <c r="D36" s="43" t="n">
+      <c r="D36" s="42" t="n">
         <v>4.45e-07</v>
       </c>
-      <c r="E36" s="49" t="inlineStr">
+      <c r="E36" s="48" t="inlineStr">
         <is>
           <t>CO₂(aq)+H₂O ⇌ H⁺+HCO₃⁻, pKa1 6.35 (25 °C).</t>
         </is>
@@ -6259,11 +6427,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D37" s="20">
+      <c r="D37" s="149">
         <f>-LOG10(SQRT(Ka1_carb*(CO2_diss/1000)))</f>
         <v/>
       </c>
-      <c r="E37" s="48" t="inlineStr">
+      <c r="E37" s="47" t="inlineStr">
         <is>
           <t>Unbuffered worst case (pure water + CO₂) — lower bound only; the Sydow phosphate medium holds pH near setpoint.</t>
         </is>
@@ -6285,10 +6453,10 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D38" s="43" t="n">
+      <c r="D38" s="42" t="n">
         <v>7.8e-06</v>
       </c>
-      <c r="E38" s="49" t="inlineStr">
+      <c r="E38" s="48" t="inlineStr">
         <is>
           <t>Sander (2023). H₂ ~1.7× less soluble than O₂.</t>
         </is>
@@ -6310,10 +6478,10 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D39" s="43" t="n">
+      <c r="D39" s="42" t="n">
         <v>500</v>
       </c>
-      <c r="E39" s="49" t="inlineStr">
+      <c r="E39" s="48" t="inlineStr">
         <is>
           <t>Sander (2023): d ln(Hcp)/d(1/T) for H₂ (weak T-dependence).</t>
         </is>
@@ -6335,11 +6503,11 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="149">
         <f>H_H2ref*EXP(H_H2T*(1/T_K-1/T_ref))</f>
         <v/>
       </c>
-      <c r="E40" s="21" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>van 't Hoff to reactor T.</t>
         </is>
@@ -6361,11 +6529,11 @@
           <t>mol/m³</t>
         </is>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="149">
         <f>H_H2_T*P_atm</f>
         <v/>
       </c>
-      <c r="E41" s="21" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>Max dissolved H₂ at 1 atm — the cells' H₂ ceiling.</t>
         </is>
@@ -6387,11 +6555,11 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D42" s="20">
+      <c r="D42" s="149">
         <f>C_H2_sat*(V_charge/1000000)/rH2_gen*60</f>
         <v/>
       </c>
-      <c r="E42" s="21" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>Lag: dissolved H₂ saturates this fast unconsumed, then bubbles off (lost + explosive headspace). Mirrors the O₂ lag timescale.</t>
         </is>
@@ -6413,11 +6581,11 @@
           <t>1/h</t>
         </is>
       </c>
-      <c r="D43" s="20">
+      <c r="D43" s="149">
         <f>rH2_gen/(V_charge/1000000)/C_H2_sat</f>
         <v/>
       </c>
-      <c r="E43" s="48" t="inlineStr">
+      <c r="E43" s="47" t="inlineStr">
         <is>
           <t>H₂ evolved ÷ saturable pool. ≫1 → cells must consume in near-real-time or it escapes.</t>
         </is>
@@ -6439,16 +6607,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D44" s="20">
+      <c r="D44" s="149">
         <f>IF(H2_turnover&gt;1,"EXPLOSIVE","watch")</f>
         <v/>
       </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="E44" s="23" t="inlineStr">
         <is>
           <t>On when H₂ escapes faster than it dissolves (H2_turnover&gt;1) → explosive H₂+O₂ headspace (4–94% in O₂). On at any useful current — headspace venting is mandatory.</t>
         </is>
       </c>
-      <c r="F44" s="109" t="inlineStr">
+      <c r="F44" s="94" t="inlineStr">
         <is>
           <t>Pink no longer used here - red fill = hazard (H2 evolving faster than it dissolves), not a data gap.</t>
         </is>
@@ -6470,7 +6638,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="D45" s="75">
+      <c r="D45" s="156">
         <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,2,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,2,FALSE),NA())</f>
         <v/>
       </c>
@@ -6491,7 +6659,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="D46" s="72">
+      <c r="D46" s="150">
         <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE),NA())</f>
         <v/>
       </c>
@@ -6512,7 +6680,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="D47" s="72">
+      <c r="D47" s="150">
         <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE),NA())</f>
         <v/>
       </c>
@@ -6533,51 +6701,51 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="D48" s="72">
+      <c r="D48" s="150">
         <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,5,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,5,FALSE),NA())</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="68" t="n"/>
-      <c r="C49" s="68" t="n"/>
-      <c r="D49" s="68" t="n"/>
-      <c r="E49" s="68" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
+      <c r="D49" s="62" t="n"/>
+      <c r="E49" s="62" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="67" t="inlineStr">
+      <c r="A50" s="61" t="inlineStr">
         <is>
           <t>HOB LOOKUP  (dissolved O₂ thresholds, mg/L)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="63" t="inlineStr">
+      <c r="A51" s="57" t="inlineStr">
         <is>
           <t>Organism</t>
         </is>
       </c>
-      <c r="B51" s="63" t="inlineStr">
+      <c r="B51" s="57" t="inlineStr">
         <is>
           <t>minimum DO</t>
         </is>
       </c>
-      <c r="C51" s="63" t="inlineStr">
+      <c r="C51" s="57" t="inlineStr">
         <is>
           <t>optimum DO</t>
         </is>
       </c>
-      <c r="D51" s="63" t="inlineStr">
+      <c r="D51" s="57" t="inlineStr">
         <is>
           <t>impairment DO</t>
         </is>
       </c>
-      <c r="E51" s="63" t="inlineStr">
+      <c r="E51" s="57" t="inlineStr">
         <is>
           <t>toxic DO</t>
         </is>
       </c>
-      <c r="F51" s="63" t="inlineStr">
+      <c r="F51" s="57" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -6589,7 +6757,7 @@
           <t>Cupriavidus necator</t>
         </is>
       </c>
-      <c r="B52" s="68" t="inlineStr">
+      <c r="B52" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -6603,7 +6771,7 @@
       <c r="E52" t="n">
         <v>11.5</v>
       </c>
-      <c r="F52" s="66" t="inlineStr">
+      <c r="F52" s="60" t="inlineStr">
         <is>
           <t>11.5 = Wilde &amp; Schlegel 1982 literature datum; model's operative O2 ceiling is computed via Henry (~10.7 mg/L at 30C) - the two differ slightly</t>
         </is>
@@ -6615,17 +6783,17 @@
           <t>Xanthobacter autotrophicus</t>
         </is>
       </c>
-      <c r="B53" s="68" t="inlineStr">
+      <c r="B53" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C53" s="68" t="inlineStr">
+      <c r="C53" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="D53" s="68" t="inlineStr">
+      <c r="D53" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -6645,22 +6813,22 @@
           <t>Xanthobacter flavus</t>
         </is>
       </c>
-      <c r="B54" s="68" t="inlineStr">
+      <c r="B54" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C54" s="68" t="inlineStr">
+      <c r="C54" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="D54" s="68" t="inlineStr">
+      <c r="D54" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="E54" s="68" t="inlineStr">
+      <c r="E54" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -6677,22 +6845,22 @@
           <t>Xanthobacter tagetidis</t>
         </is>
       </c>
-      <c r="B55" s="68" t="inlineStr">
+      <c r="B55" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C55" s="68" t="inlineStr">
+      <c r="C55" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="D55" s="68" t="inlineStr">
+      <c r="D55" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="E55" s="68" t="inlineStr">
+      <c r="E55" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -6709,22 +6877,22 @@
           <t>Cupriavidus metallidurans</t>
         </is>
       </c>
-      <c r="B56" s="68" t="inlineStr">
+      <c r="B56" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C56" s="68" t="inlineStr">
+      <c r="C56" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="D56" s="68" t="inlineStr">
+      <c r="D56" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="E56" s="68" t="inlineStr">
+      <c r="E56" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -6741,22 +6909,22 @@
           <t>UdG (mixed)</t>
         </is>
       </c>
-      <c r="B57" s="68" t="inlineStr">
+      <c r="B57" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C57" s="68" t="inlineStr">
+      <c r="C57" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="D57" s="68" t="inlineStr">
+      <c r="D57" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="E57" s="68" t="inlineStr">
+      <c r="E57" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -6768,37 +6936,37 @@
       </c>
     </row>
     <row r="58">
-      <c r="D58" s="75" t="n"/>
+      <c r="D58" s="67" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="67" t="inlineStr">
+      <c r="A59" s="61" t="inlineStr">
         <is>
           <t>MEDIA LOOKUP</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="63" t="inlineStr">
+      <c r="A60" s="57" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="B60" s="63" t="inlineStr">
+      <c r="B60" s="57" t="inlineStr">
         <is>
           <t>buffer</t>
         </is>
       </c>
-      <c r="C60" s="63" t="inlineStr">
+      <c r="C60" s="57" t="inlineStr">
         <is>
           <t>buffer conc (mM)</t>
         </is>
       </c>
-      <c r="D60" s="63" t="inlineStr">
+      <c r="D60" s="57" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="E60" s="63" t="inlineStr">
+      <c r="E60" s="57" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -6815,7 +6983,7 @@
           <t>phosphate</t>
         </is>
       </c>
-      <c r="C61" s="68" t="inlineStr">
+      <c r="C61" s="62" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -6845,12 +7013,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="8">
       <formula>"EXPLOSIVE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D44">
-    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("EXPLOSIVE",D44))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6875,34 +7043,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="52" t="inlineStr">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>MASS TRANSFER</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="53" t="inlineStr">
+      <c r="A2" s="52" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B2" s="53" t="inlineStr">
+      <c r="B2" s="52" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C2" s="53" t="inlineStr">
+      <c r="C2" s="52" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D2" s="53" t="inlineStr">
+      <c r="D2" s="52" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E2" s="53" t="inlineStr">
+      <c r="E2" s="52" t="inlineStr">
         <is>
           <t>Source / assumption</t>
         </is>
@@ -6912,18 +7080,18 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="6" t="n"/>
       <c r="C3" s="7" t="n"/>
-      <c r="D3" s="28" t="n"/>
+      <c r="D3" s="27" t="n"/>
       <c r="E3" s="8" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>IMPORTS (from other tabs)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="7" t="n"/>
-      <c r="D4" s="28" t="n"/>
+      <c r="D4" s="27" t="n"/>
       <c r="E4" s="8" t="n"/>
     </row>
     <row r="5">
@@ -6942,15 +7110,15 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D5" s="136">
+      <c r="D5" s="157">
         <f>Geometry!$D$52</f>
         <v/>
       </c>
-      <c r="E5" s="137">
+      <c r="E5" s="119">
         <f>HYPERLINK("#Geometry!D52","→ Geometry")</f>
         <v/>
       </c>
-      <c r="F5" s="109" t="inlineStr">
+      <c r="F5" s="94" t="inlineStr">
         <is>
           <t>Magnetic stir bar. Pioreactor max 20 mm; confirm the supplied bar's length. Input.</t>
         </is>
@@ -6972,11 +7140,11 @@
           <t>mol/m³</t>
         </is>
       </c>
-      <c r="D6" s="119">
+      <c r="D6" s="138">
         <f>Biology!$D$27</f>
         <v/>
       </c>
-      <c r="E6" s="112">
+      <c r="E6" s="97">
         <f>HYPERLINK("#Biology!D27","→ Biology")</f>
         <v/>
       </c>
@@ -6997,11 +7165,11 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D7" s="119">
+      <c r="D7" s="138">
         <f>Biology!$D$26</f>
         <v/>
       </c>
-      <c r="E7" s="112">
+      <c r="E7" s="97">
         <f>HYPERLINK("#Biology!D26","→ Biology")</f>
         <v/>
       </c>
@@ -7022,11 +7190,11 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D8" s="119">
+      <c r="D8" s="138">
         <f>Biology!$D$18</f>
         <v/>
       </c>
-      <c r="E8" s="112">
+      <c r="E8" s="97">
         <f>HYPERLINK("#Biology!D18","→ Biology")</f>
         <v/>
       </c>
@@ -7047,11 +7215,11 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D9" s="119">
+      <c r="D9" s="138">
         <f>Biology!$D$19</f>
         <v/>
       </c>
-      <c r="E9" s="112">
+      <c r="E9" s="97">
         <f>HYPERLINK("#Biology!D19","→ Biology")</f>
         <v/>
       </c>
@@ -7072,11 +7240,11 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D10" s="119">
+      <c r="D10" s="138">
         <f>Biology!$D$15</f>
         <v/>
       </c>
-      <c r="E10" s="112">
+      <c r="E10" s="97">
         <f>HYPERLINK("#Biology!D15","→ Biology")</f>
         <v/>
       </c>
@@ -7097,11 +7265,11 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D11" s="119">
+      <c r="D11" s="138">
         <f>Biology!$D$16</f>
         <v/>
       </c>
-      <c r="E11" s="112">
+      <c r="E11" s="97">
         <f>HYPERLINK("#Biology!D16","→ Biology")</f>
         <v/>
       </c>
@@ -7122,11 +7290,11 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D12" s="119">
+      <c r="D12" s="138">
         <f>Biology!$D$24</f>
         <v/>
       </c>
-      <c r="E12" s="112">
+      <c r="E12" s="97">
         <f>HYPERLINK("#Biology!D24","→ Biology")</f>
         <v/>
       </c>
@@ -7147,11 +7315,11 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D13" s="117">
+      <c r="D13" s="139">
         <f>Electrochemistry!$D$29</f>
         <v/>
       </c>
-      <c r="E13" s="112">
+      <c r="E13" s="97">
         <f>HYPERLINK("#Electrochemistry!D29","→ Electrochemistry")</f>
         <v/>
       </c>
@@ -7172,11 +7340,11 @@
           <t>mm²</t>
         </is>
       </c>
-      <c r="D14" s="113">
+      <c r="D14" s="136">
         <f>Geometry!$D$44</f>
         <v/>
       </c>
-      <c r="E14" s="112">
+      <c r="E14" s="97">
         <f>HYPERLINK("#Geometry!D44","→ Geometry")</f>
         <v/>
       </c>
@@ -7197,11 +7365,11 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D15" s="113">
+      <c r="D15" s="136">
         <f>Geometry!$D$20</f>
         <v/>
       </c>
-      <c r="E15" s="112">
+      <c r="E15" s="97">
         <f>HYPERLINK("#Geometry!D20","→ Geometry")</f>
         <v/>
       </c>
@@ -7222,11 +7390,11 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D16" s="113">
+      <c r="D16" s="136">
         <f>Geometry!$D$41</f>
         <v/>
       </c>
-      <c r="E16" s="112">
+      <c r="E16" s="97">
         <f>HYPERLINK("#Geometry!D41","→ Geometry")</f>
         <v/>
       </c>
@@ -7247,11 +7415,11 @@
           <t>mm²</t>
         </is>
       </c>
-      <c r="D17" s="113">
+      <c r="D17" s="136">
         <f>Geometry!$D$21</f>
         <v/>
       </c>
-      <c r="E17" s="112">
+      <c r="E17" s="97">
         <f>HYPERLINK("#Geometry!D21","→ Geometry")</f>
         <v/>
       </c>
@@ -7272,11 +7440,11 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D18" s="113">
+      <c r="D18" s="136">
         <f>Geometry!$D$31</f>
         <v/>
       </c>
-      <c r="E18" s="112">
+      <c r="E18" s="97">
         <f>HYPERLINK("#Geometry!D31","→ Geometry")</f>
         <v/>
       </c>
@@ -7297,11 +7465,11 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D19" s="113">
+      <c r="D19" s="136">
         <f>Geometry!$D$49</f>
         <v/>
       </c>
-      <c r="E19" s="112">
+      <c r="E19" s="97">
         <f>HYPERLINK("#Geometry!D49","→ Geometry")</f>
         <v/>
       </c>
@@ -7322,11 +7490,11 @@
           <t>0-5</t>
         </is>
       </c>
-      <c r="D20" s="138">
+      <c r="D20" s="139">
         <f>Electrochemistry!$D$32</f>
         <v/>
       </c>
-      <c r="E20" s="112">
+      <c r="E20" s="97">
         <f>HYPERLINK("#Electrochemistry!D32","→ Electrochemistry")</f>
         <v/>
       </c>
@@ -7351,7 +7519,7 @@
         <f>Electrochemistry!$D$31</f>
         <v/>
       </c>
-      <c r="E21" s="112">
+      <c r="E21" s="97">
         <f>HYPERLINK("#Electrochemistry!D31","→ Electrochemistry")</f>
         <v/>
       </c>
@@ -7367,11 +7535,11 @@
           <t>DO_opt</t>
         </is>
       </c>
-      <c r="D22" s="116">
+      <c r="D22" s="138">
         <f>Biology!$D$46</f>
         <v/>
       </c>
-      <c r="E22" s="112">
+      <c r="E22" s="97">
         <f>HYPERLINK("#Biology!D46","→ Biology")</f>
         <v/>
       </c>
@@ -7387,11 +7555,11 @@
           <t>DO_impair</t>
         </is>
       </c>
-      <c r="D23" s="116">
+      <c r="D23" s="138">
         <f>Biology!$D$47</f>
         <v/>
       </c>
-      <c r="E23" s="112">
+      <c r="E23" s="97">
         <f>HYPERLINK("#Biology!D47","→ Biology")</f>
         <v/>
       </c>
@@ -7407,11 +7575,11 @@
           <t>DO_toxic</t>
         </is>
       </c>
-      <c r="D24" s="116">
+      <c r="D24" s="138">
         <f>Biology!$D$48</f>
         <v/>
       </c>
-      <c r="E24" s="112">
+      <c r="E24" s="97">
         <f>HYPERLINK("#Biology!D48","→ Biology")</f>
         <v/>
       </c>
@@ -7427,11 +7595,11 @@
           <t>DO_min</t>
         </is>
       </c>
-      <c r="D25" s="116">
+      <c r="D25" s="138">
         <f>Biology!$D$45</f>
         <v/>
       </c>
-      <c r="E25" s="112">
+      <c r="E25" s="97">
         <f>HYPERLINK("#Biology!D45","→ Biology")</f>
         <v/>
       </c>
@@ -7440,7 +7608,7 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="35" t="n"/>
+      <c r="D26" s="34" t="n"/>
       <c r="E26" s="18" t="n"/>
     </row>
     <row r="27">
@@ -7459,7 +7627,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D27" s="28" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>Tube</t>
         </is>
@@ -7486,7 +7654,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Sintered</t>
         </is>
@@ -7513,7 +7681,7 @@
           <t>N/m</t>
         </is>
       </c>
-      <c r="D29" s="44" t="n">
+      <c r="D29" s="43" t="n">
         <v>0.0712</v>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -7538,7 +7706,7 @@
           <t>kg/m³</t>
         </is>
       </c>
-      <c r="D30" s="36" t="n">
+      <c r="D30" s="35" t="n">
         <v>995.65</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -7563,7 +7731,7 @@
           <t>m/s²</t>
         </is>
       </c>
-      <c r="D31" s="39" t="n">
+      <c r="D31" s="38" t="n">
         <v>9.806649999999999</v>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -7588,7 +7756,7 @@
           <t>m²/s</t>
         </is>
       </c>
-      <c r="D32" s="40" t="n">
+      <c r="D32" s="39" t="n">
         <v>2.249e-09</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -7613,7 +7781,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D33" s="40" t="n">
+      <c r="D33" s="39" t="n">
         <v>205</v>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -7638,7 +7806,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D34" s="40" t="n">
+      <c r="D34" s="39" t="n">
         <v>130</v>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -7663,7 +7831,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D35" s="40" t="n">
+      <c r="D35" s="39" t="n">
         <v>70</v>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -7688,7 +7856,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D36" s="40" t="n">
+      <c r="D36" s="39" t="n">
         <v>28</v>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -7713,7 +7881,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D37" s="40" t="n">
+      <c r="D37" s="39" t="n">
         <v>13</v>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -7738,7 +7906,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D38" s="37" t="n">
+      <c r="D38" s="36" t="n">
         <v>1.3</v>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -7763,7 +7931,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D39" s="107">
+      <c r="D39" s="158">
         <f>CHOOSE(por_grade+1,por0_um,por1_um,por2_um,por3_um,por4_um,por5_um)/1000000</f>
         <v/>
       </c>
@@ -7789,7 +7957,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D40" s="107">
+      <c r="D40" s="158">
         <f>spg_ID/1000</f>
         <v/>
       </c>
@@ -7815,7 +7983,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D41" s="107">
+      <c r="D41" s="158">
         <f>IF(sparger=spg_name_1,tube_d_m,IF(sparger=spg_name_2,por_pore,NA()))</f>
         <v/>
       </c>
@@ -7841,7 +8009,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D42" s="20">
+      <c r="D42" s="149">
         <f>(6*d_orifice*sigma/(rho_L*g_const))^(1/3)</f>
         <v/>
       </c>
@@ -7867,7 +8035,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="146">
         <f>d_bubble*1000</f>
         <v/>
       </c>
@@ -7889,7 +8057,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D44" s="36" t="n">
+      <c r="D44" s="35" t="n">
         <v>2.14</v>
       </c>
       <c r="E44" s="18" t="inlineStr">
@@ -7914,7 +8082,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D45" s="46" t="n">
+      <c r="D45" s="45" t="n">
         <v>0.505</v>
       </c>
       <c r="E45" s="18" t="inlineStr">
@@ -7939,7 +8107,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D46" s="35">
+      <c r="D46" s="147">
         <f>SQRT(mend_a*sigma/(rho_L*d_bubble)+mend_b*g_const*d_bubble)</f>
         <v/>
       </c>
@@ -7965,7 +8133,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D47" s="20">
+      <c r="D47" s="149">
         <f>(Q_CO2/1000000/60)/(A_x/1000000)</f>
         <v/>
       </c>
@@ -7991,7 +8159,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D48" s="20">
+      <c r="D48" s="149">
         <f>u_sg/u_rise</f>
         <v/>
       </c>
@@ -8017,7 +8185,7 @@
           <t>1/m</t>
         </is>
       </c>
-      <c r="D49" s="30">
+      <c r="D49" s="143">
         <f>6*holdup/d_bubble</f>
         <v/>
       </c>
@@ -8043,7 +8211,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D50" s="35">
+      <c r="D50" s="147">
         <f>d_bubble/u_rise</f>
         <v/>
       </c>
@@ -8069,7 +8237,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D51" s="20">
+      <c r="D51" s="149">
         <f>2*SQRT(D_O2/(PI()*t_contact))</f>
         <v/>
       </c>
@@ -8095,7 +8263,7 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D52" s="20">
+      <c r="D52" s="149">
         <f>kL*a_int</f>
         <v/>
       </c>
@@ -8121,11 +8289,11 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D53" s="42">
+      <c r="D53" s="155">
         <f>kLa_sparge*duty</f>
         <v/>
       </c>
-      <c r="E53" s="98" t="inlineStr">
+      <c r="E53" s="86" t="inlineStr">
         <is>
           <t>Sparge-on regime only; not meaningful in the surface-strip-dominated default</t>
         </is>
@@ -8147,7 +8315,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D54" s="20">
+      <c r="D54" s="149">
         <f>IF(d_bubble&lt;0.001,0,kLa_sparge*(V_charge/1000000)*O2_ceil_C*3600)</f>
         <v/>
       </c>
@@ -8173,7 +8341,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D55" s="20">
+      <c r="D55" s="149">
         <f>strip_sparge*duty</f>
         <v/>
       </c>
@@ -8199,7 +8367,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D56" s="34">
+      <c r="D56" s="146">
         <f>IF(O2_excess&gt;0,strip_avg/O2_excess,NA())</f>
         <v/>
       </c>
@@ -8225,7 +8393,7 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D57" s="20">
+      <c r="D57" s="149">
         <f>IF(O2_excess&gt;0,O2_excess/3600/((V_charge/1000000)*O2_ceil_C),NA())</f>
         <v/>
       </c>
@@ -8251,7 +8419,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D58" s="32" t="n">
+      <c r="D58" s="31" t="n">
         <v>0.05</v>
       </c>
       <c r="E58" s="18" t="inlineStr">
@@ -8276,7 +8444,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D59" s="41">
+      <c r="D59" s="152">
         <f>IF(u_sg&gt;u_g_max,"RISK","OK")</f>
         <v/>
       </c>
@@ -8302,11 +8470,11 @@
           <t>kg/m³</t>
         </is>
       </c>
-      <c r="D60" s="20">
+      <c r="D60" s="149">
         <f>P_atm*(M_CO2/1000)/(R_gas*T_K)</f>
         <v/>
       </c>
-      <c r="E60" s="21" t="inlineStr">
+      <c r="E60" s="20" t="inlineStr">
         <is>
           <t>Ideal gas at surface conditions; for the orifice Weber number.</t>
         </is>
@@ -8328,10 +8496,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D61" s="22" t="n">
+      <c r="D61" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="24" t="inlineStr">
+      <c r="E61" s="23" t="inlineStr">
         <is>
           <t>Tube = 1. Sinter pore count unknown; 1 = worst case. DATA GAP.</t>
         </is>
@@ -8353,11 +8521,11 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D62" s="20">
+      <c r="D62" s="149">
         <f>(Q_CO2/1000000/60)/(n_pores_active*(PI()/4*d_orifice^2))</f>
         <v/>
       </c>
-      <c r="E62" s="99" t="inlineStr">
+      <c r="E62" s="87" t="inlineStr">
         <is>
           <t>Sparge-on regime only; not meaningful in the surface-strip-dominated default</t>
         </is>
@@ -8379,11 +8547,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D63" s="20">
+      <c r="D63" s="149">
         <f>rho_CO2*v_orifice^2*d_orifice/sigma</f>
         <v/>
       </c>
-      <c r="E63" s="99" t="inlineStr">
+      <c r="E63" s="87" t="inlineStr">
         <is>
           <t>Sparge-on regime only; not meaningful in the surface-strip-dominated default</t>
         </is>
@@ -8405,11 +8573,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D64" s="20">
+      <c r="D64" s="149">
         <f>IF(d_bubble&lt;0.001,"Sinter OOR – add fine-bubble model",IF(We_orifice&lt;2,"Static","Dynamic"))</f>
         <v/>
       </c>
-      <c r="E64" s="21" t="inlineStr">
+      <c r="E64" s="20" t="inlineStr">
         <is>
           <t>Tate's law assumes quasi-static detachment (We&lt;~2). 'Sinter OOR' = sub-mm bubble; the fine-sinter model isn't built yet.</t>
         </is>
@@ -8431,11 +8599,11 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D65" s="20">
+      <c r="D65" s="149">
         <f>O2_ceil_C*(V_charge/1000000)/O2_excess*60</f>
         <v/>
       </c>
-      <c r="E65" s="21" t="inlineStr">
+      <c r="E65" s="20" t="inlineStr">
         <is>
           <t>Minutes to reach the O₂ ceiling from ~0 with no removal (steady, etaF=1) — the O₂ timescale.</t>
         </is>
@@ -8457,11 +8625,11 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D66" s="20">
+      <c r="D66" s="149">
         <f>IF(O2_excess-strip_avg&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_excess-strip_avg)*60,9999)</f>
         <v/>
       </c>
-      <c r="E66" s="21" t="inlineStr">
+      <c r="E66" s="20" t="inlineStr">
         <is>
           <t>As above, crediting time-averaged bubble strip (≈unchanged → bubbles aren't the mechanism). 9999 = cleared.</t>
         </is>
@@ -8483,11 +8651,11 @@
           <t>1/min</t>
         </is>
       </c>
-      <c r="D67" s="84">
-        <f>Summary!$D$8</f>
-        <v/>
-      </c>
-      <c r="E67" s="23" t="inlineStr">
+      <c r="D67" s="159">
+        <f>Summary!$D$7</f>
+        <v/>
+      </c>
+      <c r="E67" s="22" t="inlineStr">
         <is>
           <t>Pioreactor stir setpoint. RPM floor ~125 (stalls below). Input/confirm.</t>
         </is>
@@ -8509,11 +8677,11 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D68" s="20">
+      <c r="D68" s="149">
         <f>PI()*(stir_len/1000)*stir_rpm/60</f>
         <v/>
       </c>
-      <c r="E68" s="21" t="inlineStr">
+      <c r="E68" s="20" t="inlineStr">
         <is>
           <t>π·d·rpm/60.</t>
         </is>
@@ -8535,11 +8703,11 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D69" s="20">
+      <c r="D69" s="149">
         <f>tip_speed/(vial_ID/1000)</f>
         <v/>
       </c>
-      <c r="E69" s="48" t="inlineStr">
+      <c r="E69" s="47" t="inlineStr">
         <is>
           <t>Surface renewal ≈ tip speed / vial ID. Coarse proxy.</t>
         </is>
@@ -8561,11 +8729,11 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D70" s="20">
+      <c r="D70" s="149">
         <f>2*SQRT(D_O2*s_renew/PI())</f>
         <v/>
       </c>
-      <c r="E70" s="48" t="inlineStr">
+      <c r="E70" s="47" t="inlineStr">
         <is>
           <t>Danckwerts surface-renewal estimate — coarse; measure by gassing-out (§15).</t>
         </is>
@@ -8587,11 +8755,11 @@
           <t>1/m</t>
         </is>
       </c>
-      <c r="D71" s="20">
+      <c r="D71" s="149">
         <f>interface_A/V_charge</f>
         <v/>
       </c>
-      <c r="E71" s="21" t="inlineStr">
+      <c r="E71" s="20" t="inlineStr">
         <is>
           <t>Free-surface area / liquid volume (mm²/mL = 1/m); uses interface_A (§1B).</t>
         </is>
@@ -8613,11 +8781,11 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D72" s="20">
+      <c r="D72" s="149">
         <f>kL_surf*a_surf</f>
         <v/>
       </c>
-      <c r="E72" s="48" t="inlineStr">
+      <c r="E72" s="47" t="inlineStr">
         <is>
           <t>kL_surf × a_surf.</t>
         </is>
@@ -8639,11 +8807,11 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D73" s="20">
+      <c r="D73" s="149">
         <f>kLa_surf_used*(V_charge/1000000)*O2_ceil_C*3600</f>
         <v/>
       </c>
-      <c r="E73" s="48" t="inlineStr">
+      <c r="E73" s="47" t="inlineStr">
         <is>
           <t>O₂ removed across the stirred surface at ceiling driving force, headspace ~O₂-free. Best case.</t>
         </is>
@@ -8665,11 +8833,11 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D74" s="20">
+      <c r="D74" s="149">
         <f>IF(O2_excess&gt;0,surf_strip/O2_excess,NA())</f>
         <v/>
       </c>
-      <c r="E74" s="48" t="inlineStr">
+      <c r="E74" s="47" t="inlineStr">
         <is>
           <t>Surface strip : surplus. Coarse (kL_surf). ≫ bubble path — the dominant O₂ route.</t>
         </is>
@@ -8691,11 +8859,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D75" s="20">
+      <c r="D75" s="149">
         <f>IF(CO2_supply&gt;0,O2_excess/CO2_supply,NA())</f>
         <v/>
       </c>
-      <c r="E75" s="21" t="inlineStr">
+      <c r="E75" s="20" t="inlineStr">
         <is>
           <t>Headspace O₂ fraction at which the vented CO₂ carries the surplus out. kL-independent.</t>
         </is>
@@ -8717,11 +8885,11 @@
           <t>µM</t>
         </is>
       </c>
-      <c r="D76" s="20">
+      <c r="D76" s="149">
         <f>H_O2_T*y_O2_vent*P_atm*1000</f>
         <v/>
       </c>
-      <c r="E76" s="21" t="inlineStr">
+      <c r="E76" s="20" t="inlineStr">
         <is>
           <t>Dissolved O₂ matching that headspace fraction. ≪ ceiling → vent-feasible.</t>
         </is>
@@ -8743,11 +8911,11 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D77" s="20">
+      <c r="D77" s="149">
         <f>headspace_V/(Q_CO2*duty)</f>
         <v/>
       </c>
-      <c r="E77" s="21" t="inlineStr">
+      <c r="E77" s="20" t="inlineStr">
         <is>
           <t>Avg CO₂ flow to displace one headspace volume.</t>
         </is>
@@ -8769,11 +8937,11 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D78" s="20">
+      <c r="D78" s="149">
         <f>IF(O2_excess&gt;0,(strip_avg+surf_strip)/O2_excess,NA())</f>
         <v/>
       </c>
-      <c r="E78" s="100" t="inlineStr">
+      <c r="E78" s="88" t="inlineStr">
         <is>
           <t>Upper bound: surface + sparge O2 sinks are in series (liquid-&gt;headspace-&gt;vent), not strictly additive</t>
         </is>
@@ -8795,11 +8963,11 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D79" s="20">
+      <c r="D79" s="149">
         <f>O2_ceil_C*(V_charge/1000000)/O2_net_gen*60</f>
         <v/>
       </c>
-      <c r="E79" s="21" t="inlineStr">
+      <c r="E79" s="20" t="inlineStr">
         <is>
           <t>Lag/establishment: no biological O₂ uptake yet, so the full net O₂ accumulates. Worst case.</t>
         </is>
@@ -8821,11 +8989,11 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D80" s="20">
+      <c r="D80" s="149">
         <f>IF(O2_net_gen-strip_avg-surf_strip&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_net_gen-strip_avg-surf_strip)*60,9999)</f>
         <v/>
       </c>
-      <c r="E80" s="48" t="inlineStr">
+      <c r="E80" s="47" t="inlineStr">
         <is>
           <t>LAG-with-removal partner to t_O2_ceiling_lag: cells not yet consuming, so removal (bubble + surface) must offset the full net electrolytic O₂ (O2_net_gen, which already nets the cathodic sink), not the steady surplus. 9999 = removal holds the ceiling (no finite time).</t>
         </is>
@@ -8847,12 +9015,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D81" s="47" t="inlineStr">
+      <c r="D81" s="46" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="E81" s="23" t="inlineStr">
+      <c r="E81" s="22" t="inlineStr">
         <is>
           <t>Manual = use the values you type below; Optimal = the model computes &amp; applies the optimum. Dropdown.</t>
         </is>
@@ -8874,10 +9042,10 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D82" s="47" t="n">
+      <c r="D82" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="E82" s="23" t="inlineStr">
+      <c r="E82" s="22" t="inlineStr">
         <is>
           <t>Your pulse length, used when sched_mode=Manual.</t>
         </is>
@@ -8899,10 +9067,10 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D83" s="47" t="n">
+      <c r="D83" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="E83" s="23" t="inlineStr">
+      <c r="E83" s="22" t="inlineStr">
         <is>
           <t>Your interval, used when sched_mode=Manual.</t>
         </is>
@@ -8924,11 +9092,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D84" s="76">
+      <c r="D84" s="160">
         <f>IF(AND(ISNUMBER(DO_opt),ISNUMBER(DO_toxic)),DO_opt/DO_toxic,0.5)</f>
         <v/>
       </c>
-      <c r="E84" s="23" t="inlineStr">
+      <c r="E84" s="22" t="inlineStr">
         <is>
           <t>Hold DO at ≤ this × the inhibition ceiling. Lower = safer O₂ margin → needs more flushing. Input.</t>
         </is>
@@ -8950,10 +9118,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D85" s="47" t="n">
+      <c r="D85" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E85" s="23" t="inlineStr">
+      <c r="E85" s="22" t="inlineStr">
         <is>
           <t>Required CO₂ supply : fixation demand. Input.</t>
         </is>
@@ -8975,11 +9143,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D86" s="20">
+      <c r="D86" s="149">
         <f>carbon_margin_min*CO2_cons/(nCO2_rate*3600)</f>
         <v/>
       </c>
-      <c r="E86" s="21" t="inlineStr">
+      <c r="E86" s="20" t="inlineStr">
         <is>
           <t>Duty needed so CO₂ supply ≥ margin × fixation demand.</t>
         </is>
@@ -9001,11 +9169,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D87" s="20">
+      <c r="D87" s="149">
         <f>O2_net_gen/(target_DO_frac*(O2_ceil_Pa/P_atm))/(nCO2_rate*3600)</f>
         <v/>
       </c>
-      <c r="E87" s="21" t="inlineStr">
+      <c r="E87" s="20" t="inlineStr">
         <is>
           <t>Duty so the vented CO₂ throughput carries the worst-case (lag, no uptake) net O₂ out at ≤ target DO. Usually the binding floor.</t>
         </is>
@@ -9027,11 +9195,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D88" s="20">
+      <c r="D88" s="149">
         <f>MAX(duty_carbon,duty_O2vent)</f>
         <v/>
       </c>
-      <c r="E88" s="21" t="inlineStr">
+      <c r="E88" s="20" t="inlineStr">
         <is>
           <t>Least feasible CO₂ (binding of the two floors). O₂-venting binds, not pH (buffer holds pH; over-dose limited by pCO₂ lag).</t>
         </is>
@@ -9053,11 +9221,11 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D89" s="20">
+      <c r="D89" s="149">
         <f>target_DO_frac*t_O2_ceiling_lag</f>
         <v/>
       </c>
-      <c r="E89" s="21" t="inlineStr">
+      <c r="E89" s="20" t="inlineStr">
         <is>
           <t>Pulses must be frequent enough that DO doesn't spike past target between flushes (lag worst-case).</t>
         </is>
@@ -9079,11 +9247,11 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D90" s="50">
+      <c r="D90" s="161">
         <f>MAX(pulse_floor,flush_factor*headspace_V/(Q_CO2/60))</f>
         <v/>
       </c>
-      <c r="E90" s="51" t="inlineStr">
+      <c r="E90" s="50" t="inlineStr">
         <is>
           <t>ANSWER. Shortest reliable pulse → most frequent, smoothest DO, best OD-read windows.</t>
         </is>
@@ -9105,11 +9273,11 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D91" s="50">
+      <c r="D91" s="161">
         <f>MIN(spg_dur_opt/(60*duty_opt),spg_int_max)</f>
         <v/>
       </c>
-      <c r="E91" s="51" t="inlineStr">
+      <c r="E91" s="50" t="inlineStr">
         <is>
           <t>ANSWER. From optimal duty at the floor pulse, capped by the O₂-flush frequency limit. Set sched_mode=Optimal to apply.</t>
         </is>
@@ -9131,11 +9299,11 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D92" s="20">
+      <c r="D92" s="149">
         <f>spg_int_opt*60</f>
         <v/>
       </c>
-      <c r="E92" s="51" t="inlineStr">
+      <c r="E92" s="50" t="inlineStr">
         <is>
           <t>Convenience: interval in seconds.</t>
         </is>
@@ -9157,11 +9325,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D93" s="20">
+      <c r="D93" s="149">
         <f>spg_dur_opt/(spg_int_opt*60)</f>
         <v/>
       </c>
-      <c r="E93" s="21" t="inlineStr">
+      <c r="E93" s="20" t="inlineStr">
         <is>
           <t>Achieved duty at the optimum (= duty_opt unless the flush-frequency cap binds, raising it).</t>
         </is>
@@ -9183,11 +9351,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D94" s="20">
+      <c r="D94" s="149">
         <f>IF(spg_int_opt&lt;spg_dur_opt/(60*duty_opt)-0.0001,"O2-FREQ",IF(duty_O2vent&gt;=duty_carbon,"O2-VENT","CARBON"))</f>
         <v/>
       </c>
-      <c r="E94" s="21" t="inlineStr">
+      <c r="E94" s="20" t="inlineStr">
         <is>
           <t>Which limit sets the schedule: O2-VENT (O₂ removal), O2-FREQ (flush frequency), or CARBON.</t>
         </is>
@@ -9209,11 +9377,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D95" s="20">
+      <c r="D95" s="149">
         <f>IF(spg_int_opt*60-spg_dur_opt&gt;=5,"OK","TIGHT")</f>
         <v/>
       </c>
-      <c r="E95" s="21" t="inlineStr">
+      <c r="E95" s="20" t="inlineStr">
         <is>
           <t>≥5 s gap between pulses for an OD read. Can't measure OD while sparging.</t>
         </is>
@@ -9235,11 +9403,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D96" s="20">
+      <c r="D96" s="149">
         <f>"see note →"</f>
         <v/>
       </c>
-      <c r="E96" s="48" t="inlineStr">
+      <c r="E96" s="47" t="inlineStr">
         <is>
           <t>Constraint-proxy optimiser, not a fitted growth model — no validated μ(O₂,pH,CO₂) or lag kinetics exist for this system. Gives the lag-minimising direction, not an exact optimum; bounded by etaF, surface kL and the unbuffered-pH simplification. Validate empirically.</t>
         </is>
@@ -9261,10 +9429,10 @@
           <t>1/h</t>
         </is>
       </c>
-      <c r="D97" s="47" t="n">
+      <c r="D97" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="E97" s="48" t="inlineStr">
+      <c r="E97" s="47" t="inlineStr">
         <is>
           <t>Measured surface kLa (gassing-out). 0 = use the §11 estimate. kLa = slope of −LN(1−DO/DO_sat) vs time.</t>
         </is>
@@ -9286,11 +9454,11 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D98" s="20">
+      <c r="D98" s="149">
         <f>IF(kLa_meas&gt;0,kLa_meas/3600,kLa_surf)</f>
         <v/>
       </c>
-      <c r="E98" s="21" t="inlineStr">
+      <c r="E98" s="20" t="inlineStr">
         <is>
           <t>What §11 actually uses: the measured value if entered, otherwise the theoretical estimate. Swap estimate→truth here once measured.</t>
         </is>
@@ -9312,7 +9480,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D99" s="87">
+      <c r="D99" s="162">
         <f>min_sparge_cal</f>
         <v/>
       </c>
@@ -9338,7 +9506,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D100" s="87">
+      <c r="D100" s="162">
         <f>CO2_pulse*pulses_h</f>
         <v/>
       </c>
@@ -9364,7 +9532,7 @@
           <t>J/mol/K</t>
         </is>
       </c>
-      <c r="D101" s="88" t="n">
+      <c r="D101" s="78" t="n">
         <v>8.314462618</v>
       </c>
       <c r="E101" t="inlineStr">
@@ -9389,7 +9557,7 @@
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D102" s="87">
+      <c r="D102" s="162">
         <f>IF(has_cal&gt;0,flowrate_cal*60,NA())</f>
         <v/>
       </c>
@@ -9415,7 +9583,7 @@
           <t>g/mol</t>
         </is>
       </c>
-      <c r="D103" s="88" t="n">
+      <c r="D103" s="78" t="n">
         <v>44.0095</v>
       </c>
       <c r="E103" t="inlineStr">
@@ -9440,7 +9608,7 @@
           <t>mol/s</t>
         </is>
       </c>
-      <c r="D104" s="87">
+      <c r="D104" s="162">
         <f>P_atm*(Q_CO2/1000000/60)/(R_gas*T_K)</f>
         <v/>
       </c>
@@ -9466,7 +9634,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D105" s="87">
+      <c r="D105" s="162">
         <f>spg_dur/(spg_int*60)</f>
         <v/>
       </c>
@@ -9492,7 +9660,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D106" s="88" t="n">
+      <c r="D106" s="78" t="n">
         <v>1</v>
       </c>
       <c r="E106" t="inlineStr">
@@ -9502,7 +9670,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="63" t="inlineStr">
+      <c r="A107" s="57" t="inlineStr">
         <is>
           <t>STEADY-STATE DO CHECK (surface stripping vs organism band)</t>
         </is>
@@ -9524,7 +9692,7 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="D108" s="72">
+      <c r="D108" s="150">
         <f>O2_excess/(kLa_surf_used*3600*(V_charge/1000000))*32</f>
         <v/>
       </c>
@@ -9540,7 +9708,7 @@
           <t>DO_ss_vs_opt</t>
         </is>
       </c>
-      <c r="D109" s="72">
+      <c r="D109" s="150">
         <f>IF(ISNUMBER(DO_opt),IF(DO_ss&lt;=DO_opt,"at/under optimum",IF(DO_ss&lt;DO_impair,"above optimum, under impairment","OVER IMPAIRMENT - surface strip insufficient")),"organism optimum unknown")</f>
         <v/>
       </c>
@@ -9556,7 +9724,7 @@
           <t>DO_ss_vs_min</t>
         </is>
       </c>
-      <c r="D110" s="72">
+      <c r="D110" s="150">
         <f>IF(ISNUMBER(DO_min),IF(DO_ss&gt;=DO_min,"above minimum","BELOW MINIMUM"),"minimum DO unknown - measure")</f>
         <v/>
       </c>
@@ -9572,11 +9740,11 @@
           <t>tip_warn</t>
         </is>
       </c>
-      <c r="D111" s="72">
+      <c r="D111" s="150">
         <f>IF(tip_speed&gt;1.5,"TIP SPEED &gt; 1.5 m/s","OK")</f>
         <v/>
       </c>
-      <c r="E111" s="86" t="inlineStr">
+      <c r="E111" s="76" t="inlineStr">
         <is>
           <t>Conservative shear limit: &lt;1.5 m/s impeller-tip velocity recommended to avoid adverse cell-growth effects (BioProcess International, cell-culture norm); precautionary for robust HOB.</t>
         </is>
@@ -9598,7 +9766,7 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D112" s="72">
+      <c r="D112" s="150">
         <f>spg_dur_opt/(60*duty_carbon)</f>
         <v/>
       </c>
@@ -9614,18 +9782,18 @@
           <t>sched_regime</t>
         </is>
       </c>
-      <c r="D113" s="72">
+      <c r="D113" s="150">
         <f>IF(ISNUMBER(DO_ss),IF(DO_ss&lt;DO_impair,"Surface stripping holds DO under impairment - sparge is CARBON-limited (long interval); the O2-limited interval is the conservative fallback until kL_surf is measured","Surface stripping insufficient - sparge must vent O2 - use the O2-limited interval"),"organism DO unknown")</f>
         <v/>
       </c>
-      <c r="E113" s="86" t="inlineStr">
+      <c r="E113" s="76" t="inlineStr">
         <is>
           <t>Resolved by measuring kL_surf (improvement #1).</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="63" t="inlineStr">
+      <c r="A114" s="57" t="inlineStr">
         <is>
           <t>CO₂ DOSING &amp; SCHEDULE (folded from Dosing)</t>
         </is>
@@ -9642,8 +9810,8 @@
           <t>Reactor</t>
         </is>
       </c>
-      <c r="D115" s="71">
-        <f>Summary!$D$3</f>
+      <c r="D115" s="163">
+        <f>Summary!$D$2</f>
         <v/>
       </c>
     </row>
@@ -9658,7 +9826,7 @@
           <t>latest_date</t>
         </is>
       </c>
-      <c r="D116" s="72">
+      <c r="D116" s="150">
         <f>SUMPRODUCT(MAX(('CO2 flows'!$A$4:$A$201=Reactor)*('CO2 flows'!$J$4:$J$201&gt;0)*'CO2 flows'!$B$4:$B$201))</f>
         <v/>
       </c>
@@ -9679,7 +9847,7 @@
           <t>ml/s</t>
         </is>
       </c>
-      <c r="D117" s="72">
+      <c r="D117" s="150">
         <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$201=Reactor)*('CO2 flows'!$B$4:$B$201=latest_date)*'CO2 flows'!$J$4:$J$201)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$4:$A$201=Reactor)*('CO2 flows'!$B$4:$B$201=latest_date)*('CO2 flows'!$J$4:$J$201&gt;0)*1))</f>
         <v/>
       </c>
@@ -9700,7 +9868,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D118" s="72">
+      <c r="D118" s="150">
         <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$201=Reactor)*('CO2 flows'!$B$4:$B$201=latest_date)*'CO2 flows'!$I$4:$I$201)/MAX(1,SUMPRODUCT(('CO2 flows'!$A$4:$A$201=Reactor)*('CO2 flows'!$B$4:$B$201=latest_date)*('CO2 flows'!$J$4:$J$201&gt;0)*1))</f>
         <v/>
       </c>
@@ -9721,7 +9889,7 @@
           <t>count</t>
         </is>
       </c>
-      <c r="D119" s="72">
+      <c r="D119" s="150">
         <f>SUMPRODUCT(('CO2 flows'!$A$4:$A$201=Reactor)*('CO2 flows'!$J$4:$J$201&gt;0)*1)</f>
         <v/>
       </c>
@@ -9737,7 +9905,7 @@
           <t>cal_warning</t>
         </is>
       </c>
-      <c r="D120" s="72">
+      <c r="D120" s="150">
         <f>IF(has_cal&gt;0,"calibrated: "&amp;Reactor,"NO CALIBRATION for "&amp;Reactor&amp;" - add a row in CO2 flows with nominal flowrate + minimum sparge")</f>
         <v/>
       </c>
@@ -9758,7 +9926,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D121" s="72">
+      <c r="D121" s="150">
         <f>IF(sched_mode="Optimal",spg_dur_opt,IF(sched_mode="Manual",spg_dur_man,NA()))</f>
         <v/>
       </c>
@@ -9779,7 +9947,7 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D122" s="72">
+      <c r="D122" s="150">
         <f>IF(sched_mode="Optimal",spg_int_opt,IF(sched_mode="Manual",spg_int_man,NA()))</f>
         <v/>
       </c>
@@ -9800,7 +9968,7 @@
           <t>mol</t>
         </is>
       </c>
-      <c r="D123" s="72">
+      <c r="D123" s="150">
         <f>nCO2_rate*spg_dur</f>
         <v/>
       </c>
@@ -9821,7 +9989,7 @@
           <t>/h</t>
         </is>
       </c>
-      <c r="D124" s="72">
+      <c r="D124" s="150">
         <f>60/spg_int</f>
         <v/>
       </c>
@@ -9842,7 +10010,7 @@
           <t>/d</t>
         </is>
       </c>
-      <c r="D125" s="72">
+      <c r="D125" s="150">
         <f>pulses_h*24</f>
         <v/>
       </c>
@@ -9863,7 +10031,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D126" s="72">
+      <c r="D126" s="150">
         <f>IF(CO2_cons&gt;0,CO2_supply/CO2_cons,NA())</f>
         <v/>
       </c>
@@ -9884,7 +10052,7 @@
           <t>mol</t>
         </is>
       </c>
-      <c r="D127" s="72">
+      <c r="D127" s="150">
         <f>O2_excess/60*spg_int</f>
         <v/>
       </c>
@@ -9905,7 +10073,7 @@
           <t>mol</t>
         </is>
       </c>
-      <c r="D128" s="72">
+      <c r="D128" s="150">
         <f>strip_sparge/3600*spg_dur</f>
         <v/>
       </c>
@@ -9926,7 +10094,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D129" s="72">
+      <c r="D129" s="150">
         <f>IF(O2_accum&gt;0,O2_strip_pulse/O2_accum,NA())</f>
         <v/>
       </c>
@@ -9942,7 +10110,7 @@
           <t>dur_ok</t>
         </is>
       </c>
-      <c r="D130" s="72">
+      <c r="D130" s="150">
         <f>IF(spg_dur&gt;=pulse_floor,"OK","LOW")</f>
         <v/>
       </c>
@@ -9963,18 +10131,18 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D131" s="72">
+      <c r="D131" s="150">
         <f>O2_excess*32/(DO_impair*3600*(V_charge/1000000)*a_surf)</f>
         <v/>
       </c>
-      <c r="E131" s="66" t="inlineStr">
+      <c r="E131" s="60" t="inlineStr">
         <is>
           <t>Measured kL_surf must EXCEED this or DO_ss breaches impairment; current model kL_surf vs this = the safety margin. See protocol surface-kla.md</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="D132" s="72" t="n"/>
+      <c r="D132" s="66" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D32">
@@ -9990,10 +10158,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="6">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="8">
       <formula>"RISK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10058,20 +10226,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64">
-    <cfRule type="expression" priority="16" dxfId="1">
+    <cfRule type="expression" priority="16" dxfId="2">
       <formula>ISNUMBER(SEARCH("OOR",D64))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="6">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
       <formula>"TIGHT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110:D112">
-    <cfRule type="expression" priority="14" dxfId="1">
+    <cfRule type="expression" priority="14" dxfId="2">
       <formula>OR(ISNUMBER(SEARCH("RISK",D110)),ISNUMBER(SEARCH("OVER",D110)),ISNUMBER(SEARCH("BELOW",D110)),ISNUMBER(SEARCH("EXCEED",D110)),ISNUMBER(SEARCH("NO CALIB",D110)),ISNUMBER(SEARCH("NEAREST",D110)),ISNUMBER(SEARCH("EXPLOSIVE",D110)),ISNUMBER(SEARCH("LOW",D110)),ISNUMBER(SEARCH("TIGHT",D110)),ISNUMBER(SEARCH("insufficient",D110)))</formula>
     </cfRule>
     <cfRule type="expression" priority="15" dxfId="0">
@@ -10098,1359 +10266,2297 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="52" t="inlineStr">
+      <c r="A1" s="164" t="inlineStr">
         <is>
           <t>CO₂ DOSING FLOWRATES</t>
         </is>
       </c>
+      <c r="B1" s="124" t="n"/>
+      <c r="C1" s="124" t="n"/>
+      <c r="D1" s="124" t="n"/>
+      <c r="E1" s="124" t="n"/>
+      <c r="F1" s="124" t="n"/>
+      <c r="G1" s="124" t="n"/>
+      <c r="H1" s="124" t="n"/>
+      <c r="I1" s="124" t="n"/>
+      <c r="J1" s="124" t="n"/>
+      <c r="K1" s="124" t="n"/>
+      <c r="L1" s="124" t="n"/>
+      <c r="M1" s="124" t="n"/>
+      <c r="N1" s="124" t="n"/>
+      <c r="O1" s="124" t="n"/>
+      <c r="P1" s="124" t="n"/>
+      <c r="Q1" s="124" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="53" t="inlineStr">
+      <c r="A2" s="165" t="inlineStr">
         <is>
           <t>Reactor</t>
         </is>
       </c>
-      <c r="B2" s="53" t="inlineStr">
+      <c r="B2" s="165" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C2" s="53" t="inlineStr">
+      <c r="C2" s="165" t="inlineStr">
         <is>
           <t>cylinder size</t>
         </is>
       </c>
-      <c r="D2" s="53" t="inlineStr">
+      <c r="D2" s="165" t="inlineStr">
         <is>
           <t>observed volume*</t>
         </is>
       </c>
-      <c r="E2" s="53" t="inlineStr">
-        <is>
-          <t>volume (Δ)</t>
-        </is>
-      </c>
-      <c r="F2" s="53" t="inlineStr">
+      <c r="E2" s="165" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="F2" s="165" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="G2" s="53" t="inlineStr">
+      <c r="G2" s="165" t="inlineStr">
         <is>
           <t>flowrate</t>
         </is>
       </c>
-      <c r="H2" s="53" t="inlineStr">
+      <c r="H2" s="165" t="inlineStr">
         <is>
           <t>average flowrate</t>
         </is>
       </c>
-      <c r="I2" s="53" t="inlineStr">
-        <is>
-          <t>minimum sparge time</t>
-        </is>
-      </c>
-      <c r="J2" s="53" t="inlineStr">
+      <c r="I2" s="165" t="inlineStr">
+        <is>
+          <t>minimum sparge</t>
+        </is>
+      </c>
+      <c r="J2" s="166" t="inlineStr">
         <is>
           <t>nominal flowrate</t>
         </is>
       </c>
-      <c r="L2" s="54" t="inlineStr">
+      <c r="K2" s="124" t="n"/>
+      <c r="L2" s="167" t="inlineStr">
         <is>
           <t>KEY</t>
         </is>
       </c>
-      <c r="N2" s="63" t="n"/>
+      <c r="M2" s="124" t="n"/>
+      <c r="N2" s="166" t="n"/>
+      <c r="O2" s="124" t="n"/>
+      <c r="P2" s="124" t="n"/>
+      <c r="Q2" s="124" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="n"/>
-      <c r="B3" s="53" t="n"/>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="A3" s="165" t="n"/>
+      <c r="B3" s="165" t="n"/>
+      <c r="C3" s="165" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="D3" s="53" t="inlineStr">
+      <c r="D3" s="165" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="E3" s="53" t="inlineStr">
+      <c r="E3" s="165" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="F3" s="53" t="inlineStr">
+      <c r="F3" s="165" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="G3" s="53" t="inlineStr">
+      <c r="G3" s="165" t="inlineStr">
         <is>
           <t>ml/s</t>
         </is>
       </c>
-      <c r="H3" s="53" t="inlineStr">
+      <c r="H3" s="165" t="inlineStr">
         <is>
           <t>ml/s</t>
         </is>
       </c>
-      <c r="I3" s="53" t="inlineStr">
+      <c r="I3" s="165" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="J3" s="53" t="inlineStr">
+      <c r="J3" s="124" t="inlineStr">
         <is>
           <t>ml/s</t>
         </is>
       </c>
-      <c r="L3" s="62" t="inlineStr">
+      <c r="K3" s="124" t="n"/>
+      <c r="L3" s="168" t="inlineStr">
         <is>
           <t>Flowrate set by inspection, as maximum to not give bubbles rising into vial neck</t>
         </is>
       </c>
-      <c r="N3" s="63" t="n"/>
-      <c r="O3" s="63" t="n"/>
-      <c r="P3" s="63" t="n"/>
-      <c r="Q3" s="63" t="n"/>
+      <c r="M3" s="124" t="n"/>
+      <c r="N3" s="166" t="n"/>
+      <c r="O3" s="166" t="n"/>
+      <c r="P3" s="166" t="n"/>
+      <c r="Q3" s="166" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="124" t="inlineStr">
         <is>
           <t>ed04</t>
         </is>
       </c>
-      <c r="B4" s="60" t="n">
+      <c r="B4" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="124" t="n">
         <v>50</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="101" t="n">
+      <c r="E4" s="124" t="n"/>
+      <c r="F4" s="124" t="n"/>
+      <c r="G4" s="124" t="n"/>
+      <c r="H4" s="124" t="n"/>
+      <c r="I4" s="124" t="n">
         <v>0.25</v>
       </c>
-      <c r="J4" s="101" t="n">
+      <c r="J4" s="124" t="n">
         <v>3.33</v>
       </c>
-      <c r="L4" s="61" t="inlineStr">
+      <c r="K4" s="124" t="n"/>
+      <c r="L4" s="170" t="inlineStr">
         <is>
           <t>First or last data point removed as suspect outlier</t>
         </is>
       </c>
-      <c r="O4" s="108" t="n"/>
-      <c r="P4" s="65" t="n"/>
+      <c r="M4" s="124" t="n"/>
+      <c r="N4" s="124" t="n"/>
+      <c r="O4" s="171" t="n"/>
+      <c r="P4" s="172" t="n"/>
+      <c r="Q4" s="124" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="124" t="inlineStr">
         <is>
           <t>ed04</t>
         </is>
       </c>
-      <c r="B5" s="60" t="n">
+      <c r="B5" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="124" t="n">
         <v>50</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="124" t="n">
         <v>50</v>
       </c>
-      <c r="E5" s="62">
+      <c r="E5" s="168">
         <f>D5-D4</f>
         <v/>
       </c>
-      <c r="F5" s="62" t="n">
+      <c r="F5" s="168" t="n">
         <v>15</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="124">
         <f>E5/F5</f>
         <v/>
       </c>
-      <c r="H5">
-        <f>G5</f>
-        <v/>
-      </c>
-      <c r="N5" s="66" t="n"/>
+      <c r="H5" s="124">
+        <f>AVERAGE(G5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="124" t="n"/>
+      <c r="J5" s="124" t="n"/>
+      <c r="K5" s="124" t="n"/>
+      <c r="L5" s="124" t="n"/>
+      <c r="M5" s="124" t="n"/>
+      <c r="N5" s="173" t="n"/>
+      <c r="O5" s="124" t="n"/>
+      <c r="P5" s="124" t="n"/>
+      <c r="Q5" s="124" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="124" t="inlineStr">
         <is>
           <t>ed04</t>
         </is>
       </c>
-      <c r="B6" s="60" t="n">
+      <c r="B6" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="124" t="n">
         <v>50</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="54" t="inlineStr">
+      <c r="E6" s="124" t="n"/>
+      <c r="F6" s="124" t="n"/>
+      <c r="G6" s="124" t="n"/>
+      <c r="H6" s="124" t="n"/>
+      <c r="I6" s="124" t="n"/>
+      <c r="J6" s="124" t="n"/>
+      <c r="K6" s="167" t="inlineStr">
         <is>
           <t>Point</t>
         </is>
       </c>
-      <c r="L6" s="54" t="inlineStr">
+      <c r="L6" s="167" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
+      <c r="M6" s="124" t="n"/>
+      <c r="N6" s="124" t="n"/>
+      <c r="O6" s="124" t="n"/>
+      <c r="P6" s="124" t="n"/>
+      <c r="Q6" s="124" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="124" t="inlineStr">
         <is>
           <t>ed04</t>
         </is>
       </c>
-      <c r="B7" s="60" t="n">
+      <c r="B7" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" s="124" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" s="124">
+        <f>D7-D6</f>
+        <v/>
+      </c>
+      <c r="F7" s="124" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="124">
+        <f>E7/F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="124">
+        <f>AVERAGE(G7:G9)</f>
+        <v/>
+      </c>
+      <c r="I7" s="124" t="n"/>
+      <c r="J7" s="124" t="n"/>
+      <c r="K7" s="124" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="L7" s="124" t="inlineStr">
+        <is>
+          <t>CO2 collected in measuring cyclinder over CO2-saturated water</t>
+        </is>
+      </c>
+      <c r="M7" s="124" t="n"/>
+      <c r="N7" s="166" t="n"/>
+      <c r="O7" s="124" t="n"/>
+      <c r="P7" s="124" t="n"/>
+      <c r="Q7" s="124" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B8" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C8" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" s="124" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" s="124">
+        <f>D8-D7</f>
+        <v/>
+      </c>
+      <c r="F8" s="124" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="124">
+        <f>E8/F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="124" t="n"/>
+      <c r="I8" s="124" t="n"/>
+      <c r="J8" s="124" t="n"/>
+      <c r="K8" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="L8" s="124" t="inlineStr">
+        <is>
+          <t>Collected using inlet CO2 tube rather than outlet as MEP vialcap leaking</t>
+        </is>
+      </c>
+      <c r="M8" s="124" t="n"/>
+      <c r="N8" s="124" t="n"/>
+      <c r="O8" s="124" t="n"/>
+      <c r="P8" s="124" t="n"/>
+      <c r="Q8" s="124" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B9" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C9" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" s="124" t="n">
+        <v>40</v>
+      </c>
+      <c r="E9" s="124">
+        <f>D9-D8</f>
+        <v/>
+      </c>
+      <c r="F9" s="124" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="124">
+        <f>E9/F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="124" t="n"/>
+      <c r="I9" s="124" t="n"/>
+      <c r="J9" s="124" t="n"/>
+      <c r="K9" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="L9" s="124" t="inlineStr">
+        <is>
+          <t>Collected over saturated NaHCO3 soln, as Martin  innovated without thinking</t>
+        </is>
+      </c>
+      <c r="M9" s="124" t="n"/>
+      <c r="N9" s="124" t="n"/>
+      <c r="O9" s="124" t="n"/>
+      <c r="P9" s="124" t="n"/>
+      <c r="Q9" s="124" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B10" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C10" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="124" t="n"/>
+      <c r="F10" s="124" t="n"/>
+      <c r="G10" s="124" t="n"/>
+      <c r="H10" s="124" t="n"/>
+      <c r="I10" s="124" t="n"/>
+      <c r="J10" s="124" t="n"/>
+      <c r="K10" s="124" t="n"/>
+      <c r="L10" s="124" t="n"/>
+      <c r="M10" s="124" t="n"/>
+      <c r="N10" s="124" t="n"/>
+      <c r="O10" s="124" t="n"/>
+      <c r="P10" s="124" t="n"/>
+      <c r="Q10" s="124" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B11" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C11" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" s="124" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="124">
+        <f>D11-D10</f>
+        <v/>
+      </c>
+      <c r="F11" s="124" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="124">
+        <f>E11/F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="124">
+        <f>AVERAGE(G11:G16)</f>
+        <v/>
+      </c>
+      <c r="I11" s="124" t="n"/>
+      <c r="J11" s="124" t="n"/>
+      <c r="K11" s="124" t="n"/>
+      <c r="L11" s="124" t="n"/>
+      <c r="M11" s="124" t="n"/>
+      <c r="N11" s="124" t="n"/>
+      <c r="O11" s="124" t="n"/>
+      <c r="P11" s="124" t="n"/>
+      <c r="Q11" s="124" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B12" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C12" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" s="124" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" s="124">
+        <f>D12-D11</f>
+        <v/>
+      </c>
+      <c r="F12" s="124" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="124">
+        <f>E12/F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="124" t="n"/>
+      <c r="I12" s="124" t="n"/>
+      <c r="J12" s="124" t="n"/>
+      <c r="K12" s="124" t="n"/>
+      <c r="L12" s="124" t="n"/>
+      <c r="M12" s="124" t="n"/>
+      <c r="N12" s="124" t="n"/>
+      <c r="O12" s="124" t="n"/>
+      <c r="P12" s="124" t="n"/>
+      <c r="Q12" s="124" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B13" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C13" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" s="124" t="n">
+        <v>21</v>
+      </c>
+      <c r="E13" s="124">
+        <f>D13-D12</f>
+        <v/>
+      </c>
+      <c r="F13" s="124" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="124">
+        <f>E13/F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="124" t="n"/>
+      <c r="I13" s="124" t="n"/>
+      <c r="J13" s="124" t="n"/>
+      <c r="K13" s="124" t="n"/>
+      <c r="L13" s="124" t="n"/>
+      <c r="M13" s="124" t="n"/>
+      <c r="N13" s="124" t="n"/>
+      <c r="O13" s="124" t="n"/>
+      <c r="P13" s="124" t="n"/>
+      <c r="Q13" s="124" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B14" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C14" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" s="124" t="n">
+        <v>29</v>
+      </c>
+      <c r="E14" s="124">
+        <f>D14-D13</f>
+        <v/>
+      </c>
+      <c r="F14" s="124" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="124">
+        <f>E14/F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="124" t="n"/>
+      <c r="I14" s="124" t="n"/>
+      <c r="J14" s="124" t="n"/>
+      <c r="K14" s="124" t="n"/>
+      <c r="L14" s="124" t="n"/>
+      <c r="M14" s="124" t="n"/>
+      <c r="N14" s="124" t="n"/>
+      <c r="O14" s="124" t="n"/>
+      <c r="P14" s="124" t="n"/>
+      <c r="Q14" s="124" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B15" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C15" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" s="124" t="n">
+        <v>35</v>
+      </c>
+      <c r="E15" s="124">
+        <f>D15-D14</f>
+        <v/>
+      </c>
+      <c r="F15" s="124" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="124">
+        <f>E15/F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="124" t="n"/>
+      <c r="I15" s="124" t="n"/>
+      <c r="J15" s="124" t="n"/>
+      <c r="K15" s="124" t="n"/>
+      <c r="L15" s="124" t="n"/>
+      <c r="M15" s="124" t="n"/>
+      <c r="N15" s="124" t="n"/>
+      <c r="O15" s="124" t="n"/>
+      <c r="P15" s="124" t="n"/>
+      <c r="Q15" s="124" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B16" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C16" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" s="124" t="n">
+        <v>45</v>
+      </c>
+      <c r="E16" s="124">
+        <f>D16-D15</f>
+        <v/>
+      </c>
+      <c r="F16" s="124" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="124">
+        <f>E16/F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="124" t="n"/>
+      <c r="I16" s="124" t="n"/>
+      <c r="J16" s="124" t="n"/>
+      <c r="K16" s="124" t="n"/>
+      <c r="L16" s="124" t="n"/>
+      <c r="M16" s="124" t="n"/>
+      <c r="N16" s="124" t="n"/>
+      <c r="O16" s="124" t="n"/>
+      <c r="P16" s="124" t="n"/>
+      <c r="Q16" s="124" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B17" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C17" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="124" t="n"/>
+      <c r="F17" s="124" t="n"/>
+      <c r="G17" s="124" t="n"/>
+      <c r="H17" s="124" t="n"/>
+      <c r="I17" s="124" t="n"/>
+      <c r="J17" s="124" t="n"/>
+      <c r="K17" s="124" t="n"/>
+      <c r="L17" s="124" t="n"/>
+      <c r="M17" s="124" t="n"/>
+      <c r="N17" s="124" t="n"/>
+      <c r="O17" s="124" t="n"/>
+      <c r="P17" s="124" t="n"/>
+      <c r="Q17" s="124" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B18" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C18" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" s="124" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="124">
+        <f>D18-D17</f>
+        <v/>
+      </c>
+      <c r="F18" s="124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="124">
+        <f>E18/F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="124">
+        <f>AVERAGE(G18:G23)</f>
+        <v/>
+      </c>
+      <c r="I18" s="124" t="n"/>
+      <c r="J18" s="124" t="n"/>
+      <c r="K18" s="124" t="n"/>
+      <c r="L18" s="124" t="n"/>
+      <c r="M18" s="124" t="n"/>
+      <c r="N18" s="124" t="n"/>
+      <c r="O18" s="124" t="n"/>
+      <c r="P18" s="124" t="n"/>
+      <c r="Q18" s="124" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B19" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C19" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D19" s="124" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="124">
+        <f>D19-D18</f>
+        <v/>
+      </c>
+      <c r="F19" s="124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="124">
+        <f>E19/F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="124" t="n"/>
+      <c r="I19" s="124" t="n"/>
+      <c r="J19" s="124" t="n"/>
+      <c r="K19" s="124" t="n"/>
+      <c r="L19" s="124" t="n"/>
+      <c r="M19" s="124" t="n"/>
+      <c r="N19" s="124" t="n"/>
+      <c r="O19" s="124" t="n"/>
+      <c r="P19" s="124" t="n"/>
+      <c r="Q19" s="124" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B20" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C20" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" s="124" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" s="124">
+        <f>D20-D19</f>
+        <v/>
+      </c>
+      <c r="F20" s="124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="124">
+        <f>E20/F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="124" t="n"/>
+      <c r="I20" s="124" t="n"/>
+      <c r="J20" s="124" t="n"/>
+      <c r="K20" s="124" t="n"/>
+      <c r="L20" s="124" t="n"/>
+      <c r="M20" s="124" t="n"/>
+      <c r="N20" s="124" t="n"/>
+      <c r="O20" s="124" t="n"/>
+      <c r="P20" s="124" t="n"/>
+      <c r="Q20" s="124" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B21" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C21" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D21" s="124" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" s="124">
+        <f>D21-D20</f>
+        <v/>
+      </c>
+      <c r="F21" s="124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="124">
+        <f>E21/F21</f>
+        <v/>
+      </c>
+      <c r="H21" s="124" t="n"/>
+      <c r="I21" s="124" t="n"/>
+      <c r="J21" s="124" t="n"/>
+      <c r="K21" s="124" t="n"/>
+      <c r="L21" s="124" t="n"/>
+      <c r="M21" s="124" t="n"/>
+      <c r="N21" s="124" t="n"/>
+      <c r="O21" s="124" t="n"/>
+      <c r="P21" s="124" t="n"/>
+      <c r="Q21" s="124" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B22" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C22" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D22" s="124" t="n">
+        <v>19</v>
+      </c>
+      <c r="E22" s="124">
+        <f>D22-D21</f>
+        <v/>
+      </c>
+      <c r="F22" s="124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="124">
+        <f>E22/F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="124" t="n"/>
+      <c r="I22" s="124" t="n"/>
+      <c r="J22" s="124" t="n"/>
+      <c r="K22" s="124" t="n"/>
+      <c r="L22" s="124" t="n"/>
+      <c r="M22" s="124" t="n"/>
+      <c r="N22" s="124" t="n"/>
+      <c r="O22" s="124" t="n"/>
+      <c r="P22" s="124" t="n"/>
+      <c r="Q22" s="124" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B23" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C23" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D23" s="124" t="n">
+        <v>23</v>
+      </c>
+      <c r="E23" s="124">
+        <f>D23-D22</f>
+        <v/>
+      </c>
+      <c r="F23" s="124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="124">
+        <f>E23/F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="124" t="n"/>
+      <c r="I23" s="124" t="n"/>
+      <c r="J23" s="124" t="n"/>
+      <c r="K23" s="124" t="n"/>
+      <c r="L23" s="124" t="n"/>
+      <c r="M23" s="124" t="n"/>
+      <c r="N23" s="124" t="n"/>
+      <c r="O23" s="124" t="n"/>
+      <c r="P23" s="124" t="n"/>
+      <c r="Q23" s="124" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B24" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C24" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D24" s="124" t="n">
+        <v>31</v>
+      </c>
+      <c r="E24" s="124" t="n"/>
+      <c r="F24" s="124" t="n"/>
+      <c r="G24" s="124" t="n"/>
+      <c r="H24" s="124" t="n"/>
+      <c r="I24" s="124" t="n"/>
+      <c r="J24" s="124" t="n"/>
+      <c r="K24" s="124" t="n"/>
+      <c r="L24" s="124" t="n"/>
+      <c r="M24" s="124" t="n"/>
+      <c r="N24" s="124" t="n"/>
+      <c r="O24" s="124" t="n"/>
+      <c r="P24" s="124" t="n"/>
+      <c r="Q24" s="124" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B25" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C25" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D25" s="124" t="n">
+        <v>33</v>
+      </c>
+      <c r="E25" s="124">
+        <f>D25-D24</f>
+        <v/>
+      </c>
+      <c r="F25" s="124" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G25" s="124">
+        <f>E25/F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="124">
+        <f>AVERAGE(G25:G29)</f>
+        <v/>
+      </c>
+      <c r="I25" s="124" t="n"/>
+      <c r="J25" s="124" t="n"/>
+      <c r="K25" s="124" t="n"/>
+      <c r="L25" s="124" t="n"/>
+      <c r="M25" s="124" t="n"/>
+      <c r="N25" s="124" t="n"/>
+      <c r="O25" s="124" t="n"/>
+      <c r="P25" s="124" t="n"/>
+      <c r="Q25" s="124" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B26" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C26" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D26" s="124" t="n">
+        <v>35</v>
+      </c>
+      <c r="E26" s="124">
+        <f>D26-D25</f>
+        <v/>
+      </c>
+      <c r="F26" s="124" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G26" s="124">
+        <f>E26/F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="124" t="n"/>
+      <c r="I26" s="124" t="n"/>
+      <c r="J26" s="124" t="n"/>
+      <c r="K26" s="124" t="n"/>
+      <c r="L26" s="124" t="n"/>
+      <c r="M26" s="124" t="n"/>
+      <c r="N26" s="124" t="n"/>
+      <c r="O26" s="124" t="n"/>
+      <c r="P26" s="124" t="n"/>
+      <c r="Q26" s="124" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B27" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C27" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D27" s="124" t="n">
+        <v>37</v>
+      </c>
+      <c r="E27" s="124">
+        <f>D27-D26</f>
+        <v/>
+      </c>
+      <c r="F27" s="124" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G27" s="124">
+        <f>E27/F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="124" t="n"/>
+      <c r="I27" s="124" t="n"/>
+      <c r="J27" s="124" t="n"/>
+      <c r="K27" s="124" t="n"/>
+      <c r="L27" s="124" t="n"/>
+      <c r="M27" s="124" t="n"/>
+      <c r="N27" s="124" t="n"/>
+      <c r="O27" s="124" t="n"/>
+      <c r="P27" s="124" t="n"/>
+      <c r="Q27" s="124" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B28" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C28" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D28" s="124" t="n">
+        <v>39</v>
+      </c>
+      <c r="E28" s="124">
+        <f>D28-D27</f>
+        <v/>
+      </c>
+      <c r="F28" s="124" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G28" s="124">
+        <f>E28/F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="124" t="n"/>
+      <c r="I28" s="124" t="n"/>
+      <c r="J28" s="124" t="n"/>
+      <c r="K28" s="124" t="n"/>
+      <c r="L28" s="124" t="n"/>
+      <c r="M28" s="124" t="n"/>
+      <c r="N28" s="124" t="n"/>
+      <c r="O28" s="124" t="n"/>
+      <c r="P28" s="124" t="n"/>
+      <c r="Q28" s="124" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B29" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C29" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D29" s="124" t="n">
+        <v>41</v>
+      </c>
+      <c r="E29" s="124">
+        <f>D29-D28</f>
+        <v/>
+      </c>
+      <c r="F29" s="124" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G29" s="124">
+        <f>E29/F29</f>
+        <v/>
+      </c>
+      <c r="H29" s="124" t="n"/>
+      <c r="I29" s="124" t="n"/>
+      <c r="J29" s="124" t="n"/>
+      <c r="K29" s="124" t="n"/>
+      <c r="L29" s="124" t="n"/>
+      <c r="M29" s="124" t="n"/>
+      <c r="N29" s="124" t="n"/>
+      <c r="O29" s="124" t="n"/>
+      <c r="P29" s="124" t="n"/>
+      <c r="Q29" s="124" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B30" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C30" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D30" s="124" t="n">
+        <v>42</v>
+      </c>
+      <c r="E30" s="124">
+        <f>D30-D29</f>
+        <v/>
+      </c>
+      <c r="F30" s="124" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G30" s="124">
+        <f>E30/F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="124">
+        <f>AVERAGE(G30:G34)</f>
+        <v/>
+      </c>
+      <c r="I30" s="124" t="n"/>
+      <c r="J30" s="124" t="n"/>
+      <c r="K30" s="124" t="n"/>
+      <c r="L30" s="124" t="n"/>
+      <c r="M30" s="124" t="n"/>
+      <c r="N30" s="124" t="n"/>
+      <c r="O30" s="124" t="n"/>
+      <c r="P30" s="124" t="n"/>
+      <c r="Q30" s="124" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B31" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C31" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D31" s="124" t="n">
+        <v>43</v>
+      </c>
+      <c r="E31" s="124">
+        <f>D31-D30</f>
+        <v/>
+      </c>
+      <c r="F31" s="124" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G31" s="124">
+        <f>E31/F31</f>
+        <v/>
+      </c>
+      <c r="H31" s="124" t="n"/>
+      <c r="I31" s="124" t="n"/>
+      <c r="J31" s="124" t="n"/>
+      <c r="K31" s="124" t="n"/>
+      <c r="L31" s="124" t="n"/>
+      <c r="M31" s="124" t="n"/>
+      <c r="N31" s="124" t="n"/>
+      <c r="O31" s="124" t="n"/>
+      <c r="P31" s="124" t="n"/>
+      <c r="Q31" s="124" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B32" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C32" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D32" s="124" t="n">
+        <v>44</v>
+      </c>
+      <c r="E32" s="124">
+        <f>D32-D31</f>
+        <v/>
+      </c>
+      <c r="F32" s="124" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G32" s="124">
+        <f>E32/F32</f>
+        <v/>
+      </c>
+      <c r="H32" s="124" t="n"/>
+      <c r="I32" s="124" t="n"/>
+      <c r="J32" s="124" t="n"/>
+      <c r="K32" s="124" t="n"/>
+      <c r="L32" s="124" t="n"/>
+      <c r="M32" s="124" t="n"/>
+      <c r="N32" s="124" t="n"/>
+      <c r="O32" s="124" t="n"/>
+      <c r="P32" s="124" t="n"/>
+      <c r="Q32" s="124" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B33" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C33" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D33" s="124" t="n">
+        <v>45</v>
+      </c>
+      <c r="E33" s="124">
+        <f>D33-D32</f>
+        <v/>
+      </c>
+      <c r="F33" s="124" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G33" s="124">
+        <f>E33/F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="124" t="n"/>
+      <c r="I33" s="124" t="n"/>
+      <c r="J33" s="124" t="n"/>
+      <c r="K33" s="124" t="n"/>
+      <c r="L33" s="124" t="n"/>
+      <c r="M33" s="124" t="n"/>
+      <c r="N33" s="124" t="n"/>
+      <c r="O33" s="124" t="n"/>
+      <c r="P33" s="124" t="n"/>
+      <c r="Q33" s="124" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B34" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C34" s="124" t="n">
+        <v>50</v>
+      </c>
+      <c r="D34" s="124" t="n">
+        <v>46</v>
+      </c>
+      <c r="E34" s="124">
+        <f>D34-D33</f>
+        <v/>
+      </c>
+      <c r="F34" s="124" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G34" s="124">
+        <f>E34/F34</f>
+        <v/>
+      </c>
+      <c r="H34" s="124" t="n"/>
+      <c r="I34" s="124" t="n"/>
+      <c r="J34" s="124" t="n"/>
+      <c r="K34" s="124" t="n"/>
+      <c r="L34" s="124" t="n"/>
+      <c r="M34" s="124" t="n"/>
+      <c r="N34" s="124" t="n"/>
+      <c r="O34" s="124" t="n"/>
+      <c r="P34" s="124" t="n"/>
+      <c r="Q34" s="124" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B35" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C35" s="124" t="n">
         <v>10</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D35" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="124">
+        <f>D35-D34</f>
+        <v/>
+      </c>
+      <c r="F35" s="124" t="n"/>
+      <c r="G35" s="124" t="n"/>
+      <c r="H35" s="124" t="n"/>
+      <c r="I35" s="124" t="n"/>
+      <c r="J35" s="124" t="n"/>
+      <c r="K35" s="124" t="n"/>
+      <c r="L35" s="124" t="n"/>
+      <c r="M35" s="124" t="n"/>
+      <c r="N35" s="124" t="n"/>
+      <c r="O35" s="124" t="n"/>
+      <c r="P35" s="124" t="n"/>
+      <c r="Q35" s="124" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B36" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C36" s="124" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" s="124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E36" s="124">
+        <f>D36-D35</f>
+        <v/>
+      </c>
+      <c r="F36" s="124" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G36" s="170">
+        <f>E36/F36</f>
+        <v/>
+      </c>
+      <c r="H36" s="124" t="n"/>
+      <c r="I36" s="124" t="n"/>
+      <c r="J36" s="124" t="n"/>
+      <c r="K36" s="124" t="n"/>
+      <c r="L36" s="124" t="n"/>
+      <c r="M36" s="124" t="n"/>
+      <c r="N36" s="124" t="n"/>
+      <c r="O36" s="124" t="n"/>
+      <c r="P36" s="124" t="n"/>
+      <c r="Q36" s="124" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B37" s="169" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C37" s="124" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" s="124" t="n">
         <v>1.2</v>
       </c>
-      <c r="E7">
-        <f>D7-D42</f>
-        <v/>
-      </c>
-      <c r="F7" t="n">
+      <c r="E37" s="124">
+        <f>D37-D36</f>
+        <v/>
+      </c>
+      <c r="F37" s="124" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7">
-        <f>E7/F7</f>
-        <v/>
-      </c>
-      <c r="H7">
-        <f>AVERAGE(G7:G9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="G37" s="124">
+        <f>E37/F37</f>
+        <v/>
+      </c>
+      <c r="H37" s="124">
+        <f>AVERAGE(G37:G39)</f>
+        <v/>
+      </c>
+      <c r="I37" s="124" t="n"/>
+      <c r="J37" s="124" t="n"/>
+      <c r="K37" s="124" t="n"/>
+      <c r="L37" s="124" t="n"/>
+      <c r="M37" s="124" t="n"/>
+      <c r="N37" s="124" t="n"/>
+      <c r="O37" s="124" t="n"/>
+      <c r="P37" s="124" t="n"/>
+      <c r="Q37" s="124" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="124" t="inlineStr">
         <is>
           <t>ed04</t>
         </is>
       </c>
-      <c r="B8" s="60" t="n">
+      <c r="B38" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C38" s="124" t="n">
         <v>10</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D38" s="124" t="n">
         <v>2.2</v>
       </c>
-      <c r="E8">
-        <f>D8-D7</f>
-        <v/>
-      </c>
-      <c r="F8" t="n">
+      <c r="E38" s="124">
+        <f>D38-D37</f>
+        <v/>
+      </c>
+      <c r="F38" s="124" t="n">
         <v>0.2</v>
       </c>
-      <c r="G8">
-        <f>E8/F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="G38" s="124">
+        <f>E38/F38</f>
+        <v/>
+      </c>
+      <c r="H38" s="124" t="n"/>
+      <c r="I38" s="124" t="n"/>
+      <c r="J38" s="124" t="n"/>
+      <c r="K38" s="124" t="n"/>
+      <c r="L38" s="124" t="n"/>
+      <c r="M38" s="124" t="n"/>
+      <c r="N38" s="124" t="n"/>
+      <c r="O38" s="124" t="n"/>
+      <c r="P38" s="124" t="n"/>
+      <c r="Q38" s="124" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="124" t="inlineStr">
         <is>
           <t>ed04</t>
         </is>
       </c>
-      <c r="B9" s="60" t="n">
+      <c r="B39" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C39" s="124" t="n">
         <v>10</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D39" s="124" t="n">
         <v>3</v>
       </c>
-      <c r="E9">
-        <f>D9-D8</f>
-        <v/>
-      </c>
-      <c r="F9" t="n">
+      <c r="E39" s="124">
+        <f>D39-D38</f>
+        <v/>
+      </c>
+      <c r="F39" s="124" t="n">
         <v>0.2</v>
       </c>
-      <c r="G9">
-        <f>E9/F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="G39" s="124">
+        <f>E39/F39</f>
+        <v/>
+      </c>
+      <c r="H39" s="124" t="n"/>
+      <c r="I39" s="124" t="n"/>
+      <c r="J39" s="124" t="n"/>
+      <c r="K39" s="124" t="n"/>
+      <c r="L39" s="124" t="n"/>
+      <c r="M39" s="124" t="n"/>
+      <c r="N39" s="124" t="n"/>
+      <c r="O39" s="124" t="n"/>
+      <c r="P39" s="124" t="n"/>
+      <c r="Q39" s="124" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="124" t="inlineStr">
         <is>
           <t>ed04</t>
         </is>
       </c>
-      <c r="B10" s="60" t="n">
+      <c r="B40" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C40" s="124" t="n">
         <v>10</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D40" s="124" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="E40" s="124" t="n"/>
+      <c r="F40" s="124" t="n"/>
+      <c r="G40" s="124" t="n"/>
+      <c r="H40" s="124" t="n"/>
+      <c r="I40" s="124" t="n"/>
+      <c r="J40" s="124" t="n"/>
+      <c r="K40" s="124" t="n"/>
+      <c r="L40" s="124" t="n"/>
+      <c r="M40" s="124" t="n"/>
+      <c r="N40" s="124" t="n"/>
+      <c r="O40" s="124" t="n"/>
+      <c r="P40" s="124" t="n"/>
+      <c r="Q40" s="124" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="124" t="inlineStr">
         <is>
           <t>ed04</t>
         </is>
       </c>
-      <c r="B11" s="60" t="n">
+      <c r="B41" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C41" s="124" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D41" s="124" t="n">
         <v>0.4</v>
       </c>
-      <c r="E11">
-        <f>D11-D10</f>
-        <v/>
-      </c>
-      <c r="F11" t="n">
+      <c r="E41" s="124">
+        <f>D41-D40</f>
+        <v/>
+      </c>
+      <c r="F41" s="124" t="n">
         <v>0.1</v>
       </c>
-      <c r="G11">
-        <f>E11/F11</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>AVERAGE(G11:G46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="60" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="G41" s="124">
+        <f>E41/F41</f>
+        <v/>
+      </c>
+      <c r="H41" s="124">
+        <f>AVERAGE(G41:G45)</f>
+        <v/>
+      </c>
+      <c r="I41" s="124" t="n"/>
+      <c r="J41" s="124" t="n"/>
+      <c r="K41" s="124" t="n"/>
+      <c r="L41" s="124" t="n"/>
+      <c r="M41" s="124" t="n"/>
+      <c r="N41" s="124" t="n"/>
+      <c r="O41" s="124" t="n"/>
+      <c r="P41" s="124" t="n"/>
+      <c r="Q41" s="124" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="124" t="inlineStr">
         <is>
           <t>ed04</t>
         </is>
       </c>
-      <c r="B13" s="60" t="n">
+      <c r="B42" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="n">
-        <v>12</v>
-      </c>
-      <c r="E13">
-        <f>D13-D6</f>
-        <v/>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13">
-        <f>E13/F13</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>AVERAGE(G13:G15)</f>
-        <v/>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>CO2 collected in measuring cylinder over CO2-saturated water</t>
-        </is>
-      </c>
-      <c r="N13" s="63" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C42" s="124" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="124" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E42" s="124">
+        <f>D42-D41</f>
+        <v/>
+      </c>
+      <c r="F42" s="124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G42" s="124">
+        <f>E42/F42</f>
+        <v/>
+      </c>
+      <c r="H42" s="124" t="n"/>
+      <c r="I42" s="124" t="n"/>
+      <c r="J42" s="124" t="n"/>
+      <c r="K42" s="124" t="n"/>
+      <c r="L42" s="124" t="n"/>
+      <c r="M42" s="124" t="n"/>
+      <c r="N42" s="124" t="n"/>
+      <c r="O42" s="124" t="n"/>
+      <c r="P42" s="124" t="n"/>
+      <c r="Q42" s="124" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="124" t="inlineStr">
         <is>
           <t>ed04</t>
         </is>
       </c>
-      <c r="B14" s="60" t="n">
+      <c r="B43" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="n">
-        <v>26</v>
-      </c>
-      <c r="E14">
-        <f>D14-D13</f>
-        <v/>
-      </c>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14">
-        <f>E14/F14</f>
-        <v/>
-      </c>
-      <c r="K14" s="60" t="n">
+      <c r="C43" s="124" t="n">
+        <v>10</v>
+      </c>
+      <c r="D43" s="124" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E43" s="124">
+        <f>D43-D42</f>
+        <v/>
+      </c>
+      <c r="F43" s="124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G43" s="124">
+        <f>E43/F43</f>
+        <v/>
+      </c>
+      <c r="H43" s="124" t="n"/>
+      <c r="I43" s="124" t="n"/>
+      <c r="J43" s="124" t="n"/>
+      <c r="K43" s="124" t="n"/>
+      <c r="L43" s="124" t="n"/>
+      <c r="M43" s="124" t="n"/>
+      <c r="N43" s="124" t="n"/>
+      <c r="O43" s="124" t="n"/>
+      <c r="P43" s="124" t="n"/>
+      <c r="Q43" s="124" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B44" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Collected using inlet CO2 tube rather than outlet as MEP vialcap leaking</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="C44" s="124" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="124">
+        <f>D44-D43</f>
+        <v/>
+      </c>
+      <c r="F44" s="124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G44" s="124">
+        <f>E44/F44</f>
+        <v/>
+      </c>
+      <c r="H44" s="124" t="n"/>
+      <c r="I44" s="124" t="n"/>
+      <c r="J44" s="124" t="n"/>
+      <c r="K44" s="124" t="n"/>
+      <c r="L44" s="124" t="n"/>
+      <c r="M44" s="124" t="n"/>
+      <c r="N44" s="124" t="n"/>
+      <c r="O44" s="124" t="n"/>
+      <c r="P44" s="124" t="n"/>
+      <c r="Q44" s="124" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="124" t="inlineStr">
         <is>
           <t>ed04</t>
         </is>
       </c>
-      <c r="B15" s="60" t="n">
+      <c r="B45" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="C15" t="n">
-        <v>50</v>
-      </c>
-      <c r="D15" t="n">
-        <v>40</v>
-      </c>
-      <c r="E15">
-        <f>D15-D14</f>
-        <v/>
-      </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15">
-        <f>E15/F15</f>
-        <v/>
-      </c>
-      <c r="K15" s="60" t="n">
+      <c r="C45" s="124" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" s="124" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E45" s="124">
+        <f>D45-D44</f>
+        <v/>
+      </c>
+      <c r="F45" s="124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G45" s="124">
+        <f>E45/F45</f>
+        <v/>
+      </c>
+      <c r="H45" s="124" t="n"/>
+      <c r="I45" s="124" t="n"/>
+      <c r="J45" s="124" t="n"/>
+      <c r="K45" s="124" t="n"/>
+      <c r="L45" s="124" t="n"/>
+      <c r="M45" s="124" t="n"/>
+      <c r="N45" s="124" t="n"/>
+      <c r="O45" s="124" t="n"/>
+      <c r="P45" s="124" t="n"/>
+      <c r="Q45" s="124" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="124" t="inlineStr">
+        <is>
+          <t>ed04</t>
+        </is>
+      </c>
+      <c r="B46" s="169" t="n">
         <v>46190</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Collected over saturated NaHCO3 soln, as Martin innovated without thinking</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B16" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C16" t="n">
-        <v>50</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B17" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D17" t="n">
-        <v>6</v>
-      </c>
-      <c r="E17">
-        <f>D17-D16</f>
-        <v/>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <f>E17/F17</f>
-        <v/>
-      </c>
-      <c r="H17">
-        <f>AVERAGE(G17:G22)</f>
-        <v/>
-      </c>
-      <c r="K17" s="121" t="n"/>
-      <c r="L17" s="109" t="inlineStr">
-        <is>
-          <t>Light blue = calibration input the model reads (latest date per reactor)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B18" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="n">
-        <v>15</v>
-      </c>
-      <c r="E18">
-        <f>D18-D17</f>
-        <v/>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18">
-        <f>E18/F18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B19" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C19" t="n">
-        <v>50</v>
-      </c>
-      <c r="D19" t="n">
-        <v>21</v>
-      </c>
-      <c r="E19">
-        <f>D19-D18</f>
-        <v/>
-      </c>
-      <c r="F19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19">
-        <f>E19/F19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B20" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" t="n">
-        <v>29</v>
-      </c>
-      <c r="E20">
-        <f>D20-D19</f>
-        <v/>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20">
-        <f>E20/F20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B21" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C21" t="n">
-        <v>50</v>
-      </c>
-      <c r="D21" t="n">
-        <v>35</v>
-      </c>
-      <c r="E21">
-        <f>D21-D20</f>
-        <v/>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21">
-        <f>E21/F21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B22" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C22" t="n">
-        <v>50</v>
-      </c>
-      <c r="D22" t="n">
-        <v>45</v>
-      </c>
-      <c r="E22">
-        <f>D22-D21</f>
-        <v/>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22">
-        <f>E22/F22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B23" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C23" t="n">
-        <v>50</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B24" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C24" t="n">
-        <v>50</v>
-      </c>
-      <c r="D24" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24">
-        <f>D24-D23</f>
-        <v/>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <f>E24/F24</f>
-        <v/>
-      </c>
-      <c r="H24">
-        <f>AVERAGE(G24:G29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B25" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C25" t="n">
-        <v>50</v>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25">
-        <f>D25-D24</f>
-        <v/>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <f>E25/F25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B26" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C26" t="n">
-        <v>50</v>
-      </c>
-      <c r="D26" t="n">
-        <v>11</v>
-      </c>
-      <c r="E26">
-        <f>D26-D25</f>
-        <v/>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <f>E26/F26</f>
-        <v/>
-      </c>
-      <c r="L26" s="63" t="inlineStr">
-        <is>
-          <t>HOW TO ADD A CALIBRATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B27" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C27" t="n">
-        <v>50</v>
-      </c>
-      <c r="D27" t="n">
-        <v>15</v>
-      </c>
-      <c r="E27">
-        <f>D27-D26</f>
-        <v/>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <f>E27/F27</f>
-        <v/>
-      </c>
-      <c r="L27" s="66" t="inlineStr">
-        <is>
-          <t>1. Add a row: reactor ID (col A), date (col B), then the burst measurements (vol/time).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B28" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C28" t="n">
-        <v>50</v>
-      </c>
-      <c r="D28" t="n">
-        <v>19</v>
-      </c>
-      <c r="E28">
-        <f>D28-D27</f>
-        <v/>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <f>E28/F28</f>
-        <v/>
-      </c>
-      <c r="L28" s="66" t="inlineStr">
-        <is>
-          <t>2. Enter the chosen nominal flowrate (col J, ml/s) and minimum reliable sparge (col I, s) for that reactor+date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B29" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C29" t="n">
-        <v>50</v>
-      </c>
-      <c r="D29" t="n">
-        <v>23</v>
-      </c>
-      <c r="E29">
-        <f>D29-D28</f>
-        <v/>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <f>E29/F29</f>
-        <v/>
-      </c>
-      <c r="L29" s="66" t="inlineStr">
-        <is>
-          <t>3. The model reads the LATEST dated J/I for the selected reactor automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B30" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C30" t="n">
-        <v>50</v>
-      </c>
-      <c r="D30" t="n">
-        <v>31</v>
-      </c>
-      <c r="L30" s="66" t="inlineStr">
-        <is>
-          <t>Derivation (ed04): nominal 3.33 ml/s = inspection-set max (no bubbles into the neck), confirmed by long-pulse slope;</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B31" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C31" t="n">
-        <v>50</v>
-      </c>
-      <c r="D31" t="n">
-        <v>33</v>
-      </c>
-      <c r="E31">
-        <f>D31-D30</f>
-        <v/>
-      </c>
-      <c r="F31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G31">
-        <f>E31/F31</f>
-        <v/>
-      </c>
-      <c r="H31">
-        <f>AVERAGE(G31:G35)</f>
-        <v/>
-      </c>
-      <c r="L31" s="66" t="inlineStr">
-        <is>
-          <t>min sparge 0.25 s = shortest repeatable shot (1 ml); at &lt;=0.2 s per-pulse flow is erratic (open/close bolus dominates). See protocol: flow-calibration.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B32" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C32" t="n">
-        <v>50</v>
-      </c>
-      <c r="D32" t="n">
-        <v>35</v>
-      </c>
-      <c r="E32">
-        <f>D32-D31</f>
-        <v/>
-      </c>
-      <c r="F32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G32">
-        <f>E32/F32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B33" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C33" t="n">
-        <v>50</v>
-      </c>
-      <c r="D33" t="n">
-        <v>37</v>
-      </c>
-      <c r="E33">
-        <f>D33-D32</f>
-        <v/>
-      </c>
-      <c r="F33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G33">
-        <f>E33/F33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B34" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C34" t="n">
-        <v>50</v>
-      </c>
-      <c r="D34" t="n">
-        <v>39</v>
-      </c>
-      <c r="E34">
-        <f>D34-D33</f>
-        <v/>
-      </c>
-      <c r="F34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G34">
-        <f>E34/F34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B35" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C35" t="n">
-        <v>50</v>
-      </c>
-      <c r="D35" t="n">
-        <v>41</v>
-      </c>
-      <c r="E35">
-        <f>D35-D34</f>
-        <v/>
-      </c>
-      <c r="F35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G35">
-        <f>E35/F35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B36" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C36" t="n">
-        <v>50</v>
-      </c>
-      <c r="D36" t="n">
-        <v>42</v>
-      </c>
-      <c r="E36">
-        <f>D36-D35</f>
-        <v/>
-      </c>
-      <c r="F36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G36">
-        <f>E36/F36</f>
-        <v/>
-      </c>
-      <c r="H36">
-        <f>AVERAGE(G36:G40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B37" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C37" t="n">
-        <v>50</v>
-      </c>
-      <c r="D37" t="n">
-        <v>43</v>
-      </c>
-      <c r="E37">
-        <f>D37-D36</f>
-        <v/>
-      </c>
-      <c r="F37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G37">
-        <f>E37/F37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B38" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C38" t="n">
-        <v>50</v>
-      </c>
-      <c r="D38" t="n">
-        <v>44</v>
-      </c>
-      <c r="E38">
-        <f>D38-D37</f>
-        <v/>
-      </c>
-      <c r="F38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G38">
-        <f>E38/F38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B39" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C39" t="n">
-        <v>50</v>
-      </c>
-      <c r="D39" t="n">
-        <v>45</v>
-      </c>
-      <c r="E39">
-        <f>D39-D38</f>
-        <v/>
-      </c>
-      <c r="F39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G39">
-        <f>E39/F39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B40" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C40" t="n">
-        <v>50</v>
-      </c>
-      <c r="D40" t="n">
-        <v>46</v>
-      </c>
-      <c r="E40">
-        <f>D40-D39</f>
-        <v/>
-      </c>
-      <c r="F40" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G40">
-        <f>E40/F40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B41" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C41" t="n">
+      <c r="C46" s="124" t="n">
         <v>10</v>
       </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B42" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C42" t="n">
-        <v>10</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E42">
-        <f>D42-D41</f>
-        <v/>
-      </c>
-      <c r="F42" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G42" s="61">
-        <f>E42/F42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B43" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C43" t="n">
-        <v>10</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E43">
-        <f>D43-D11</f>
-        <v/>
-      </c>
-      <c r="F43" t="n">
+      <c r="D46" s="124" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E46" s="124">
+        <f>D46-D45</f>
+        <v/>
+      </c>
+      <c r="F46" s="124" t="n">
         <v>0.1</v>
       </c>
-      <c r="G43">
-        <f>E43/F43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B44" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C44" t="n">
-        <v>10</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E44">
-        <f>D44-D43</f>
-        <v/>
-      </c>
-      <c r="F44" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G44">
-        <f>E44/F44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B45" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C45" t="n">
-        <v>10</v>
-      </c>
-      <c r="D45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45">
-        <f>D45-D44</f>
-        <v/>
-      </c>
-      <c r="F45" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G45">
-        <f>E45/F45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B46" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C46" t="n">
-        <v>10</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E46">
-        <f>D46-D45</f>
-        <v/>
-      </c>
-      <c r="F46" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G46">
+      <c r="G46" s="170">
         <f>E46/F46</f>
         <v/>
       </c>
+      <c r="H46" s="124" t="n"/>
+      <c r="I46" s="124" t="n"/>
+      <c r="J46" s="124" t="n"/>
+      <c r="K46" s="124" t="n"/>
+      <c r="L46" s="124" t="n"/>
+      <c r="M46" s="124" t="n"/>
+      <c r="N46" s="124" t="n"/>
+      <c r="O46" s="124" t="n"/>
+      <c r="P46" s="124" t="n"/>
+      <c r="Q46" s="124" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>ed04</t>
-        </is>
-      </c>
-      <c r="B47" s="60" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C47" t="n">
-        <v>10</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E47">
-        <f>D47-D46</f>
-        <v/>
-      </c>
-      <c r="F47" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G47" s="61">
-        <f>E47/F47</f>
-        <v/>
-      </c>
+      <c r="A47" s="124" t="n"/>
+      <c r="B47" s="169" t="n"/>
+      <c r="C47" s="124" t="n"/>
+      <c r="D47" s="124" t="n"/>
+      <c r="E47" s="124" t="n"/>
+      <c r="F47" s="124" t="n"/>
+      <c r="G47" s="124" t="n"/>
+      <c r="H47" s="124" t="n"/>
+      <c r="I47" s="124" t="n"/>
+      <c r="J47" s="124" t="n"/>
+      <c r="K47" s="124" t="n"/>
+      <c r="L47" s="124" t="n"/>
+      <c r="M47" s="124" t="n"/>
+      <c r="N47" s="124" t="n"/>
+      <c r="O47" s="124" t="n"/>
+      <c r="P47" s="124" t="n"/>
+      <c r="Q47" s="124" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="60" t="n"/>
+      <c r="A48" s="124" t="n"/>
+      <c r="B48" s="124" t="n"/>
+      <c r="C48" s="124" t="n"/>
+      <c r="D48" s="124" t="n"/>
+      <c r="E48" s="124" t="n"/>
+      <c r="F48" s="124" t="n"/>
+      <c r="G48" s="124" t="n"/>
+      <c r="H48" s="124" t="n"/>
+      <c r="I48" s="124" t="n"/>
+      <c r="J48" s="124" t="n"/>
+      <c r="K48" s="124" t="n"/>
+      <c r="L48" s="124" t="n"/>
+      <c r="M48" s="124" t="n"/>
+      <c r="N48" s="124" t="n"/>
+      <c r="O48" s="124" t="n"/>
+      <c r="P48" s="124" t="n"/>
+      <c r="Q48" s="124" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="174" t="n"/>
+      <c r="B49" s="124" t="n"/>
+      <c r="C49" s="124" t="n"/>
+      <c r="D49" s="124" t="n"/>
+      <c r="E49" s="124" t="n"/>
+      <c r="F49" s="124" t="n"/>
+      <c r="G49" s="124" t="n"/>
+      <c r="H49" s="124" t="n"/>
+      <c r="I49" s="124" t="n"/>
+      <c r="J49" s="124" t="n"/>
+      <c r="K49" s="124" t="n"/>
+      <c r="L49" s="124" t="n"/>
+      <c r="M49" s="124" t="n"/>
+      <c r="N49" s="124" t="n"/>
+      <c r="O49" s="124" t="n"/>
+      <c r="P49" s="124" t="n"/>
+      <c r="Q49" s="124" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="67" t="n"/>
+      <c r="A50" s="166" t="n"/>
+      <c r="B50" s="166" t="n"/>
+      <c r="C50" s="166" t="n"/>
+      <c r="D50" s="166" t="n"/>
+      <c r="E50" s="166" t="n"/>
+      <c r="F50" s="124" t="n"/>
+      <c r="G50" s="124" t="n"/>
+      <c r="H50" s="124" t="n"/>
+      <c r="I50" s="124" t="n"/>
+      <c r="J50" s="124" t="n"/>
+      <c r="K50" s="124" t="n"/>
+      <c r="L50" s="124" t="n"/>
+      <c r="M50" s="124" t="n"/>
+      <c r="N50" s="124" t="n"/>
+      <c r="O50" s="124" t="n"/>
+      <c r="P50" s="124" t="n"/>
+      <c r="Q50" s="124" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="63" t="n"/>
-      <c r="B51" s="63" t="n"/>
-      <c r="C51" s="63" t="n"/>
-      <c r="D51" s="63" t="n"/>
-      <c r="E51" s="63" t="n"/>
+      <c r="A51" s="124" t="n"/>
+      <c r="B51" s="171" t="n"/>
+      <c r="C51" s="124" t="n"/>
+      <c r="D51" s="124" t="n"/>
+      <c r="E51" s="124" t="n"/>
+      <c r="F51" s="124" t="n"/>
+      <c r="G51" s="124" t="n"/>
+      <c r="H51" s="124" t="n"/>
+      <c r="I51" s="124" t="n"/>
+      <c r="J51" s="124" t="n"/>
+      <c r="K51" s="124" t="n"/>
+      <c r="L51" s="124" t="n"/>
+      <c r="M51" s="124" t="n"/>
+      <c r="N51" s="124" t="n"/>
+      <c r="O51" s="124" t="n"/>
+      <c r="P51" s="124" t="n"/>
+      <c r="Q51" s="124" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="108" t="n"/>
+      <c r="A52" s="173" t="n"/>
+      <c r="B52" s="124" t="n"/>
+      <c r="C52" s="124" t="n"/>
+      <c r="D52" s="124" t="n"/>
+      <c r="E52" s="124" t="n"/>
+      <c r="F52" s="124" t="n"/>
+      <c r="G52" s="124" t="n"/>
+      <c r="H52" s="124" t="n"/>
+      <c r="I52" s="124" t="n"/>
+      <c r="J52" s="124" t="n"/>
+      <c r="K52" s="124" t="n"/>
+      <c r="L52" s="124" t="n"/>
+      <c r="M52" s="124" t="n"/>
+      <c r="N52" s="124" t="n"/>
+      <c r="O52" s="124" t="n"/>
+      <c r="P52" s="124" t="n"/>
+      <c r="Q52" s="124" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="66" t="n"/>
+      <c r="A53" s="124" t="n"/>
+      <c r="B53" s="124" t="n"/>
+      <c r="C53" s="124" t="n"/>
+      <c r="D53" s="124" t="n"/>
+      <c r="E53" s="124" t="n"/>
+      <c r="F53" s="124" t="n"/>
+      <c r="G53" s="124" t="n"/>
+      <c r="H53" s="124" t="n"/>
+      <c r="I53" s="124" t="n"/>
+      <c r="J53" s="124" t="n"/>
+      <c r="K53" s="124" t="n"/>
+      <c r="L53" s="124" t="n"/>
+      <c r="M53" s="124" t="n"/>
+      <c r="N53" s="124" t="n"/>
+      <c r="O53" s="124" t="n"/>
+      <c r="P53" s="124" t="n"/>
+      <c r="Q53" s="124" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="174" t="n"/>
+      <c r="B54" s="124" t="n"/>
+      <c r="C54" s="124" t="n"/>
+      <c r="D54" s="124" t="n"/>
+      <c r="E54" s="124" t="n"/>
+      <c r="F54" s="124" t="n"/>
+      <c r="G54" s="124" t="n"/>
+      <c r="H54" s="124" t="n"/>
+      <c r="I54" s="124" t="n"/>
+      <c r="J54" s="124" t="n"/>
+      <c r="K54" s="124" t="n"/>
+      <c r="L54" s="124" t="n"/>
+      <c r="M54" s="124" t="n"/>
+      <c r="N54" s="124" t="n"/>
+      <c r="O54" s="124" t="n"/>
+      <c r="P54" s="124" t="n"/>
+      <c r="Q54" s="124" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="67" t="n"/>
+      <c r="A55" s="124" t="n"/>
+      <c r="B55" s="124" t="n"/>
+      <c r="C55" s="124" t="n"/>
+      <c r="D55" s="124" t="n"/>
+      <c r="E55" s="124" t="n"/>
+      <c r="F55" s="124" t="n"/>
+      <c r="G55" s="124" t="n"/>
+      <c r="H55" s="124" t="n"/>
+      <c r="I55" s="124" t="n"/>
+      <c r="J55" s="124" t="n"/>
+      <c r="K55" s="124" t="n"/>
+      <c r="L55" s="124" t="n"/>
+      <c r="M55" s="124" t="n"/>
+      <c r="N55" s="124" t="n"/>
+      <c r="O55" s="124" t="n"/>
+      <c r="P55" s="124" t="n"/>
+      <c r="Q55" s="124" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="124" t="n"/>
+      <c r="B56" s="124" t="n"/>
+      <c r="C56" s="124" t="n"/>
+      <c r="D56" s="124" t="n"/>
+      <c r="E56" s="124" t="n"/>
+      <c r="F56" s="124" t="n"/>
+      <c r="G56" s="124" t="n"/>
+      <c r="H56" s="124" t="n"/>
+      <c r="I56" s="124" t="n"/>
+      <c r="J56" s="124" t="n"/>
+      <c r="K56" s="124" t="n"/>
+      <c r="L56" s="124" t="n"/>
+      <c r="M56" s="124" t="n"/>
+      <c r="N56" s="124" t="n"/>
+      <c r="O56" s="124" t="n"/>
+      <c r="P56" s="124" t="n"/>
+      <c r="Q56" s="124" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="124" t="n"/>
+      <c r="B57" s="124" t="n"/>
+      <c r="C57" s="124" t="n"/>
+      <c r="D57" s="124" t="n"/>
+      <c r="E57" s="124" t="n"/>
+      <c r="F57" s="124" t="n"/>
+      <c r="G57" s="124" t="n"/>
+      <c r="H57" s="124" t="n"/>
+      <c r="I57" s="124" t="n"/>
+      <c r="J57" s="124" t="n"/>
+      <c r="K57" s="124" t="n"/>
+      <c r="L57" s="124" t="n"/>
+      <c r="M57" s="124" t="n"/>
+      <c r="N57" s="124" t="n"/>
+      <c r="O57" s="124" t="n"/>
+      <c r="P57" s="124" t="n"/>
+      <c r="Q57" s="124" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="124" t="n"/>
+      <c r="B58" s="124" t="n"/>
+      <c r="C58" s="124" t="n"/>
+      <c r="D58" s="124" t="n"/>
+      <c r="E58" s="124" t="n"/>
+      <c r="F58" s="124" t="n"/>
+      <c r="G58" s="124" t="n"/>
+      <c r="H58" s="124" t="n"/>
+      <c r="I58" s="124" t="n"/>
+      <c r="J58" s="124" t="n"/>
+      <c r="K58" s="124" t="n"/>
+      <c r="L58" s="124" t="n"/>
+      <c r="M58" s="124" t="n"/>
+      <c r="N58" s="124" t="n"/>
+      <c r="O58" s="124" t="n"/>
+      <c r="P58" s="124" t="n"/>
+      <c r="Q58" s="124" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="124" t="n"/>
+      <c r="B59" s="124" t="n"/>
+      <c r="C59" s="124" t="n"/>
+      <c r="D59" s="124" t="n"/>
+      <c r="E59" s="124" t="n"/>
+      <c r="F59" s="124" t="n"/>
+      <c r="G59" s="124" t="n"/>
+      <c r="H59" s="124" t="n"/>
+      <c r="I59" s="124" t="n"/>
+      <c r="J59" s="124" t="n"/>
+      <c r="K59" s="124" t="n"/>
+      <c r="L59" s="124" t="n"/>
+      <c r="M59" s="124" t="n"/>
+      <c r="N59" s="124" t="n"/>
+      <c r="O59" s="124" t="n"/>
+      <c r="P59" s="124" t="n"/>
+      <c r="Q59" s="124" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="124" t="n"/>
+      <c r="B60" s="124" t="n"/>
+      <c r="C60" s="124" t="n"/>
+      <c r="D60" s="124" t="n"/>
+      <c r="E60" s="124" t="n"/>
+      <c r="F60" s="124" t="n"/>
+      <c r="G60" s="124" t="n"/>
+      <c r="H60" s="124" t="n"/>
+      <c r="I60" s="124" t="n"/>
+      <c r="J60" s="124" t="n"/>
+      <c r="K60" s="124" t="n"/>
+      <c r="L60" s="124" t="n"/>
+      <c r="M60" s="124" t="n"/>
+      <c r="N60" s="124" t="n"/>
+      <c r="O60" s="124" t="n"/>
+      <c r="P60" s="124" t="n"/>
+      <c r="Q60" s="124" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="124" t="n"/>
+      <c r="B61" s="124" t="n"/>
+      <c r="C61" s="124" t="n"/>
+      <c r="D61" s="124" t="n"/>
+      <c r="E61" s="124" t="n"/>
+      <c r="F61" s="124" t="n"/>
+      <c r="G61" s="124" t="n"/>
+      <c r="H61" s="124" t="n"/>
+      <c r="I61" s="124" t="n"/>
+      <c r="J61" s="124" t="n"/>
+      <c r="K61" s="124" t="n"/>
+      <c r="L61" s="124" t="n"/>
+      <c r="M61" s="124" t="n"/>
+      <c r="N61" s="124" t="n"/>
+      <c r="O61" s="124" t="n"/>
+      <c r="P61" s="124" t="n"/>
+      <c r="Q61" s="124" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="124" t="n"/>
+      <c r="B62" s="124" t="n"/>
+      <c r="C62" s="124" t="n"/>
+      <c r="D62" s="124" t="n"/>
+      <c r="E62" s="124" t="n"/>
+      <c r="F62" s="124" t="n"/>
+      <c r="G62" s="124" t="n"/>
+      <c r="H62" s="124" t="n"/>
+      <c r="I62" s="124" t="n"/>
+      <c r="J62" s="124" t="n"/>
+      <c r="K62" s="124" t="n"/>
+      <c r="L62" s="124" t="n"/>
+      <c r="M62" s="124" t="n"/>
+      <c r="N62" s="124" t="n"/>
+      <c r="O62" s="124" t="n"/>
+      <c r="P62" s="124" t="n"/>
+      <c r="Q62" s="124" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="124" t="n"/>
+      <c r="B63" s="124" t="n"/>
+      <c r="C63" s="124" t="n"/>
+      <c r="D63" s="124" t="n"/>
+      <c r="E63" s="124" t="n"/>
+      <c r="F63" s="124" t="n"/>
+      <c r="G63" s="124" t="n"/>
+      <c r="H63" s="124" t="n"/>
+      <c r="I63" s="124" t="n"/>
+      <c r="J63" s="124" t="n"/>
+      <c r="K63" s="124" t="n"/>
+      <c r="L63" s="124" t="n"/>
+      <c r="M63" s="124" t="n"/>
+      <c r="N63" s="124" t="n"/>
+      <c r="O63" s="124" t="n"/>
+      <c r="P63" s="124" t="n"/>
+      <c r="Q63" s="124" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="124" t="n"/>
+      <c r="B64" s="124" t="n"/>
+      <c r="C64" s="124" t="n"/>
+      <c r="D64" s="124" t="n"/>
+      <c r="E64" s="124" t="n"/>
+      <c r="F64" s="124" t="n"/>
+      <c r="G64" s="124" t="n"/>
+      <c r="H64" s="124" t="n"/>
+      <c r="I64" s="124" t="n"/>
+      <c r="J64" s="124" t="n"/>
+      <c r="K64" s="124" t="n"/>
+      <c r="L64" s="124" t="n"/>
+      <c r="M64" s="124" t="n"/>
+      <c r="N64" s="124" t="n"/>
+      <c r="O64" s="124" t="n"/>
+      <c r="P64" s="124" t="n"/>
+      <c r="Q64" s="124" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="124" t="n"/>
+      <c r="B65" s="124" t="n"/>
+      <c r="C65" s="124" t="n"/>
+      <c r="D65" s="124" t="n"/>
+      <c r="E65" s="124" t="n"/>
+      <c r="F65" s="124" t="n"/>
+      <c r="G65" s="124" t="n"/>
+      <c r="H65" s="124" t="n"/>
+      <c r="I65" s="124" t="n"/>
+      <c r="J65" s="124" t="n"/>
+      <c r="K65" s="124" t="n"/>
+      <c r="L65" s="124" t="n"/>
+      <c r="M65" s="124" t="n"/>
+      <c r="N65" s="124" t="n"/>
+      <c r="O65" s="124" t="n"/>
+      <c r="P65" s="124" t="n"/>
+      <c r="Q65" s="124" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="124" t="n"/>
+      <c r="B66" s="124" t="n"/>
+      <c r="C66" s="124" t="n"/>
+      <c r="D66" s="124" t="n"/>
+      <c r="E66" s="124" t="n"/>
+      <c r="F66" s="124" t="n"/>
+      <c r="G66" s="124" t="n"/>
+      <c r="H66" s="124" t="n"/>
+      <c r="I66" s="124" t="n"/>
+      <c r="J66" s="124" t="n"/>
+      <c r="K66" s="124" t="n"/>
+      <c r="L66" s="124" t="n"/>
+      <c r="M66" s="124" t="n"/>
+      <c r="N66" s="124" t="n"/>
+      <c r="O66" s="124" t="n"/>
+      <c r="P66" s="124" t="n"/>
+      <c r="Q66" s="124" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="124" t="n"/>
+      <c r="B67" s="124" t="n"/>
+      <c r="C67" s="124" t="n"/>
+      <c r="D67" s="124" t="n"/>
+      <c r="E67" s="124" t="n"/>
+      <c r="F67" s="124" t="n"/>
+      <c r="G67" s="124" t="n"/>
+      <c r="H67" s="124" t="n"/>
+      <c r="I67" s="124" t="n"/>
+      <c r="J67" s="124" t="n"/>
+      <c r="K67" s="124" t="n"/>
+      <c r="L67" s="124" t="n"/>
+      <c r="M67" s="124" t="n"/>
+      <c r="N67" s="124" t="n"/>
+      <c r="O67" s="124" t="n"/>
+      <c r="P67" s="124" t="n"/>
+      <c r="Q67" s="124" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="124" t="n"/>
+      <c r="B68" s="124" t="n"/>
+      <c r="C68" s="124" t="n"/>
+      <c r="D68" s="124" t="n"/>
+      <c r="E68" s="124" t="n"/>
+      <c r="F68" s="124" t="n"/>
+      <c r="G68" s="124" t="n"/>
+      <c r="H68" s="124" t="n"/>
+      <c r="I68" s="124" t="n"/>
+      <c r="J68" s="124" t="n"/>
+      <c r="K68" s="124" t="n"/>
+      <c r="L68" s="124" t="n"/>
+      <c r="M68" s="124" t="n"/>
+      <c r="N68" s="124" t="n"/>
+      <c r="O68" s="124" t="n"/>
+      <c r="P68" s="124" t="n"/>
+      <c r="Q68" s="124" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="124" t="n"/>
+      <c r="B69" s="124" t="n"/>
+      <c r="C69" s="124" t="n"/>
+      <c r="D69" s="124" t="n"/>
+      <c r="E69" s="124" t="n"/>
+      <c r="F69" s="124" t="n"/>
+      <c r="G69" s="124" t="n"/>
+      <c r="H69" s="124" t="n"/>
+      <c r="I69" s="124" t="n"/>
+      <c r="J69" s="124" t="n"/>
+      <c r="K69" s="124" t="n"/>
+      <c r="L69" s="124" t="n"/>
+      <c r="M69" s="124" t="n"/>
+      <c r="N69" s="124" t="n"/>
+      <c r="O69" s="124" t="n"/>
+      <c r="P69" s="124" t="n"/>
+      <c r="Q69" s="124" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="124" t="n"/>
+      <c r="B70" s="124" t="n"/>
+      <c r="C70" s="124" t="n"/>
+      <c r="D70" s="124" t="n"/>
+      <c r="E70" s="124" t="n"/>
+      <c r="F70" s="124" t="n"/>
+      <c r="G70" s="124" t="n"/>
+      <c r="H70" s="124" t="n"/>
+      <c r="I70" s="124" t="n"/>
+      <c r="J70" s="124" t="n"/>
+      <c r="K70" s="124" t="n"/>
+      <c r="L70" s="124" t="n"/>
+      <c r="M70" s="124" t="n"/>
+      <c r="N70" s="124" t="n"/>
+      <c r="O70" s="124" t="n"/>
+      <c r="P70" s="124" t="n"/>
+      <c r="Q70" s="124" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="124" t="n"/>
+      <c r="B71" s="124" t="n"/>
+      <c r="C71" s="124" t="n"/>
+      <c r="D71" s="124" t="n"/>
+      <c r="E71" s="124" t="n"/>
+      <c r="F71" s="124" t="n"/>
+      <c r="G71" s="124" t="n"/>
+      <c r="H71" s="124" t="n"/>
+      <c r="I71" s="124" t="n"/>
+      <c r="J71" s="124" t="n"/>
+      <c r="K71" s="124" t="n"/>
+      <c r="L71" s="124" t="n"/>
+      <c r="M71" s="124" t="n"/>
+      <c r="N71" s="124" t="n"/>
+      <c r="O71" s="124" t="n"/>
+      <c r="P71" s="124" t="n"/>
+      <c r="Q71" s="124" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="173" t="n"/>
+      <c r="B72" s="124" t="n"/>
+      <c r="C72" s="124" t="n"/>
+      <c r="D72" s="124" t="n"/>
+      <c r="E72" s="124" t="n"/>
+      <c r="F72" s="124" t="n"/>
+      <c r="G72" s="124" t="n"/>
+      <c r="H72" s="124" t="n"/>
+      <c r="I72" s="124" t="n"/>
+      <c r="J72" s="124" t="n"/>
+      <c r="K72" s="124" t="n"/>
+      <c r="L72" s="124" t="n"/>
+      <c r="M72" s="124" t="n"/>
+      <c r="N72" s="124" t="n"/>
+      <c r="O72" s="124" t="n"/>
+      <c r="P72" s="124" t="n"/>
+      <c r="Q72" s="124" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="66" t="n"/>
+      <c r="A73" s="173" t="n"/>
+      <c r="B73" s="124" t="n"/>
+      <c r="C73" s="124" t="n"/>
+      <c r="D73" s="124" t="n"/>
+      <c r="E73" s="124" t="n"/>
+      <c r="F73" s="124" t="n"/>
+      <c r="G73" s="124" t="n"/>
+      <c r="H73" s="124" t="n"/>
+      <c r="I73" s="124" t="n"/>
+      <c r="J73" s="124" t="n"/>
+      <c r="K73" s="124" t="n"/>
+      <c r="L73" s="124" t="n"/>
+      <c r="M73" s="124" t="n"/>
+      <c r="N73" s="124" t="n"/>
+      <c r="O73" s="124" t="n"/>
+      <c r="P73" s="124" t="n"/>
+      <c r="Q73" s="124" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="66" t="n"/>
+      <c r="A74" s="124" t="n"/>
+      <c r="B74" s="124" t="n"/>
+      <c r="C74" s="124" t="n"/>
+      <c r="D74" s="124" t="n"/>
+      <c r="E74" s="124" t="n"/>
+      <c r="F74" s="124" t="n"/>
+      <c r="G74" s="124" t="n"/>
+      <c r="H74" s="124" t="n"/>
+      <c r="I74" s="124" t="n"/>
+      <c r="J74" s="124" t="n"/>
+      <c r="K74" s="124" t="n"/>
+      <c r="L74" s="124" t="n"/>
+      <c r="M74" s="124" t="n"/>
+      <c r="N74" s="124" t="n"/>
+      <c r="O74" s="124" t="n"/>
+      <c r="P74" s="124" t="n"/>
+      <c r="Q74" s="124" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="174" t="n"/>
+      <c r="B75" s="124" t="n"/>
+      <c r="C75" s="124" t="n"/>
+      <c r="D75" s="124" t="n"/>
+      <c r="E75" s="124" t="n"/>
+      <c r="F75" s="124" t="n"/>
+      <c r="G75" s="124" t="n"/>
+      <c r="H75" s="124" t="n"/>
+      <c r="I75" s="124" t="n"/>
+      <c r="J75" s="124" t="n"/>
+      <c r="K75" s="124" t="n"/>
+      <c r="L75" s="124" t="n"/>
+      <c r="M75" s="124" t="n"/>
+      <c r="N75" s="124" t="n"/>
+      <c r="O75" s="124" t="n"/>
+      <c r="P75" s="124" t="n"/>
+      <c r="Q75" s="124" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="67" t="n"/>
+      <c r="A76" s="61" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G5:G47 I5:I48">

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t>Time between doses (conservative, O2-safe). The 'interval can be relaxed?' check below says if you can dose less often.</t>
+          <t>Time between doses. Now credits surface O2 stripping (kL_surf proxy); when surface handles the O2 this is carbon-limited. Refine via the kL_surf measurement.</t>
         </is>
       </c>
     </row>
@@ -10131,12 +10131,12 @@
         </is>
       </c>
       <c r="D87" s="61">
-        <f>O2_net_gen/(target_DO_frac*(O2_ceil_Pa/P_atm))/(nCO2_rate*3600)</f>
+        <f>MAX(0,O2_net_gen-surf_strip)/(target_DO_frac*(O2_ceil_Pa/P_atm))/(nCO2_rate*3600)</f>
         <v/>
       </c>
       <c r="E87" s="131" t="inlineStr">
         <is>
-          <t>Duty so the vented CO₂ throughput carries the worst-case (lag, no uptake) net O₂ out at ≤ target DO. Usually the binding floor.</t>
+          <t>O2 the sparge must vent = net O2 minus surface stripping (proxy); 0 when surface stripping alone holds DO</t>
         </is>
       </c>
       <c r="F87" s="20" t="n"/>
@@ -10185,12 +10185,12 @@
         </is>
       </c>
       <c r="D89" s="61">
-        <f>target_DO_frac*t_O2_ceiling_lag</f>
+        <f>target_DO_frac*O2_ceil_C*(V_charge/1000000)/MAX(0.000000000001,O2_net_gen-surf_strip)*60</f>
         <v/>
       </c>
       <c r="E89" s="131" t="inlineStr">
         <is>
-          <t>Pulses must be frequent enough that DO doesn't spike past target between flushes (lag worst-case).</t>
+          <t>O2-limited interval, now crediting surface stripping (surf_strip from the kL_surf proxy) rather than assuming zero; refine by measuring kL_surf</t>
         </is>
       </c>
       <c r="F89" s="20" t="n"/>

--- a/Media/electroPioreactorGasModel-modular.xlsx
+++ b/Media/electroPioreactorGasModel-modular.xlsx
@@ -1142,7 +1142,7 @@
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="26">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1318,6 +1318,30 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2204,7 +2228,7 @@
       <c r="B26" s="20" t="n"/>
       <c r="C26" s="20" t="n"/>
       <c r="D26" s="118">
-        <f>IFERROR(IF('Mass Transfer'!$D$126&gt;=1,"OK","UNDER (CO2 &lt; demand)"),"calibrate this reactor first")</f>
+        <f>IFERROR(IF('Mass Transfer'!$D$126&gt;=1,"OK","SHORTFALL (CO2 &lt; demand)"),"calibrate this reactor first")</f>
         <v/>
       </c>
       <c r="E26" s="24">
@@ -2951,14 +2975,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:D33">
-    <cfRule type="expression" priority="11" dxfId="15" stopIfTrue="1">
-      <formula>OR(ISNUMBER(SEARCH("INCONSISTENT",D19)),ISNUMBER(SEARCH("OVER",D19)),ISNUMBER(SEARCH("BELOW",D19)),ISNUMBER(SEARCH("EXCEED",D19)),ISNUMBER(SEARCH("NO CALIB",D19)),ISNUMBER(SEARCH("calibrate this",D19)),ISNUMBER(SEARCH("RISK",D19)),ISNUMBER(SEARCH("EXPLOSIVE",D19)),ISNUMBER(SEARCH("OOR",D19)),ISNUMBER(SEARCH("insufficient",D19)),ISNUMBER(SEARCH("TIP SPEED",D19)),ISNUMBER(SEARCH("UNDER",D19)),EXACT(D19,"OUT"),EXACT(D19,"LOW"))</formula>
+    <cfRule type="expression" priority="11" dxfId="23" stopIfTrue="1">
+      <formula>OR(ISNUMBER(SEARCH("INCONSISTENT",D19)),ISNUMBER(SEARCH("OVER",D19)),ISNUMBER(SEARCH("BELOW",D19)),ISNUMBER(SEARCH("EXCEED",D19)),ISNUMBER(SEARCH("NO CALIB",D19)),ISNUMBER(SEARCH("calibrate this",D19)),ISNUMBER(SEARCH("RISK",D19)),ISNUMBER(SEARCH("EXPLOSIVE",D19)),ISNUMBER(SEARCH("OOR",D19)),ISNUMBER(SEARCH("insufficient",D19)),ISNUMBER(SEARCH("TIP SPEED",D19)),ISNUMBER(SEARCH("SHORTFALL",D19)),EXACT(D19,"OUT"),EXACT(D19,"LOW"))</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" dxfId="14" stopIfTrue="1">
+    <cfRule type="expression" priority="12" dxfId="24" stopIfTrue="1">
       <formula>OR(ISNUMBER(SEARCH("above optimum",D19)),ISNUMBER(SEARCH("watch",D19)),ISNUMBER(SEARCH("NEAREST",D19)),ISNUMBER(SEARCH("unknown",D19)),ISNUMBER(SEARCH("TIGHT",D19)))</formula>
     </cfRule>
-    <cfRule type="expression" priority="13" dxfId="13" stopIfTrue="1">
-      <formula>OR(EXACT(D19,"OK"),ISNUMBER(SEARCH("calibrated:",D19)),ISNUMBER(SEARCH("under optimum",D19)),ISNUMBER(SEARCH("above min",D19)),ISNUMBER(SEARCH("CARBON-limited",D19)),ISNUMBER(SEARCH("Static",D19)),ISNUMBER(SEARCH("Dynamic",D19)))</formula>
+    <cfRule type="expression" priority="13" dxfId="25" stopIfTrue="1">
+      <formula>OR(EXACT(D19,"OK"),ISNUMBER(SEARCH("calibrated:",D19)),ISNUMBER(SEARCH("optimum",D19)),ISNUMBER(SEARCH("above min",D19)),ISNUMBER(SEARCH("CARBON-limited",D19)),ISNUMBER(SEARCH("Static",D19)),ISNUMBER(SEARCH("Dynamic",D19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
